--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SUTIScompras\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maurofilho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216C238E-AEED-4878-8B34-6C601AAF8CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6018E3-D313-4BEC-8135-F1BDE64769C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-825" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="496">
   <si>
     <t>Departamento</t>
   </si>
@@ -843,7 +843,10 @@
     <t>SISLOG 122001 - Aquisição de Workstations</t>
   </si>
   <si>
-    <t>MINUTA CONTRATO E TERMO DE HOMOLOGAÇÃO EM DIGITAÇÃO</t>
+    <t>GEFIN CACTIC</t>
+  </si>
+  <si>
+    <t>para conhecimento e providências.</t>
   </si>
   <si>
     <t>Aquisição</t>
@@ -870,187 +873,199 @@
     <t>SISLOG 121437 KIT MOUSE E TECLADO COM FIO</t>
   </si>
   <si>
+    <t>GELIC</t>
+  </si>
+  <si>
+    <t>GEIN</t>
+  </si>
+  <si>
+    <t>202600010030662</t>
+  </si>
+  <si>
+    <t>Sislog 120082 -Ingressos do CONSAD-feito pelo GECG</t>
+  </si>
+  <si>
+    <t>ANEXO II</t>
+  </si>
+  <si>
+    <t>202600005015076</t>
+  </si>
+  <si>
+    <t>119902 Ingresso participação no Simpósio SBCAS 2026</t>
+  </si>
+  <si>
+    <t>Emitida a nota de empenho, encaminhem-se os autos à SUTIS para conhecimento e demais providências cabíveis.</t>
+  </si>
+  <si>
+    <t>202600005015052</t>
+  </si>
+  <si>
+    <t>119899 - Aquisição de ingresso para a participação no Simpósio Brasileiro de Sistemas de Informação (SBSI)</t>
+  </si>
+  <si>
+    <t>202500005019071</t>
+  </si>
+  <si>
+    <t>SISLOG 114940  - Kits Mouse &amp; teclado com fio/sem fio</t>
+  </si>
+  <si>
+    <t>Comunicamos que o julgamento do Pregão Eletrônico 173/2025, objeto em epígrafe, realizar-se-á dia 14/10/2025 (terça-feira) às 09:00 h,</t>
+  </si>
+  <si>
+    <t>202400005028451</t>
+  </si>
+  <si>
+    <t>SISLOG 108212 estabilizador de tensão, potência mínima de 500 va, tensão de 220 v, capacidade mínima para 4 tomada - SEI nº 202500010009280 - Digitalizado e encaminhado a GCC</t>
+  </si>
+  <si>
+    <t>Extrato de Publicação - Contrato 13 (71284812). E-mail 71304720 ao fornecedor.contato@brasillprodutos.com.br. Aguardando a publicação no PNCP para o início da contagem da vigência, conforme a Cláusula Quarta.</t>
+  </si>
+  <si>
+    <t>13/2025</t>
+  </si>
+  <si>
+    <t>202500005000064</t>
+  </si>
+  <si>
+    <t>SISLOG 111806 CERTIFICADOS DIGITAIS PROCESSO PRÉVIO  202400010046932. Processo paralelo da contratação: SEI 202500010039434.</t>
+  </si>
+  <si>
+    <t>CONTRATO EM GESTÃO DA GETEC</t>
+  </si>
+  <si>
+    <t>50/2025</t>
+  </si>
+  <si>
+    <t>202400010051978</t>
+  </si>
+  <si>
+    <t>Aquisição de Suprimentos de Informática diversos, Estabilizador ,Pen drive - 32 GBHeadset (Fone de ouvido) derivado da Ata de Registro de Preços nº 004/2024 - SEAD/GECC resultante do Pregão Eletrônico 'SRP' nº 001/2023 (processo SEI nº 202100005019301). Aditivo ao Contrato nº 113/2024/SES no percentual de 25% (vinte e cinco por cento) – BRASLYNC</t>
+  </si>
+  <si>
+    <t>113/2024</t>
+  </si>
+  <si>
+    <t>202500010034499</t>
+  </si>
+  <si>
+    <t>ADESÃO A ARP PARA AQUISIÇÃO DE WORKSTATION PARA O LACEN</t>
+  </si>
+  <si>
+    <t>Está no LACEN para gestão CONTRATO</t>
+  </si>
+  <si>
+    <t>202500005035836</t>
+  </si>
+  <si>
+    <t>SISLOG 117278 - Aquisição de kits de Mouse e Teclado com e sem fio</t>
+  </si>
+  <si>
+    <t>houve a apresentação de propostas, as quais foram todas desclassificadas e/ou os licitantes inabilitados, inviabilizando a adjudicação do objeto, declaro o certame FRACASSADO.</t>
+  </si>
+  <si>
+    <t>SESG</t>
+  </si>
+  <si>
+    <t>202400005045335</t>
+  </si>
+  <si>
+    <t>SISLOG nº 110808 gestão de competências Software GALERA.APP LEME CONSULTORIA EM GESTÃO DE RH LTDA. PROCESSO SEI PARALELO 202500010040069</t>
+  </si>
+  <si>
+    <t>PARA RENOVAÇÃO</t>
+  </si>
+  <si>
+    <t>52/2025</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>FORNECEDOR VOGEL ALGAR. PROC - Serviços de telecomunicações para tráfego de dados</t>
+  </si>
+  <si>
+    <t>22/2020</t>
+  </si>
+  <si>
+    <t>202600005022365</t>
+  </si>
+  <si>
+    <t>SISLOG 121388 GALERA APP</t>
+  </si>
+  <si>
+    <t>Envio para elaboração da Portaria e do Termo de Referência</t>
+  </si>
+  <si>
+    <t>202500005030582</t>
+  </si>
+  <si>
+    <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 11</t>
+  </si>
+  <si>
+    <t>GESTÃO DAS AREAS RESPONSÁVEIS</t>
+  </si>
+  <si>
+    <t>11/2026</t>
+  </si>
+  <si>
+    <t>202500010031707</t>
+  </si>
+  <si>
+    <t>Aditivo 25% Moniotres 24P AOC , total 109 monitores</t>
+  </si>
+  <si>
+    <t>SOB GESTÃO DA GETEC</t>
+  </si>
+  <si>
+    <t>62/2025</t>
+  </si>
+  <si>
+    <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 9</t>
+  </si>
+  <si>
+    <t>GECORSET</t>
+  </si>
+  <si>
+    <t>para conhecimento e providências que julgar cabíveis.</t>
+  </si>
+  <si>
+    <t>09/2026</t>
+  </si>
+  <si>
+    <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 10</t>
+  </si>
+  <si>
+    <t>10/2026</t>
+  </si>
+  <si>
+    <t>21/2020</t>
+  </si>
+  <si>
+    <t>202600005028401</t>
+  </si>
+  <si>
+    <t>SISLOG 122325 - Adesão À ARP 020/2026. 300 monitores 24"</t>
+  </si>
+  <si>
+    <t>DOD E ETP</t>
+  </si>
+  <si>
+    <t>202600005028837</t>
+  </si>
+  <si>
+    <t>SISLOG 122416 - Adesão À ARP 010/2025 MGI. 300 monitores 24"</t>
+  </si>
+  <si>
+    <t>AUTORIZADA ADESÃO PELA UNIDADE GERENCIADORA NO SIASG</t>
+  </si>
+  <si>
+    <t>202600005026702</t>
+  </si>
+  <si>
+    <t>SISLOG 121994- Aquisição Webcam e Headset</t>
+  </si>
+  <si>
     <t>GEFIN</t>
-  </si>
-  <si>
-    <t>PARA PROSSEGUIMENTO</t>
-  </si>
-  <si>
-    <t>GEIN</t>
-  </si>
-  <si>
-    <t>202600010030662</t>
-  </si>
-  <si>
-    <t>Sislog 120082 -Ingressos do CONSAD-feito pelo GECG</t>
-  </si>
-  <si>
-    <t>ANEXO II</t>
-  </si>
-  <si>
-    <t>202600005015076</t>
-  </si>
-  <si>
-    <t>119902 Ingresso participação no Simpósio SBCAS 2026</t>
-  </si>
-  <si>
-    <t>Emitida a nota de empenho, encaminhem-se os autos à SUTIS para conhecimento e demais providências cabíveis.</t>
-  </si>
-  <si>
-    <t>202600005015052</t>
-  </si>
-  <si>
-    <t>119899 - Aquisição de ingresso para a participação no Simpósio Brasileiro de Sistemas de Informação (SBSI)</t>
-  </si>
-  <si>
-    <t>202500005019071</t>
-  </si>
-  <si>
-    <t>SISLOG 114940  - Kits Mouse &amp; teclado com fio/sem fio</t>
-  </si>
-  <si>
-    <t>Comunicamos que o julgamento do Pregão Eletrônico 173/2025, objeto em epígrafe, realizar-se-á dia 14/10/2025 (terça-feira) às 09:00 h,</t>
-  </si>
-  <si>
-    <t>202400005028451</t>
-  </si>
-  <si>
-    <t>SISLOG 108212 estabilizador de tensão, potência mínima de 500 va, tensão de 220 v, capacidade mínima para 4 tomada - SEI nº 202500010009280 - Digitalizado e encaminhado a GCC</t>
-  </si>
-  <si>
-    <t>Extrato de Publicação - Contrato 13 (71284812). E-mail 71304720 ao fornecedor.contato@brasillprodutos.com.br. Aguardando a publicação no PNCP para o início da contagem da vigência, conforme a Cláusula Quarta.</t>
-  </si>
-  <si>
-    <t>13/2025</t>
-  </si>
-  <si>
-    <t>202500005000064</t>
-  </si>
-  <si>
-    <t>SISLOG 111806 CERTIFICADOS DIGITAIS PROCESSO PRÉVIO  202400010046932. Processo paralelo da contratação: SEI 202500010039434.</t>
-  </si>
-  <si>
-    <t>CONTRATO EM GESTÃO DA GETEC</t>
-  </si>
-  <si>
-    <t>50/2025</t>
-  </si>
-  <si>
-    <t>202400010051978</t>
-  </si>
-  <si>
-    <t>Aquisição de Suprimentos de Informática diversos, Estabilizador ,Pen drive - 32 GBHeadset (Fone de ouvido) derivado da Ata de Registro de Preços nº 004/2024 - SEAD/GECC resultante do Pregão Eletrônico 'SRP' nº 001/2023 (processo SEI nº 202100005019301). Aditivo ao Contrato nº 113/2024/SES no percentual de 25% (vinte e cinco por cento) – BRASLYNC</t>
-  </si>
-  <si>
-    <t>113/2024</t>
-  </si>
-  <si>
-    <t>202500010034499</t>
-  </si>
-  <si>
-    <t>ADESÃO A ARP PARA AQUISIÇÃO DE WORKSTATION PARA O LACEN</t>
-  </si>
-  <si>
-    <t>Está no LACEN para gestão CONTRATO</t>
-  </si>
-  <si>
-    <t>202500005035836</t>
-  </si>
-  <si>
-    <t>SISLOG 117278 - Aquisição de kits de Mouse e Teclado com e sem fio</t>
-  </si>
-  <si>
-    <t>GELIC</t>
-  </si>
-  <si>
-    <t>houve a apresentação de propostas, as quais foram todas desclassificadas e/ou os licitantes inabilitados, inviabilizando a adjudicação do objeto, declaro o certame FRACASSADO.</t>
-  </si>
-  <si>
-    <t>SESG</t>
-  </si>
-  <si>
-    <t>202400005045335</t>
-  </si>
-  <si>
-    <t>SISLOG nº 110808 gestão de competências Software GALERA.APP LEME CONSULTORIA EM GESTÃO DE RH LTDA. PROCESSO SEI PARALELO 202500010040069</t>
-  </si>
-  <si>
-    <t>PARA RENOVAÇÃO</t>
-  </si>
-  <si>
-    <t>52/2025</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>FORNECEDOR VOGEL ALGAR. PROC - Serviços de telecomunicações para tráfego de dados</t>
-  </si>
-  <si>
-    <t>22/2020</t>
-  </si>
-  <si>
-    <t>202600005022365</t>
-  </si>
-  <si>
-    <t>SISLOG 121388 GALERA APP</t>
-  </si>
-  <si>
-    <t>Envio para elaboração da Portaria e do Termo de Referência</t>
-  </si>
-  <si>
-    <t>202500005030582</t>
-  </si>
-  <si>
-    <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 11</t>
-  </si>
-  <si>
-    <t>GESTÃO DAS AREAS RESPONSÁVEIS</t>
-  </si>
-  <si>
-    <t>11/2026</t>
-  </si>
-  <si>
-    <t>202500010031707</t>
-  </si>
-  <si>
-    <t>Aditivo 25% Moniotres 24P AOC , total 109 monitores</t>
-  </si>
-  <si>
-    <t>SOB GESTÃO DA GETEC</t>
-  </si>
-  <si>
-    <t>62/2025</t>
-  </si>
-  <si>
-    <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 9</t>
-  </si>
-  <si>
-    <t>GECORSET</t>
-  </si>
-  <si>
-    <t>para conhecimento e providências que julgar cabíveis.</t>
-  </si>
-  <si>
-    <t>09/2026</t>
-  </si>
-  <si>
-    <t>SISLOG 116770 - Licenças de Softwares de prateleira. PROCESSO PARALELO  202600010009927 CCONT CONTRATO 10</t>
-  </si>
-  <si>
-    <t>10/2026</t>
-  </si>
-  <si>
-    <t>21/2020</t>
-  </si>
-  <si>
-    <t>202600005026702</t>
-  </si>
-  <si>
-    <t>SISLOG 121994- Aquisição Webcam e Headset</t>
-  </si>
-  <si>
-    <t>PORTARIA E TERMO DE REFERÊNCIA</t>
   </si>
   <si>
     <t>202500010044120</t>
@@ -1181,6 +1196,15 @@
     <t>64/2025</t>
   </si>
   <si>
+    <t>202600005028258</t>
+  </si>
+  <si>
+    <t>SISLOG 122292 - Adesão À ARP 020/2026. 100 notebooks</t>
+  </si>
+  <si>
+    <t>DOD E ETP OFÍCIO FORNECEDOR</t>
+  </si>
+  <si>
     <t>202300005025650</t>
   </si>
   <si>
@@ -1331,6 +1355,12 @@
     <t>SISLOG 121821 ARP nº 001/2026 do TJ-GO - 500 micromputadores</t>
   </si>
   <si>
+    <t>CACTIC GEPO</t>
+  </si>
+  <si>
+    <t>GEPO NÃO EMITIU ANEXO II</t>
+  </si>
+  <si>
     <t>202600010062463</t>
   </si>
   <si>
@@ -1346,7 +1376,10 @@
     <t>SISLOG 113930 -GLOBAL TI Contratação de solução de Inteligência Artificial (IA). Processo 202500010079078 paralelo CCONT</t>
   </si>
   <si>
-    <t>Encaminhem-se a GCC para conhecimento do empenho e para devidas providencias quanto ao Apostilamento</t>
+    <t>PROCSET</t>
+  </si>
+  <si>
+    <t>Feita a minuta do 1º Termo Aditivo, encaminho o processo à PROCSET para apreciação.</t>
   </si>
   <si>
     <t>93/2025</t>
@@ -1431,16 +1464,10 @@
     <t>FORNECEDOR MEMORA. Contratação de mão de obra de infra e banco.</t>
   </si>
   <si>
-    <t>CACTIC  GCC GECONT</t>
-  </si>
-  <si>
-    <t>ATENDER DILIGÊNCIA 21 DA CACTIC  CONTABILIDADE PARA ANÁLISE para cadastro da IPOF</t>
+    <t>para análise e manifestação, bem como para posterior remessa à Procuradoria-Geral do Estado para apreciação conclusiva, haja vista que o valor supera R$ 10.000.000,00</t>
   </si>
   <si>
     <t>83/2023</t>
-  </si>
-  <si>
-    <t>2º</t>
   </si>
   <si>
     <t>202300010017830</t>
@@ -1877,18 +1904,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V123"/>
+  <dimension ref="A1:V126"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
@@ -1984,7 +2001,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -2020,7 +2037,7 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="J3" t="s">
         <v>28</v>
@@ -2056,7 +2073,7 @@
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="J4" t="s">
         <v>38</v>
@@ -2092,7 +2109,7 @@
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="J5" t="s">
         <v>28</v>
@@ -2128,7 +2145,7 @@
         <v>45141</v>
       </c>
       <c r="I6" s="3">
-        <v>1120</v>
+        <v>1132</v>
       </c>
       <c r="J6" t="s">
         <v>38</v>
@@ -2176,7 +2193,7 @@
         <v>45140</v>
       </c>
       <c r="I7" s="3">
-        <v>1121</v>
+        <v>1133</v>
       </c>
       <c r="J7" t="s">
         <v>52</v>
@@ -2229,7 +2246,7 @@
         <v>45198</v>
       </c>
       <c r="I8" s="3">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="J8" t="s">
         <v>52</v>
@@ -2282,7 +2299,7 @@
         <v>45702</v>
       </c>
       <c r="I9" s="3">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="J9" t="s">
         <v>28</v>
@@ -2330,7 +2347,7 @@
         <v>45372</v>
       </c>
       <c r="I10" s="3">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="J10" t="s">
         <v>38</v>
@@ -2378,7 +2395,7 @@
         <v>45453</v>
       </c>
       <c r="I11" s="3">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="J11" t="s">
         <v>28</v>
@@ -2426,7 +2443,7 @@
         <v>44980</v>
       </c>
       <c r="I12" s="3">
-        <v>1281</v>
+        <v>1293</v>
       </c>
       <c r="J12" t="s">
         <v>52</v>
@@ -2473,7 +2490,7 @@
         <v>45107</v>
       </c>
       <c r="I13" s="3">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="J13" t="s">
         <v>52</v>
@@ -2520,7 +2537,7 @@
         <v>45154</v>
       </c>
       <c r="I14" s="3">
-        <v>1107</v>
+        <v>1119</v>
       </c>
       <c r="J14" t="s">
         <v>52</v>
@@ -2567,7 +2584,7 @@
         <v>45189</v>
       </c>
       <c r="I15" s="3">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
@@ -2614,7 +2631,7 @@
         <v>45145</v>
       </c>
       <c r="I16" s="3">
-        <v>1116</v>
+        <v>1128</v>
       </c>
       <c r="J16" t="s">
         <v>52</v>
@@ -2661,7 +2678,7 @@
         <v>45107</v>
       </c>
       <c r="I17" s="3">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
@@ -2708,7 +2725,7 @@
         <v>45208</v>
       </c>
       <c r="I18" s="3">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="J18" t="s">
         <v>52</v>
@@ -2755,7 +2772,7 @@
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="J19" t="s">
         <v>52</v>
@@ -2802,7 +2819,7 @@
         <v>45034</v>
       </c>
       <c r="I20" s="3">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="J20" t="s">
         <v>28</v>
@@ -2838,7 +2855,7 @@
         <v>45152</v>
       </c>
       <c r="I21" s="3">
-        <v>1109</v>
+        <v>1121</v>
       </c>
       <c r="J21" t="s">
         <v>38</v>
@@ -2885,7 +2902,7 @@
         <v>44908</v>
       </c>
       <c r="I22" s="3">
-        <v>1353</v>
+        <v>1365</v>
       </c>
       <c r="J22" t="s">
         <v>52</v>
@@ -2932,7 +2949,7 @@
         <v>45007</v>
       </c>
       <c r="I23" s="3">
-        <v>1254</v>
+        <v>1266</v>
       </c>
       <c r="J23" t="s">
         <v>38</v>
@@ -2977,7 +2994,7 @@
         <v>45202</v>
       </c>
       <c r="I24" s="3">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="J24" t="s">
         <v>28</v>
@@ -3013,7 +3030,7 @@
         <v>45226</v>
       </c>
       <c r="I25" s="3">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
@@ -3060,7 +3077,7 @@
         <v>45224</v>
       </c>
       <c r="I26" s="3">
-        <v>1037</v>
+        <v>1049</v>
       </c>
       <c r="J26" t="s">
         <v>52</v>
@@ -3107,7 +3124,7 @@
         <v>45481</v>
       </c>
       <c r="I27" s="3">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="J27" t="s">
         <v>38</v>
@@ -3149,7 +3166,7 @@
         <v>45134</v>
       </c>
       <c r="I28" s="3">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="J28" t="s">
         <v>52</v>
@@ -3196,7 +3213,7 @@
         <v>45043</v>
       </c>
       <c r="I29" s="3">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="J29" t="s">
         <v>28</v>
@@ -3232,7 +3249,7 @@
         <v>45395</v>
       </c>
       <c r="I30" s="3">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="J30" t="s">
         <v>28</v>
@@ -3268,7 +3285,7 @@
         <v>45251</v>
       </c>
       <c r="I31" s="3">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="J31" t="s">
         <v>28</v>
@@ -3304,7 +3321,7 @@
         <v>45175</v>
       </c>
       <c r="I32" s="3">
-        <v>1086</v>
+        <v>1098</v>
       </c>
       <c r="J32" t="s">
         <v>38</v>
@@ -3351,7 +3368,7 @@
         <v>45400</v>
       </c>
       <c r="I33" s="3">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="J33" t="s">
         <v>38</v>
@@ -3398,7 +3415,7 @@
         <v>45252</v>
       </c>
       <c r="I34" s="3">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="J34" t="s">
         <v>38</v>
@@ -3434,7 +3451,7 @@
         <v>45267</v>
       </c>
       <c r="I35" s="3">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="J35" t="s">
         <v>28</v>
@@ -3470,7 +3487,7 @@
         <v>45404</v>
       </c>
       <c r="I36" s="3">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="J36" t="s">
         <v>28</v>
@@ -3506,7 +3523,7 @@
         <v>45236</v>
       </c>
       <c r="I37" s="3">
-        <v>1025</v>
+        <v>1037</v>
       </c>
       <c r="J37" t="s">
         <v>38</v>
@@ -3553,7 +3570,7 @@
         <v>45209</v>
       </c>
       <c r="I38" s="3">
-        <v>1052</v>
+        <v>1064</v>
       </c>
       <c r="J38" t="s">
         <v>28</v>
@@ -3589,7 +3606,7 @@
         <v>45573</v>
       </c>
       <c r="I39" s="3">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="J39" t="s">
         <v>38</v>
@@ -3639,7 +3656,7 @@
         <v>45306</v>
       </c>
       <c r="I40" s="3">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="J40" t="s">
         <v>28</v>
@@ -3675,7 +3692,7 @@
         <v>45264</v>
       </c>
       <c r="I41" s="3">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="J41" t="s">
         <v>38</v>
@@ -3722,7 +3739,7 @@
         <v>45426</v>
       </c>
       <c r="I42" s="3">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="J42" t="s">
         <v>28</v>
@@ -3758,7 +3775,7 @@
         <v>45359</v>
       </c>
       <c r="I43" s="3">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="J43" t="s">
         <v>28</v>
@@ -3794,7 +3811,7 @@
         <v>45595</v>
       </c>
       <c r="I44" s="3">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="J44" t="s">
         <v>38</v>
@@ -3838,7 +3855,7 @@
         <v>45562</v>
       </c>
       <c r="I45" s="3">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="J45" t="s">
         <v>38</v>
@@ -3880,7 +3897,7 @@
         <v>45488</v>
       </c>
       <c r="I46" s="3">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="J46" t="s">
         <v>38</v>
@@ -3922,7 +3939,7 @@
         <v>45552</v>
       </c>
       <c r="I47" s="3">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="J47" t="s">
         <v>38</v>
@@ -3940,7 +3957,7 @@
         <v>47378</v>
       </c>
       <c r="T47" s="3">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
@@ -3971,7 +3988,7 @@
         <v>45540</v>
       </c>
       <c r="I48" s="3">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="J48" t="s">
         <v>38</v>
@@ -4021,7 +4038,7 @@
         <v>45566</v>
       </c>
       <c r="I49" s="3">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="J49" t="s">
         <v>38</v>
@@ -4039,7 +4056,7 @@
         <v>47343</v>
       </c>
       <c r="T49" s="3">
-        <v>1082</v>
+        <v>1070</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
@@ -4070,7 +4087,7 @@
         <v>45790</v>
       </c>
       <c r="I50" s="3">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="J50" t="s">
         <v>28</v>
@@ -4114,7 +4131,7 @@
         <v>45567</v>
       </c>
       <c r="I51" s="3">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="J51" t="s">
         <v>28</v>
@@ -4150,7 +4167,7 @@
         <v>45590</v>
       </c>
       <c r="I52" s="3">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="J52" t="s">
         <v>28</v>
@@ -4186,7 +4203,7 @@
         <v>45758</v>
       </c>
       <c r="I53" s="3">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="J53" t="s">
         <v>28</v>
@@ -4222,7 +4239,7 @@
         <v>45454</v>
       </c>
       <c r="I54" s="3">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="J54" t="s">
         <v>52</v>
@@ -4269,7 +4286,7 @@
         <v>45573</v>
       </c>
       <c r="I55" s="3">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="J55" t="s">
         <v>38</v>
@@ -4305,7 +4322,7 @@
         <v>45219</v>
       </c>
       <c r="I56" s="3">
-        <v>1042</v>
+        <v>1054</v>
       </c>
       <c r="J56" t="s">
         <v>28</v>
@@ -4341,7 +4358,7 @@
         <v>45315</v>
       </c>
       <c r="I57" s="3">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="J57" t="s">
         <v>38</v>
@@ -4377,7 +4394,7 @@
         <v>45299</v>
       </c>
       <c r="I58" s="3">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="J58" t="s">
         <v>28</v>
@@ -4413,7 +4430,7 @@
         <v>45462</v>
       </c>
       <c r="I59" s="3">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="J59" t="s">
         <v>38</v>
@@ -4449,7 +4466,7 @@
         <v>45538</v>
       </c>
       <c r="I60" s="3">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="J60" t="s">
         <v>52</v>
@@ -4467,7 +4484,7 @@
         <v>47301</v>
       </c>
       <c r="T60" s="3">
-        <v>1040</v>
+        <v>1028</v>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
@@ -4498,7 +4515,7 @@
         <v>45847</v>
       </c>
       <c r="I61" s="3">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="J61" t="s">
         <v>28</v>
@@ -4534,7 +4551,7 @@
         <v>45839</v>
       </c>
       <c r="I62" s="3">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="J62" t="s">
         <v>28</v>
@@ -4570,7 +4587,7 @@
         <v>46246</v>
       </c>
       <c r="I63" s="3">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J63" t="s">
         <v>28</v>
@@ -4597,19 +4614,19 @@
         <v>263</v>
       </c>
       <c r="F64" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="G64" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H64" s="2">
         <v>46259</v>
       </c>
       <c r="I64" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J64" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M64" s="3"/>
       <c r="T64" s="3"/>
@@ -4621,31 +4638,31 @@
         <v>26</v>
       </c>
       <c r="B65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C65" s="2">
         <v>46126</v>
       </c>
       <c r="D65" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E65" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F65" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="G65" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H65" s="2">
         <v>46182</v>
       </c>
       <c r="I65" s="3">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M65" s="3"/>
       <c r="T65" s="3"/>
@@ -4657,7 +4674,7 @@
         <v>26</v>
       </c>
       <c r="B66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C66" s="2">
         <v>46211</v>
@@ -4666,22 +4683,22 @@
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F66" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G66" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H66" s="2">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="I66" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J66" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M66" s="3"/>
       <c r="T66" s="3"/>
@@ -4716,7 +4733,7 @@
         <v>46156</v>
       </c>
       <c r="I67" s="3">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J67" t="s">
         <v>38</v>
@@ -4754,7 +4771,7 @@
         <v>46155</v>
       </c>
       <c r="I68" s="3">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="J68" t="s">
         <v>38</v>
@@ -4792,7 +4809,7 @@
         <v>46157</v>
       </c>
       <c r="I69" s="3">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="J69" t="s">
         <v>38</v>
@@ -4830,7 +4847,7 @@
         <v>45943</v>
       </c>
       <c r="I70" s="3">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="J70" t="s">
         <v>28</v>
@@ -4868,7 +4885,7 @@
         <v>45715</v>
       </c>
       <c r="I71" s="3">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="J71" t="s">
         <v>52</v>
@@ -4917,7 +4934,7 @@
         <v>45817</v>
       </c>
       <c r="I72" s="3">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="J72" t="s">
         <v>52</v>
@@ -4935,7 +4952,7 @@
         <v>46909</v>
       </c>
       <c r="T72" s="3">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="U72" s="3"/>
       <c r="V72" s="4">
@@ -4968,7 +4985,7 @@
         <v>45911</v>
       </c>
       <c r="I73" s="3">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="J73" t="s">
         <v>52</v>
@@ -5020,7 +5037,7 @@
         <v>45895</v>
       </c>
       <c r="I74" s="3">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="J74" t="s">
         <v>38</v>
@@ -5049,16 +5066,16 @@
         <v>302</v>
       </c>
       <c r="F75" t="s">
+        <v>274</v>
+      </c>
+      <c r="G75" t="s">
         <v>303</v>
-      </c>
-      <c r="G75" t="s">
-        <v>304</v>
       </c>
       <c r="H75" s="2">
         <v>46196</v>
       </c>
       <c r="I75" s="3">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J75" t="s">
         <v>28</v>
@@ -5072,10 +5089,10 @@
     </row>
     <row r="76" spans="1:22">
       <c r="A76" t="s">
+        <v>304</v>
+      </c>
+      <c r="B76" t="s">
         <v>305</v>
-      </c>
-      <c r="B76" t="s">
-        <v>306</v>
       </c>
       <c r="C76" s="2">
         <v>45665</v>
@@ -5084,25 +5101,25 @@
         <v>35</v>
       </c>
       <c r="E76" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
       </c>
       <c r="G76" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H76" s="2">
         <v>46198</v>
       </c>
       <c r="I76" s="3">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="J76" t="s">
         <v>38</v>
       </c>
       <c r="K76" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L76" s="2">
         <v>46071</v>
@@ -5111,7 +5128,7 @@
         <v>406</v>
       </c>
       <c r="O76" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P76" s="2">
         <v>46294</v>
@@ -5121,7 +5138,7 @@
       </c>
       <c r="T76" s="3"/>
       <c r="U76" s="3">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="V76" s="4">
         <v>51071</v>
@@ -5141,7 +5158,7 @@
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F77" t="s">
         <v>42</v>
@@ -5153,13 +5170,13 @@
         <v>45790</v>
       </c>
       <c r="I77" s="3">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="J77" t="s">
         <v>52</v>
       </c>
       <c r="K77" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L77" s="2">
         <v>43964</v>
@@ -5187,7 +5204,7 @@
         <v>26</v>
       </c>
       <c r="B78" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C78" s="2">
         <v>46210</v>
@@ -5196,22 +5213,22 @@
         <v>35</v>
       </c>
       <c r="E78" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F78" t="s">
         <v>177</v>
       </c>
       <c r="G78" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H78" s="2">
         <v>46259</v>
       </c>
       <c r="I78" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J78" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M78" s="3"/>
       <c r="T78" s="3"/>
@@ -5225,7 +5242,7 @@
         <v>42</v>
       </c>
       <c r="B79" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C79" s="2">
         <v>45915</v>
@@ -5234,25 +5251,25 @@
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F79" t="s">
         <v>141</v>
       </c>
       <c r="G79" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H79" s="2">
         <v>46094</v>
       </c>
       <c r="I79" s="3">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J79" t="s">
         <v>38</v>
       </c>
       <c r="K79" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L79" s="2">
         <v>46086</v>
@@ -5264,7 +5281,7 @@
         <v>47181</v>
       </c>
       <c r="T79" s="3">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="U79" s="3"/>
       <c r="V79" s="4">
@@ -5276,7 +5293,7 @@
         <v>42</v>
       </c>
       <c r="B80" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C80" s="2">
         <v>45950</v>
@@ -5285,25 +5302,25 @@
         <v>44</v>
       </c>
       <c r="E80" t="s">
+        <v>320</v>
+      </c>
+      <c r="F80" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" t="s">
         <v>321</v>
-      </c>
-      <c r="F80" t="s">
-        <v>42</v>
-      </c>
-      <c r="G80" t="s">
-        <v>322</v>
       </c>
       <c r="H80" s="2">
         <v>45975</v>
       </c>
       <c r="I80" s="3">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="J80" t="s">
         <v>38</v>
       </c>
       <c r="K80" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L80" s="2">
         <v>45978</v>
@@ -5331,7 +5348,7 @@
         <v>42</v>
       </c>
       <c r="B81" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C81" s="2">
         <v>45915</v>
@@ -5340,25 +5357,25 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
+        <v>323</v>
+      </c>
+      <c r="F81" t="s">
         <v>324</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>325</v>
-      </c>
-      <c r="G81" t="s">
-        <v>326</v>
       </c>
       <c r="H81" s="2">
         <v>46241</v>
       </c>
       <c r="I81" s="3">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J81" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K81" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L81" s="2">
         <v>46086</v>
@@ -5370,7 +5387,7 @@
         <v>47181</v>
       </c>
       <c r="T81" s="3">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
@@ -5382,7 +5399,7 @@
         <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C82" s="2">
         <v>45915</v>
@@ -5391,25 +5408,25 @@
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F82" t="s">
         <v>141</v>
       </c>
       <c r="G82" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H82" s="2">
         <v>46094</v>
       </c>
       <c r="I82" s="3">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J82" t="s">
         <v>38</v>
       </c>
       <c r="K82" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L82" s="2">
         <v>46086</v>
@@ -5421,7 +5438,7 @@
         <v>47181</v>
       </c>
       <c r="T82" s="3">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="U82" s="3"/>
       <c r="V82" s="4">
@@ -5454,13 +5471,13 @@
         <v>45790</v>
       </c>
       <c r="I83" s="3">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="J83" t="s">
         <v>52</v>
       </c>
       <c r="K83" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L83" s="2">
         <v>43964</v>
@@ -5488,37 +5505,37 @@
         <v>42</v>
       </c>
       <c r="B84" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C84" s="2">
-        <v>46245</v>
+        <v>46260</v>
       </c>
       <c r="D84" t="s">
         <v>44</v>
       </c>
       <c r="E84" t="s">
+        <v>331</v>
+      </c>
+      <c r="F84" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" t="s">
         <v>332</v>
       </c>
-      <c r="F84" t="s">
-        <v>177</v>
-      </c>
-      <c r="G84" t="s">
-        <v>333</v>
-      </c>
       <c r="H84" s="2">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="I84" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J84" t="s">
-        <v>265</v>
+        <v>28</v>
       </c>
       <c r="M84" s="3"/>
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
       <c r="V84" s="4">
-        <v>180600</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="85" spans="1:22">
@@ -5526,50 +5543,37 @@
         <v>42</v>
       </c>
       <c r="B85" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C85" s="2">
-        <v>45819</v>
+        <v>46266</v>
       </c>
       <c r="D85" t="s">
         <v>44</v>
       </c>
       <c r="E85" t="s">
+        <v>334</v>
+      </c>
+      <c r="F85" t="s">
+        <v>274</v>
+      </c>
+      <c r="G85" t="s">
         <v>335</v>
       </c>
-      <c r="F85" t="s">
-        <v>42</v>
-      </c>
-      <c r="G85" t="s">
-        <v>336</v>
-      </c>
       <c r="H85" s="2">
-        <v>46170</v>
+        <v>46269</v>
       </c>
       <c r="I85" s="3">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="J85" t="s">
-        <v>52</v>
-      </c>
-      <c r="K85" t="s">
-        <v>337</v>
-      </c>
-      <c r="L85" s="2">
-        <v>45904</v>
-      </c>
-      <c r="M85" s="3">
-        <v>85</v>
-      </c>
-      <c r="S85" s="2">
-        <v>46273</v>
-      </c>
-      <c r="T85" s="3">
-        <v>12</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="M85" s="3"/>
+      <c r="T85" s="3"/>
       <c r="U85" s="3"/>
       <c r="V85" s="4">
-        <v>230000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="86" spans="1:22">
@@ -5577,50 +5581,37 @@
         <v>42</v>
       </c>
       <c r="B86" t="s">
+        <v>336</v>
+      </c>
+      <c r="C86" s="2">
+        <v>46245</v>
+      </c>
+      <c r="D86" t="s">
+        <v>44</v>
+      </c>
+      <c r="E86" t="s">
+        <v>337</v>
+      </c>
+      <c r="F86" t="s">
         <v>338</v>
       </c>
-      <c r="C86" s="2">
-        <v>45952</v>
-      </c>
-      <c r="D86" t="s">
-        <v>24</v>
-      </c>
-      <c r="E86" t="s">
-        <v>339</v>
-      </c>
-      <c r="F86" t="s">
-        <v>340</v>
-      </c>
       <c r="G86" t="s">
-        <v>341</v>
+        <v>265</v>
       </c>
       <c r="H86" s="2">
-        <v>46087</v>
+        <v>46267</v>
       </c>
       <c r="I86" s="3">
-        <v>174</v>
+        <v>6</v>
       </c>
       <c r="J86" t="s">
-        <v>52</v>
-      </c>
-      <c r="K86" t="s">
-        <v>342</v>
-      </c>
-      <c r="L86" s="2">
-        <v>46086</v>
-      </c>
-      <c r="M86" s="3">
-        <v>134</v>
-      </c>
-      <c r="S86" s="2">
-        <v>47910</v>
-      </c>
-      <c r="T86" s="3">
-        <v>1649</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="M86" s="3"/>
+      <c r="T86" s="3"/>
       <c r="U86" s="3"/>
       <c r="V86" s="4">
-        <v>250977.6</v>
+        <v>180600</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -5628,48 +5619,48 @@
         <v>42</v>
       </c>
       <c r="B87" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="C87" s="2">
-        <v>45775</v>
+        <v>45819</v>
       </c>
       <c r="D87" t="s">
         <v>44</v>
       </c>
       <c r="E87" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F87" t="s">
         <v>42</v>
       </c>
       <c r="G87" t="s">
-        <v>51</v>
+        <v>341</v>
       </c>
       <c r="H87" s="2">
-        <v>45861</v>
+        <v>46170</v>
       </c>
       <c r="I87" s="3">
-        <v>400</v>
+        <v>103</v>
       </c>
       <c r="J87" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K87" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="L87" s="2">
-        <v>45856</v>
+        <v>45904</v>
       </c>
       <c r="M87" s="3">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="S87" s="2">
-        <v>46225</v>
+        <v>46273</v>
       </c>
       <c r="T87" s="3"/>
       <c r="U87" s="3"/>
       <c r="V87" s="4">
-        <v>288862</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -5677,37 +5668,50 @@
         <v>42</v>
       </c>
       <c r="B88" t="s">
+        <v>343</v>
+      </c>
+      <c r="C88" s="2">
+        <v>45952</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" t="s">
         <v>344</v>
       </c>
-      <c r="C88" s="2">
-        <v>45539</v>
-      </c>
-      <c r="D88" t="s">
-        <v>44</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>345</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>346</v>
       </c>
-      <c r="G88" t="s">
-        <v>347</v>
-      </c>
       <c r="H88" s="2">
-        <v>45607</v>
+        <v>46087</v>
       </c>
       <c r="I88" s="3">
-        <v>654</v>
+        <v>186</v>
       </c>
       <c r="J88" t="s">
         <v>52</v>
       </c>
-      <c r="M88" s="3"/>
-      <c r="T88" s="3"/>
+      <c r="K88" t="s">
+        <v>347</v>
+      </c>
+      <c r="L88" s="2">
+        <v>46086</v>
+      </c>
+      <c r="M88" s="3">
+        <v>134</v>
+      </c>
+      <c r="S88" s="2">
+        <v>47910</v>
+      </c>
+      <c r="T88" s="3">
+        <v>1637</v>
+      </c>
       <c r="U88" s="3"/>
       <c r="V88" s="4">
-        <v>297600</v>
+        <v>250977.6</v>
       </c>
     </row>
     <row r="89" spans="1:22">
@@ -5715,50 +5719,48 @@
         <v>42</v>
       </c>
       <c r="B89" t="s">
+        <v>319</v>
+      </c>
+      <c r="C89" s="2">
+        <v>45775</v>
+      </c>
+      <c r="D89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E89" t="s">
         <v>348</v>
       </c>
-      <c r="C89" s="2">
-        <v>45840</v>
-      </c>
-      <c r="D89" t="s">
-        <v>24</v>
-      </c>
-      <c r="E89" t="s">
-        <v>349</v>
-      </c>
       <c r="F89" t="s">
-        <v>350</v>
+        <v>42</v>
       </c>
       <c r="G89" t="s">
-        <v>351</v>
+        <v>51</v>
       </c>
       <c r="H89" s="2">
-        <v>46002</v>
+        <v>45861</v>
       </c>
       <c r="I89" s="3">
-        <v>259</v>
+        <v>412</v>
       </c>
       <c r="J89" t="s">
         <v>38</v>
       </c>
       <c r="K89" t="s">
-        <v>352</v>
+        <v>322</v>
       </c>
       <c r="L89" s="2">
-        <v>46001</v>
+        <v>45856</v>
       </c>
       <c r="M89" s="3">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="S89" s="2">
-        <v>47097</v>
-      </c>
-      <c r="T89" s="3">
-        <v>836</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="T89" s="3"/>
       <c r="U89" s="3"/>
       <c r="V89" s="4">
-        <v>299821.5</v>
+        <v>288862</v>
       </c>
     </row>
     <row r="90" spans="1:22">
@@ -5766,50 +5768,37 @@
         <v>42</v>
       </c>
       <c r="B90" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C90" s="2">
-        <v>45868</v>
+        <v>45539</v>
       </c>
       <c r="D90" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E90" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F90" t="s">
-        <v>66</v>
+        <v>351</v>
       </c>
       <c r="G90" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H90" s="2">
-        <v>46146</v>
+        <v>45607</v>
       </c>
       <c r="I90" s="3">
-        <v>115</v>
+        <v>666</v>
       </c>
       <c r="J90" t="s">
         <v>52</v>
       </c>
-      <c r="K90" t="s">
-        <v>356</v>
-      </c>
-      <c r="L90" s="2">
-        <v>46077</v>
-      </c>
-      <c r="M90" s="3">
-        <v>209</v>
-      </c>
-      <c r="S90" s="2">
-        <v>47905</v>
-      </c>
-      <c r="T90" s="3">
-        <v>1644</v>
-      </c>
+      <c r="M90" s="3"/>
+      <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="4">
-        <v>338580</v>
+        <v>297600</v>
       </c>
     </row>
     <row r="91" spans="1:22">
@@ -5817,56 +5806,50 @@
         <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C91" s="2">
-        <v>44370</v>
+        <v>45840</v>
       </c>
       <c r="D91" t="s">
         <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F91" t="s">
-        <v>42</v>
+        <v>355</v>
       </c>
       <c r="G91" t="s">
-        <v>148</v>
+        <v>356</v>
       </c>
       <c r="H91" s="2">
-        <v>45881</v>
+        <v>46002</v>
       </c>
       <c r="I91" s="3">
-        <v>380</v>
+        <v>271</v>
       </c>
       <c r="J91" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K91" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L91" s="2">
-        <v>44589</v>
+        <v>46001</v>
       </c>
       <c r="M91" s="3">
-        <v>219</v>
-      </c>
-      <c r="O91" t="s">
-        <v>360</v>
-      </c>
-      <c r="P91" s="2">
-        <v>46419</v>
+        <v>161</v>
       </c>
       <c r="S91" s="2">
-        <v>44593</v>
-      </c>
-      <c r="T91" s="3"/>
-      <c r="U91" s="3">
-        <v>158</v>
-      </c>
+        <v>47097</v>
+      </c>
+      <c r="T91" s="3">
+        <v>824</v>
+      </c>
+      <c r="U91" s="3"/>
       <c r="V91" s="4">
-        <v>374899.96</v>
+        <v>299821.5</v>
       </c>
     </row>
     <row r="92" spans="1:22">
@@ -5874,240 +5857,251 @@
         <v>42</v>
       </c>
       <c r="B92" t="s">
+        <v>358</v>
+      </c>
+      <c r="C92" s="2">
+        <v>45868</v>
+      </c>
+      <c r="D92" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92" t="s">
+        <v>359</v>
+      </c>
+      <c r="F92" t="s">
+        <v>66</v>
+      </c>
+      <c r="G92" t="s">
+        <v>360</v>
+      </c>
+      <c r="H92" s="2">
+        <v>46146</v>
+      </c>
+      <c r="I92" s="3">
+        <v>127</v>
+      </c>
+      <c r="J92" t="s">
+        <v>52</v>
+      </c>
+      <c r="K92" t="s">
         <v>361</v>
       </c>
-      <c r="C92" s="2">
-        <v>45422</v>
-      </c>
-      <c r="D92" t="s">
-        <v>44</v>
-      </c>
-      <c r="E92" t="s">
-        <v>362</v>
-      </c>
-      <c r="F92" t="s">
-        <v>42</v>
-      </c>
-      <c r="G92" t="s">
-        <v>363</v>
-      </c>
-      <c r="H92" s="2">
-        <v>45624</v>
-      </c>
-      <c r="I92" s="3">
-        <v>637</v>
-      </c>
-      <c r="J92" t="s">
-        <v>38</v>
-      </c>
-      <c r="K92" t="s">
-        <v>364</v>
-      </c>
       <c r="L92" s="2">
-        <v>45544</v>
+        <v>46077</v>
       </c>
       <c r="M92" s="3">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="S92" s="2">
-        <v>45911</v>
-      </c>
-      <c r="T92" s="3"/>
+        <v>47905</v>
+      </c>
+      <c r="T92" s="3">
+        <v>1632</v>
+      </c>
       <c r="U92" s="3"/>
       <c r="V92" s="4">
-        <v>457600</v>
+        <v>338580</v>
       </c>
     </row>
     <row r="93" spans="1:22">
       <c r="A93" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C93" s="2">
-        <v>46038</v>
+        <v>44370</v>
       </c>
       <c r="D93" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F93" t="s">
         <v>42</v>
       </c>
       <c r="G93" t="s">
-        <v>367</v>
+        <v>148</v>
       </c>
       <c r="H93" s="2">
-        <v>46237</v>
+        <v>45881</v>
       </c>
       <c r="I93" s="3">
-        <v>24</v>
+        <v>392</v>
       </c>
       <c r="J93" t="s">
         <v>52</v>
       </c>
-      <c r="M93" s="3"/>
+      <c r="K93" t="s">
+        <v>364</v>
+      </c>
+      <c r="L93" s="2">
+        <v>44589</v>
+      </c>
+      <c r="M93" s="3">
+        <v>219</v>
+      </c>
+      <c r="O93" t="s">
+        <v>365</v>
+      </c>
+      <c r="P93" s="2">
+        <v>46419</v>
+      </c>
+      <c r="S93" s="2">
+        <v>44593</v>
+      </c>
       <c r="T93" s="3"/>
-      <c r="U93" s="3"/>
+      <c r="U93" s="3">
+        <v>146</v>
+      </c>
       <c r="V93" s="4">
-        <v>687500</v>
+        <v>374899.96</v>
       </c>
     </row>
     <row r="94" spans="1:22">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
+        <v>366</v>
+      </c>
+      <c r="C94" s="2">
+        <v>45422</v>
+      </c>
+      <c r="D94" t="s">
+        <v>44</v>
+      </c>
+      <c r="E94" t="s">
+        <v>367</v>
+      </c>
+      <c r="F94" t="s">
+        <v>42</v>
+      </c>
+      <c r="G94" t="s">
         <v>368</v>
       </c>
-      <c r="C94" s="2">
-        <v>44939</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="H94" s="2">
+        <v>45624</v>
+      </c>
+      <c r="I94" s="3">
+        <v>649</v>
+      </c>
+      <c r="J94" t="s">
+        <v>38</v>
+      </c>
+      <c r="K94" t="s">
         <v>369</v>
       </c>
-      <c r="E94" t="s">
-        <v>370</v>
-      </c>
-      <c r="F94" t="s">
-        <v>29</v>
-      </c>
-      <c r="G94" t="s">
-        <v>371</v>
-      </c>
-      <c r="H94" s="2">
-        <v>45979</v>
-      </c>
-      <c r="I94" s="3">
-        <v>282</v>
-      </c>
-      <c r="J94" t="s">
-        <v>52</v>
-      </c>
-      <c r="K94" t="s">
-        <v>372</v>
-      </c>
       <c r="L94" s="2">
-        <v>45968</v>
+        <v>45544</v>
       </c>
       <c r="M94" s="3">
-        <v>1029</v>
-      </c>
-      <c r="O94" t="s">
-        <v>360</v>
-      </c>
-      <c r="P94" s="2">
-        <v>46426</v>
+        <v>122</v>
       </c>
       <c r="S94" s="2">
-        <v>45334</v>
+        <v>45911</v>
       </c>
       <c r="T94" s="3"/>
-      <c r="U94" s="3">
-        <v>165</v>
-      </c>
+      <c r="U94" s="3"/>
       <c r="V94" s="4">
-        <v>706431.6</v>
+        <v>457600</v>
       </c>
     </row>
     <row r="95" spans="1:22">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B95" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C95" s="2">
-        <v>45673</v>
+        <v>46038</v>
       </c>
       <c r="D95" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E95" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F95" t="s">
         <v>42</v>
       </c>
       <c r="G95" t="s">
-        <v>51</v>
+        <v>372</v>
       </c>
       <c r="H95" s="2">
-        <v>46140</v>
+        <v>46237</v>
       </c>
       <c r="I95" s="3">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="J95" t="s">
         <v>52</v>
       </c>
-      <c r="K95" t="s">
-        <v>375</v>
-      </c>
       <c r="M95" s="3"/>
-      <c r="S95" s="2">
-        <v>46598</v>
-      </c>
-      <c r="T95" s="3">
-        <v>337</v>
-      </c>
+      <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="4">
-        <v>890000</v>
+        <v>687500</v>
       </c>
     </row>
     <row r="96" spans="1:22">
       <c r="A96" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B96" t="s">
+        <v>373</v>
+      </c>
+      <c r="C96" s="2">
+        <v>44939</v>
+      </c>
+      <c r="D96" t="s">
+        <v>374</v>
+      </c>
+      <c r="E96" t="s">
+        <v>375</v>
+      </c>
+      <c r="F96" t="s">
+        <v>29</v>
+      </c>
+      <c r="G96" t="s">
         <v>376</v>
       </c>
-      <c r="C96" s="2">
-        <v>45215</v>
-      </c>
-      <c r="D96" t="s">
-        <v>24</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="H96" s="2">
+        <v>45979</v>
+      </c>
+      <c r="I96" s="3">
+        <v>294</v>
+      </c>
+      <c r="J96" t="s">
+        <v>52</v>
+      </c>
+      <c r="K96" t="s">
         <v>377</v>
       </c>
-      <c r="F96" t="s">
-        <v>169</v>
-      </c>
-      <c r="G96" t="s">
-        <v>378</v>
-      </c>
-      <c r="H96" s="2">
-        <v>45687</v>
-      </c>
-      <c r="I96" s="3">
-        <v>574</v>
-      </c>
-      <c r="J96" t="s">
-        <v>38</v>
-      </c>
-      <c r="K96" t="s">
-        <v>379</v>
-      </c>
       <c r="L96" s="2">
-        <v>45685</v>
+        <v>45968</v>
       </c>
       <c r="M96" s="3">
-        <v>470</v>
+        <v>1029</v>
+      </c>
+      <c r="O96" t="s">
+        <v>365</v>
+      </c>
+      <c r="P96" s="2">
+        <v>46426</v>
       </c>
       <c r="S96" s="2">
-        <v>46780</v>
-      </c>
-      <c r="T96" s="3">
-        <v>519</v>
-      </c>
-      <c r="U96" s="3"/>
+        <v>45334</v>
+      </c>
+      <c r="T96" s="3"/>
+      <c r="U96" s="3">
+        <v>153</v>
+      </c>
       <c r="V96" s="4">
-        <v>1220266.1399999999</v>
+        <v>706431.6</v>
       </c>
     </row>
     <row r="97" spans="1:22">
@@ -6115,99 +6109,83 @@
         <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C97" s="2">
-        <v>45366</v>
+        <v>45673</v>
       </c>
       <c r="D97" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F97" t="s">
         <v>42</v>
       </c>
       <c r="G97" t="s">
-        <v>382</v>
+        <v>51</v>
       </c>
       <c r="H97" s="2">
-        <v>45481</v>
+        <v>46140</v>
       </c>
       <c r="I97" s="3">
-        <v>780</v>
+        <v>133</v>
       </c>
       <c r="J97" t="s">
         <v>52</v>
       </c>
       <c r="K97" t="s">
-        <v>383</v>
-      </c>
-      <c r="L97" s="2">
-        <v>45471</v>
-      </c>
-      <c r="M97" s="3">
-        <v>105</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="M97" s="3"/>
       <c r="S97" s="2">
-        <v>47301</v>
+        <v>46598</v>
       </c>
       <c r="T97" s="3">
-        <v>1040</v>
+        <v>325</v>
       </c>
       <c r="U97" s="3"/>
       <c r="V97" s="4">
-        <v>1245414.49</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
+        <v>42</v>
+      </c>
+      <c r="B98" t="s">
+        <v>381</v>
+      </c>
+      <c r="C98" s="2">
+        <v>46260</v>
+      </c>
+      <c r="D98" t="s">
+        <v>44</v>
+      </c>
+      <c r="E98" t="s">
+        <v>382</v>
+      </c>
+      <c r="F98" t="s">
         <v>26</v>
       </c>
-      <c r="B98" t="s">
-        <v>384</v>
-      </c>
-      <c r="C98" s="2">
-        <v>45152</v>
-      </c>
-      <c r="D98" t="s">
-        <v>267</v>
-      </c>
-      <c r="E98" t="s">
-        <v>385</v>
-      </c>
-      <c r="F98" t="s">
-        <v>29</v>
-      </c>
       <c r="G98" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="H98" s="2">
-        <v>45440</v>
+        <v>46266</v>
       </c>
       <c r="I98" s="3">
-        <v>821</v>
+        <v>7</v>
       </c>
       <c r="J98" t="s">
-        <v>52</v>
-      </c>
-      <c r="K98" t="s">
-        <v>387</v>
-      </c>
-      <c r="L98" s="2">
-        <v>45303</v>
-      </c>
-      <c r="M98" s="3">
-        <v>151</v>
-      </c>
-      <c r="S98" s="2">
-        <v>45992</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="M98" s="3"/>
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="4">
-        <v>1298031.3600000001</v>
+        <v>1170000</v>
       </c>
     </row>
     <row r="99" spans="1:22">
@@ -6215,50 +6193,50 @@
         <v>42</v>
       </c>
       <c r="B99" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C99" s="2">
-        <v>45373</v>
+        <v>45215</v>
       </c>
       <c r="D99" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E99" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F99" t="s">
-        <v>42</v>
+        <v>169</v>
       </c>
       <c r="G99" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H99" s="2">
-        <v>45492</v>
+        <v>45687</v>
       </c>
       <c r="I99" s="3">
-        <v>769</v>
+        <v>586</v>
       </c>
       <c r="J99" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K99" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="L99" s="2">
-        <v>45492</v>
+        <v>45685</v>
       </c>
       <c r="M99" s="3">
-        <v>119</v>
+        <v>470</v>
       </c>
       <c r="S99" s="2">
-        <v>46587</v>
+        <v>46780</v>
       </c>
       <c r="T99" s="3">
-        <v>326</v>
+        <v>507</v>
       </c>
       <c r="U99" s="3"/>
       <c r="V99" s="4">
-        <v>1320176.8799999999</v>
+        <v>1220266.1399999999</v>
       </c>
     </row>
     <row r="100" spans="1:22">
@@ -6266,143 +6244,150 @@
         <v>42</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C100" s="2">
-        <v>44663</v>
+        <v>45366</v>
       </c>
       <c r="D100" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E100" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F100" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="G100" t="s">
-        <v>200</v>
+        <v>390</v>
       </c>
       <c r="H100" s="2">
-        <v>45588</v>
+        <v>45481</v>
       </c>
       <c r="I100" s="3">
-        <v>673</v>
+        <v>792</v>
       </c>
       <c r="J100" t="s">
         <v>52</v>
       </c>
       <c r="K100" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="L100" s="2">
-        <v>44893</v>
+        <v>45471</v>
       </c>
       <c r="M100" s="3">
-        <v>230</v>
-      </c>
-      <c r="O100" t="s">
-        <v>59</v>
-      </c>
-      <c r="P100" s="2">
-        <v>45996</v>
+        <v>105</v>
       </c>
       <c r="S100" s="2">
-        <v>45624</v>
-      </c>
-      <c r="T100" s="3"/>
+        <v>47301</v>
+      </c>
+      <c r="T100" s="3">
+        <v>1028</v>
+      </c>
       <c r="U100" s="3"/>
       <c r="V100" s="4">
-        <v>1416380</v>
+        <v>1245414.49</v>
       </c>
     </row>
     <row r="101" spans="1:22">
       <c r="A101" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B101" t="s">
+        <v>392</v>
+      </c>
+      <c r="C101" s="2">
+        <v>45152</v>
+      </c>
+      <c r="D101" t="s">
+        <v>268</v>
+      </c>
+      <c r="E101" t="s">
+        <v>393</v>
+      </c>
+      <c r="F101" t="s">
+        <v>29</v>
+      </c>
+      <c r="G101" t="s">
         <v>394</v>
       </c>
-      <c r="C101" s="2">
-        <v>45826</v>
-      </c>
-      <c r="D101" t="s">
-        <v>24</v>
-      </c>
-      <c r="E101" t="s">
-        <v>395</v>
-      </c>
-      <c r="F101" t="s">
-        <v>66</v>
-      </c>
-      <c r="G101" t="s">
-        <v>396</v>
-      </c>
       <c r="H101" s="2">
-        <v>46079</v>
+        <v>45440</v>
       </c>
       <c r="I101" s="3">
-        <v>182</v>
+        <v>833</v>
       </c>
       <c r="J101" t="s">
         <v>52</v>
       </c>
       <c r="K101" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L101" s="2">
-        <v>46076</v>
+        <v>45303</v>
       </c>
       <c r="M101" s="3">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="S101" s="2">
-        <v>47903</v>
-      </c>
-      <c r="T101" s="3">
-        <v>1642</v>
-      </c>
+        <v>45992</v>
+      </c>
+      <c r="T101" s="3"/>
       <c r="U101" s="3"/>
       <c r="V101" s="4">
-        <v>1435000</v>
+        <v>1298031.3600000001</v>
       </c>
     </row>
     <row r="102" spans="1:22">
       <c r="A102" t="s">
-        <v>398</v>
+        <v>42</v>
       </c>
       <c r="B102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C102" s="2">
-        <v>46150</v>
+        <v>45373</v>
       </c>
       <c r="D102" t="s">
         <v>44</v>
       </c>
       <c r="E102" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F102" t="s">
-        <v>398</v>
+        <v>42</v>
       </c>
       <c r="G102" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="H102" s="2">
-        <v>46206</v>
+        <v>45492</v>
       </c>
       <c r="I102" s="3">
-        <v>55</v>
+        <v>781</v>
       </c>
       <c r="J102" t="s">
         <v>52</v>
       </c>
-      <c r="M102" s="3"/>
-      <c r="T102" s="3"/>
+      <c r="K102" t="s">
+        <v>398</v>
+      </c>
+      <c r="L102" s="2">
+        <v>45492</v>
+      </c>
+      <c r="M102" s="3">
+        <v>119</v>
+      </c>
+      <c r="S102" s="2">
+        <v>46587</v>
+      </c>
+      <c r="T102" s="3">
+        <v>314</v>
+      </c>
       <c r="U102" s="3"/>
       <c r="V102" s="4">
-        <v>1719174</v>
+        <v>1320176.8799999999</v>
       </c>
     </row>
     <row r="103" spans="1:22">
@@ -6410,37 +6395,54 @@
         <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C103" s="2">
-        <v>46094</v>
+        <v>44663</v>
       </c>
       <c r="D103" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E103" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F103" t="s">
-        <v>403</v>
+        <v>128</v>
       </c>
       <c r="G103" t="s">
-        <v>404</v>
+        <v>200</v>
       </c>
       <c r="H103" s="2">
-        <v>46211</v>
+        <v>45588</v>
       </c>
       <c r="I103" s="3">
-        <v>50</v>
+        <v>685</v>
       </c>
       <c r="J103" t="s">
         <v>52</v>
       </c>
-      <c r="M103" s="3"/>
+      <c r="K103" t="s">
+        <v>401</v>
+      </c>
+      <c r="L103" s="2">
+        <v>44893</v>
+      </c>
+      <c r="M103" s="3">
+        <v>230</v>
+      </c>
+      <c r="O103" t="s">
+        <v>59</v>
+      </c>
+      <c r="P103" s="2">
+        <v>45996</v>
+      </c>
+      <c r="S103" s="2">
+        <v>45624</v>
+      </c>
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
       <c r="V103" s="4">
-        <v>1828126.08</v>
+        <v>1416380</v>
       </c>
     </row>
     <row r="104" spans="1:22">
@@ -6448,185 +6450,177 @@
         <v>42</v>
       </c>
       <c r="B104" t="s">
+        <v>402</v>
+      </c>
+      <c r="C104" s="2">
+        <v>45826</v>
+      </c>
+      <c r="D104" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104" t="s">
+        <v>403</v>
+      </c>
+      <c r="F104" t="s">
+        <v>66</v>
+      </c>
+      <c r="G104" t="s">
+        <v>404</v>
+      </c>
+      <c r="H104" s="2">
+        <v>46079</v>
+      </c>
+      <c r="I104" s="3">
+        <v>194</v>
+      </c>
+      <c r="J104" t="s">
+        <v>52</v>
+      </c>
+      <c r="K104" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="2">
-        <v>45950</v>
-      </c>
-      <c r="D104" t="s">
-        <v>44</v>
-      </c>
-      <c r="E104" t="s">
-        <v>406</v>
-      </c>
-      <c r="F104" t="s">
-        <v>42</v>
-      </c>
-      <c r="G104" t="s">
-        <v>407</v>
-      </c>
-      <c r="H104" s="2">
-        <v>45988</v>
-      </c>
-      <c r="I104" s="3">
-        <v>273</v>
-      </c>
-      <c r="J104" t="s">
-        <v>38</v>
-      </c>
-      <c r="K104" t="s">
-        <v>408</v>
-      </c>
       <c r="L104" s="2">
-        <v>45979</v>
+        <v>46076</v>
       </c>
       <c r="M104" s="3">
-        <v>29</v>
+        <v>250</v>
       </c>
       <c r="S104" s="2">
-        <v>46343</v>
+        <v>47903</v>
       </c>
       <c r="T104" s="3">
-        <v>82</v>
+        <v>1630</v>
       </c>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
-        <v>2075682</v>
+        <v>1435000</v>
       </c>
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
-        <v>42</v>
+        <v>406</v>
       </c>
       <c r="B105" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C105" s="2">
-        <v>45511</v>
+        <v>46150</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E105" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F105" t="s">
-        <v>26</v>
+        <v>406</v>
       </c>
       <c r="G105" t="s">
-        <v>411</v>
+        <v>372</v>
       </c>
       <c r="H105" s="2">
-        <v>45786</v>
+        <v>46206</v>
       </c>
       <c r="I105" s="3">
-        <v>475</v>
+        <v>67</v>
       </c>
       <c r="J105" t="s">
-        <v>38</v>
-      </c>
-      <c r="K105" t="s">
-        <v>412</v>
-      </c>
-      <c r="L105" s="2">
-        <v>45794</v>
-      </c>
-      <c r="M105" s="3">
-        <v>283</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="M105" s="3"/>
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
       <c r="V105" s="4">
-        <v>2594055</v>
+        <v>1719174</v>
       </c>
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B106" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C106" s="2">
-        <v>45848</v>
+        <v>46094</v>
       </c>
       <c r="D106" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E106" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F106" t="s">
-        <v>224</v>
+        <v>411</v>
       </c>
       <c r="G106" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="H106" s="2">
-        <v>46014</v>
+        <v>46211</v>
       </c>
       <c r="I106" s="3">
-        <v>247</v>
+        <v>62</v>
       </c>
       <c r="J106" t="s">
-        <v>38</v>
-      </c>
-      <c r="K106" t="s">
-        <v>416</v>
-      </c>
-      <c r="L106" s="2">
-        <v>46008</v>
-      </c>
-      <c r="M106" s="3">
-        <v>160</v>
-      </c>
-      <c r="S106" s="2">
-        <v>46373</v>
-      </c>
-      <c r="T106" s="3">
-        <v>112</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="M106" s="3"/>
+      <c r="T106" s="3"/>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
-        <v>2641069.35</v>
+        <v>1828126.08</v>
       </c>
     </row>
     <row r="107" spans="1:22">
       <c r="A107" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B107" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C107" s="2">
-        <v>46030</v>
+        <v>45950</v>
       </c>
       <c r="D107" t="s">
-        <v>267</v>
+        <v>44</v>
       </c>
       <c r="E107" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F107" t="s">
+        <v>42</v>
+      </c>
+      <c r="G107" t="s">
+        <v>415</v>
+      </c>
+      <c r="H107" s="2">
+        <v>45988</v>
+      </c>
+      <c r="I107" s="3">
+        <v>285</v>
+      </c>
+      <c r="J107" t="s">
+        <v>38</v>
+      </c>
+      <c r="K107" t="s">
+        <v>416</v>
+      </c>
+      <c r="L107" s="2">
+        <v>45979</v>
+      </c>
+      <c r="M107" s="3">
         <v>29</v>
       </c>
-      <c r="G107" t="s">
-        <v>367</v>
-      </c>
-      <c r="H107" s="2">
-        <v>46237</v>
-      </c>
-      <c r="I107" s="3">
-        <v>24</v>
-      </c>
-      <c r="J107" t="s">
-        <v>52</v>
-      </c>
-      <c r="M107" s="3"/>
-      <c r="T107" s="3"/>
+      <c r="S107" s="2">
+        <v>46343</v>
+      </c>
+      <c r="T107" s="3">
+        <v>70</v>
+      </c>
       <c r="U107" s="3"/>
       <c r="V107" s="4">
-        <v>2652975.2799999998</v>
+        <v>2075682</v>
       </c>
     </row>
     <row r="108" spans="1:22">
@@ -6634,390 +6628,369 @@
         <v>42</v>
       </c>
       <c r="B108" t="s">
+        <v>417</v>
+      </c>
+      <c r="C108" s="2">
+        <v>45511</v>
+      </c>
+      <c r="D108" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108" t="s">
+        <v>418</v>
+      </c>
+      <c r="F108" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" t="s">
         <v>419</v>
       </c>
-      <c r="C108" s="2">
-        <v>45365</v>
-      </c>
-      <c r="D108" t="s">
-        <v>35</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="H108" s="2">
+        <v>45786</v>
+      </c>
+      <c r="I108" s="3">
+        <v>487</v>
+      </c>
+      <c r="J108" t="s">
+        <v>38</v>
+      </c>
+      <c r="K108" t="s">
         <v>420</v>
       </c>
-      <c r="F108" t="s">
-        <v>421</v>
-      </c>
-      <c r="G108" t="s">
-        <v>422</v>
-      </c>
-      <c r="H108" s="2">
-        <v>45568</v>
-      </c>
-      <c r="I108" s="3">
-        <v>693</v>
-      </c>
-      <c r="J108" t="s">
-        <v>52</v>
-      </c>
-      <c r="K108" t="s">
-        <v>423</v>
-      </c>
       <c r="L108" s="2">
-        <v>45567</v>
+        <v>45794</v>
       </c>
       <c r="M108" s="3">
-        <v>202</v>
-      </c>
-      <c r="S108" s="2">
-        <v>46479</v>
-      </c>
-      <c r="T108" s="3">
-        <v>218</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="T108" s="3"/>
       <c r="U108" s="3"/>
       <c r="V108" s="4">
-        <v>2780400.6</v>
+        <v>2594055</v>
       </c>
     </row>
     <row r="109" spans="1:22">
       <c r="A109" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B109" t="s">
+        <v>421</v>
+      </c>
+      <c r="C109" s="2">
+        <v>45848</v>
+      </c>
+      <c r="D109" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" t="s">
+        <v>422</v>
+      </c>
+      <c r="F109" t="s">
+        <v>224</v>
+      </c>
+      <c r="G109" t="s">
+        <v>423</v>
+      </c>
+      <c r="H109" s="2">
+        <v>46014</v>
+      </c>
+      <c r="I109" s="3">
+        <v>259</v>
+      </c>
+      <c r="J109" t="s">
+        <v>38</v>
+      </c>
+      <c r="K109" t="s">
         <v>424</v>
       </c>
-      <c r="C109" s="2">
-        <v>46245</v>
-      </c>
-      <c r="D109" t="s">
-        <v>44</v>
-      </c>
-      <c r="E109" t="s">
-        <v>425</v>
-      </c>
-      <c r="F109" t="s">
-        <v>26</v>
-      </c>
-      <c r="G109" t="s">
-        <v>264</v>
-      </c>
-      <c r="H109" s="2">
-        <v>46259</v>
-      </c>
-      <c r="I109" s="3">
-        <v>2</v>
-      </c>
-      <c r="J109" t="s">
-        <v>265</v>
-      </c>
-      <c r="M109" s="3"/>
-      <c r="T109" s="3"/>
+      <c r="L109" s="2">
+        <v>46008</v>
+      </c>
+      <c r="M109" s="3">
+        <v>160</v>
+      </c>
+      <c r="S109" s="2">
+        <v>46373</v>
+      </c>
+      <c r="T109" s="3">
+        <v>100</v>
+      </c>
       <c r="U109" s="3"/>
       <c r="V109" s="4">
-        <v>3446560</v>
+        <v>2641069.35</v>
       </c>
     </row>
     <row r="110" spans="1:22">
       <c r="A110" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B110" t="s">
+        <v>425</v>
+      </c>
+      <c r="C110" s="2">
+        <v>46030</v>
+      </c>
+      <c r="D110" t="s">
+        <v>268</v>
+      </c>
+      <c r="E110" t="s">
         <v>426</v>
       </c>
-      <c r="C110" s="2">
-        <v>46232</v>
-      </c>
-      <c r="D110" t="s">
-        <v>44</v>
-      </c>
-      <c r="E110" t="s">
-        <v>427</v>
-      </c>
       <c r="F110" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G110" t="s">
-        <v>428</v>
+        <v>372</v>
       </c>
       <c r="H110" s="2">
         <v>46237</v>
       </c>
       <c r="I110" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J110" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="M110" s="3"/>
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
       <c r="V110" s="4">
-        <v>3446570</v>
+        <v>2652975.2799999998</v>
       </c>
     </row>
     <row r="111" spans="1:22">
       <c r="A111" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B111" t="s">
+        <v>427</v>
+      </c>
+      <c r="C111" s="2">
+        <v>45365</v>
+      </c>
+      <c r="D111" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" t="s">
+        <v>428</v>
+      </c>
+      <c r="F111" t="s">
         <v>429</v>
       </c>
-      <c r="C111" s="2">
-        <v>45824</v>
-      </c>
-      <c r="D111" t="s">
-        <v>24</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>430</v>
       </c>
-      <c r="F111" t="s">
-        <v>128</v>
-      </c>
-      <c r="G111" t="s">
+      <c r="H111" s="2">
+        <v>45568</v>
+      </c>
+      <c r="I111" s="3">
+        <v>705</v>
+      </c>
+      <c r="J111" t="s">
+        <v>52</v>
+      </c>
+      <c r="K111" t="s">
         <v>431</v>
       </c>
-      <c r="H111" s="2">
-        <v>46255</v>
-      </c>
-      <c r="I111" s="3">
-        <v>6</v>
-      </c>
-      <c r="J111" t="s">
-        <v>270</v>
-      </c>
-      <c r="K111" t="s">
-        <v>432</v>
-      </c>
       <c r="L111" s="2">
-        <v>45951</v>
+        <v>45567</v>
       </c>
       <c r="M111" s="3">
-        <v>127</v>
+        <v>202</v>
       </c>
       <c r="S111" s="2">
-        <v>46316</v>
+        <v>46479</v>
       </c>
       <c r="T111" s="3">
-        <v>55</v>
+        <v>206</v>
       </c>
       <c r="U111" s="3"/>
       <c r="V111" s="4">
-        <v>4130258.58</v>
+        <v>2780400.6</v>
       </c>
     </row>
     <row r="112" spans="1:22">
       <c r="A112" t="s">
+        <v>42</v>
+      </c>
+      <c r="B112" t="s">
+        <v>432</v>
+      </c>
+      <c r="C112" s="2">
+        <v>46245</v>
+      </c>
+      <c r="D112" t="s">
+        <v>44</v>
+      </c>
+      <c r="E112" t="s">
         <v>433</v>
       </c>
-      <c r="B112" t="s">
+      <c r="F112" t="s">
         <v>434</v>
       </c>
-      <c r="C112" s="2">
-        <v>45526</v>
-      </c>
-      <c r="D112" t="s">
-        <v>35</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="G112" t="s">
         <v>435</v>
       </c>
-      <c r="F112" t="s">
-        <v>433</v>
-      </c>
-      <c r="G112" t="s">
-        <v>436</v>
-      </c>
       <c r="H112" s="2">
-        <v>45932</v>
+        <v>46268</v>
       </c>
       <c r="I112" s="3">
-        <v>329</v>
+        <v>5</v>
       </c>
       <c r="J112" t="s">
-        <v>52</v>
-      </c>
-      <c r="K112" t="s">
-        <v>437</v>
+        <v>266</v>
       </c>
       <c r="M112" s="3"/>
-      <c r="S112" s="2">
-        <v>47748</v>
-      </c>
-      <c r="T112" s="3">
-        <v>1487</v>
-      </c>
+      <c r="T112" s="3"/>
       <c r="U112" s="3"/>
       <c r="V112" s="4">
-        <v>4440928.34</v>
+        <v>3446560</v>
       </c>
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
+        <v>42</v>
+      </c>
+      <c r="B113" t="s">
+        <v>436</v>
+      </c>
+      <c r="C113" s="2">
+        <v>46232</v>
+      </c>
+      <c r="D113" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" t="s">
+        <v>437</v>
+      </c>
+      <c r="F113" t="s">
         <v>26</v>
       </c>
-      <c r="B113" t="s">
+      <c r="G113" t="s">
         <v>438</v>
       </c>
-      <c r="C113" s="2">
-        <v>45560</v>
-      </c>
-      <c r="D113" t="s">
-        <v>24</v>
-      </c>
-      <c r="E113" t="s">
-        <v>439</v>
-      </c>
-      <c r="F113" t="s">
-        <v>440</v>
-      </c>
-      <c r="G113" t="s">
-        <v>441</v>
-      </c>
       <c r="H113" s="2">
-        <v>45930</v>
+        <v>46237</v>
       </c>
       <c r="I113" s="3">
-        <v>331</v>
+        <v>36</v>
       </c>
       <c r="J113" t="s">
-        <v>38</v>
-      </c>
-      <c r="K113" t="s">
-        <v>442</v>
-      </c>
-      <c r="L113" s="2">
-        <v>45854</v>
-      </c>
-      <c r="M113" s="3">
-        <v>294</v>
-      </c>
-      <c r="S113" s="2">
-        <v>46950</v>
-      </c>
-      <c r="T113" s="3">
-        <v>689</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M113" s="3"/>
+      <c r="T113" s="3"/>
       <c r="U113" s="3"/>
       <c r="V113" s="4">
-        <v>6210000</v>
+        <v>3446570</v>
       </c>
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>275</v>
+        <v>26</v>
       </c>
       <c r="B114" t="s">
+        <v>439</v>
+      </c>
+      <c r="C114" s="2">
+        <v>45824</v>
+      </c>
+      <c r="D114" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114" t="s">
+        <v>440</v>
+      </c>
+      <c r="F114" t="s">
+        <v>441</v>
+      </c>
+      <c r="G114" t="s">
+        <v>442</v>
+      </c>
+      <c r="H114" s="2">
+        <v>46268</v>
+      </c>
+      <c r="I114" s="3">
+        <v>5</v>
+      </c>
+      <c r="J114" t="s">
+        <v>271</v>
+      </c>
+      <c r="K114" t="s">
         <v>443</v>
       </c>
-      <c r="C114" s="2">
-        <v>44607</v>
-      </c>
-      <c r="D114" t="s">
-        <v>369</v>
-      </c>
-      <c r="E114" t="s">
-        <v>444</v>
-      </c>
-      <c r="F114" t="s">
-        <v>275</v>
-      </c>
-      <c r="G114" t="s">
-        <v>445</v>
-      </c>
-      <c r="H114" s="2">
-        <v>46196</v>
-      </c>
-      <c r="I114" s="3">
-        <v>65</v>
-      </c>
-      <c r="J114" t="s">
-        <v>52</v>
-      </c>
-      <c r="K114" t="s">
-        <v>446</v>
-      </c>
       <c r="L114" s="2">
-        <v>44747</v>
+        <v>45951</v>
       </c>
       <c r="M114" s="3">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="O114" t="s">
-        <v>447</v>
-      </c>
-      <c r="P114" s="2">
-        <v>46573</v>
+        <v>59</v>
       </c>
       <c r="S114" s="2">
-        <v>45111</v>
-      </c>
-      <c r="T114" s="3"/>
-      <c r="U114" s="3">
-        <v>312</v>
-      </c>
+        <v>46316</v>
+      </c>
+      <c r="T114" s="3">
+        <v>43</v>
+      </c>
+      <c r="U114" s="3"/>
       <c r="V114" s="4">
-        <v>6571898.25</v>
+        <v>4130258.58</v>
       </c>
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B115" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C115" s="2">
-        <v>38661</v>
+        <v>45526</v>
       </c>
       <c r="D115" t="s">
         <v>35</v>
       </c>
       <c r="E115" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F115" t="s">
-        <v>26</v>
+        <v>444</v>
       </c>
       <c r="G115" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="H115" s="2">
-        <v>45993</v>
+        <v>45932</v>
       </c>
       <c r="I115" s="3">
-        <v>268</v>
+        <v>341</v>
       </c>
       <c r="J115" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K115" t="s">
-        <v>452</v>
-      </c>
-      <c r="L115" s="2">
-        <v>45993</v>
-      </c>
-      <c r="M115" s="3">
-        <v>7332</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="M115" s="3"/>
       <c r="S115" s="2">
-        <v>46540</v>
+        <v>47748</v>
       </c>
       <c r="T115" s="3">
-        <v>279</v>
+        <v>1475</v>
       </c>
       <c r="U115" s="3"/>
       <c r="V115" s="4">
-        <v>9032000</v>
+        <v>4440928.34</v>
       </c>
     </row>
     <row r="116" spans="1:22">
       <c r="A116" t="s">
-        <v>224</v>
+        <v>26</v>
       </c>
       <c r="B116" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C116" s="2">
         <v>45560</v>
@@ -7026,390 +6999,549 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="F116" t="s">
-        <v>224</v>
+        <v>451</v>
       </c>
       <c r="G116" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H116" s="2">
-        <v>45797</v>
+        <v>45930</v>
       </c>
       <c r="I116" s="3">
-        <v>464</v>
+        <v>343</v>
       </c>
       <c r="J116" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K116" t="s">
-        <v>456</v>
-      </c>
-      <c r="M116" s="3"/>
+        <v>453</v>
+      </c>
+      <c r="L116" s="2">
+        <v>45854</v>
+      </c>
+      <c r="M116" s="3">
+        <v>294</v>
+      </c>
       <c r="S116" s="2">
-        <v>46523</v>
+        <v>46950</v>
       </c>
       <c r="T116" s="3">
-        <v>262</v>
+        <v>677</v>
       </c>
       <c r="U116" s="3"/>
       <c r="V116" s="4">
-        <v>9152353</v>
+        <v>6210000</v>
       </c>
     </row>
     <row r="117" spans="1:22">
       <c r="A117" t="s">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="B117" t="s">
+        <v>454</v>
+      </c>
+      <c r="C117" s="2">
+        <v>44607</v>
+      </c>
+      <c r="D117" t="s">
+        <v>374</v>
+      </c>
+      <c r="E117" t="s">
+        <v>455</v>
+      </c>
+      <c r="F117" t="s">
+        <v>275</v>
+      </c>
+      <c r="G117" t="s">
+        <v>456</v>
+      </c>
+      <c r="H117" s="2">
+        <v>46196</v>
+      </c>
+      <c r="I117" s="3">
+        <v>77</v>
+      </c>
+      <c r="J117" t="s">
+        <v>52</v>
+      </c>
+      <c r="K117" t="s">
         <v>457</v>
       </c>
-      <c r="C117" s="2">
-        <v>44763</v>
-      </c>
-      <c r="D117" t="s">
-        <v>24</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="L117" s="2">
+        <v>44747</v>
+      </c>
+      <c r="M117" s="3">
+        <v>140</v>
+      </c>
+      <c r="O117" t="s">
         <v>458</v>
       </c>
-      <c r="F117" t="s">
-        <v>459</v>
-      </c>
-      <c r="G117" t="s">
-        <v>460</v>
-      </c>
-      <c r="H117" s="2">
-        <v>46259</v>
-      </c>
-      <c r="I117" s="3">
-        <v>2</v>
-      </c>
-      <c r="J117" t="s">
-        <v>270</v>
-      </c>
-      <c r="K117" t="s">
-        <v>461</v>
-      </c>
-      <c r="L117" s="2">
-        <v>45574</v>
-      </c>
-      <c r="M117" s="3">
-        <v>811</v>
-      </c>
-      <c r="O117" t="s">
-        <v>59</v>
-      </c>
       <c r="P117" s="2">
-        <v>46313</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>462</v>
-      </c>
-      <c r="R117" s="2">
-        <v>45786</v>
+        <v>46573</v>
       </c>
       <c r="S117" s="2">
-        <v>45218</v>
+        <v>45111</v>
       </c>
       <c r="T117" s="3"/>
       <c r="U117" s="3">
-        <v>52</v>
+        <v>300</v>
       </c>
       <c r="V117" s="4">
-        <v>10934411.34</v>
+        <v>6571898.25</v>
       </c>
     </row>
     <row r="118" spans="1:22">
       <c r="A118" t="s">
-        <v>26</v>
+        <v>459</v>
       </c>
       <c r="B118" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C118" s="2">
-        <v>45014</v>
+        <v>38661</v>
       </c>
       <c r="D118" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E118" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F118" t="s">
         <v>26</v>
       </c>
       <c r="G118" t="s">
-        <v>367</v>
+        <v>462</v>
       </c>
       <c r="H118" s="2">
-        <v>46219</v>
+        <v>45993</v>
       </c>
       <c r="I118" s="3">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="J118" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K118" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L118" s="2">
-        <v>45148</v>
+        <v>45993</v>
       </c>
       <c r="M118" s="3">
-        <v>134</v>
-      </c>
-      <c r="O118" t="s">
-        <v>360</v>
-      </c>
-      <c r="P118" s="2">
-        <v>46609</v>
+        <v>7332</v>
       </c>
       <c r="S118" s="2">
-        <v>45518</v>
-      </c>
-      <c r="T118" s="3"/>
-      <c r="U118" s="3">
-        <v>348</v>
-      </c>
+        <v>46540</v>
+      </c>
+      <c r="T118" s="3">
+        <v>267</v>
+      </c>
+      <c r="U118" s="3"/>
       <c r="V118" s="4">
-        <v>17946403.739999998</v>
+        <v>9032000</v>
       </c>
     </row>
     <row r="119" spans="1:22">
       <c r="A119" t="s">
+        <v>224</v>
+      </c>
+      <c r="B119" t="s">
+        <v>464</v>
+      </c>
+      <c r="C119" s="2">
+        <v>45560</v>
+      </c>
+      <c r="D119" t="s">
+        <v>24</v>
+      </c>
+      <c r="E119" t="s">
+        <v>465</v>
+      </c>
+      <c r="F119" t="s">
+        <v>224</v>
+      </c>
+      <c r="G119" t="s">
         <v>466</v>
       </c>
-      <c r="B119" t="s">
-        <v>467</v>
-      </c>
-      <c r="C119" s="2">
-        <v>45666</v>
-      </c>
-      <c r="D119" t="s">
-        <v>44</v>
-      </c>
-      <c r="E119" t="s">
-        <v>468</v>
-      </c>
-      <c r="F119" t="s">
-        <v>433</v>
-      </c>
-      <c r="G119" t="s">
-        <v>469</v>
-      </c>
       <c r="H119" s="2">
-        <v>46174</v>
+        <v>45797</v>
       </c>
       <c r="I119" s="3">
-        <v>87</v>
+        <v>476</v>
       </c>
       <c r="J119" t="s">
         <v>52</v>
       </c>
+      <c r="K119" t="s">
+        <v>467</v>
+      </c>
       <c r="M119" s="3"/>
-      <c r="T119" s="3"/>
+      <c r="S119" s="2">
+        <v>46523</v>
+      </c>
+      <c r="T119" s="3">
+        <v>250</v>
+      </c>
       <c r="U119" s="3"/>
       <c r="V119" s="4">
-        <v>31106553.600000001</v>
+        <v>9152353</v>
       </c>
     </row>
     <row r="120" spans="1:22">
       <c r="A120" t="s">
-        <v>433</v>
+        <v>42</v>
       </c>
       <c r="B120" t="s">
+        <v>468</v>
+      </c>
+      <c r="C120" s="2">
+        <v>44763</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120" t="s">
+        <v>469</v>
+      </c>
+      <c r="F120" t="s">
+        <v>441</v>
+      </c>
+      <c r="G120" t="s">
         <v>470</v>
       </c>
-      <c r="C120" s="2">
-        <v>45250</v>
-      </c>
-      <c r="D120" t="s">
-        <v>35</v>
-      </c>
-      <c r="E120" t="s">
+      <c r="H120" s="2">
+        <v>46266</v>
+      </c>
+      <c r="I120" s="3">
+        <v>7</v>
+      </c>
+      <c r="J120" t="s">
+        <v>271</v>
+      </c>
+      <c r="K120" t="s">
         <v>471</v>
       </c>
-      <c r="F120" t="s">
-        <v>433</v>
-      </c>
-      <c r="G120" t="s">
-        <v>472</v>
-      </c>
-      <c r="H120" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I120" s="3">
-        <v>861</v>
-      </c>
-      <c r="J120" t="s">
-        <v>52</v>
-      </c>
-      <c r="K120" t="s">
-        <v>473</v>
-      </c>
       <c r="L120" s="2">
-        <v>45401</v>
+        <v>45574</v>
       </c>
       <c r="M120" s="3">
-        <v>151</v>
+        <v>811</v>
+      </c>
+      <c r="O120" t="s">
+        <v>365</v>
+      </c>
+      <c r="P120" s="2">
+        <v>46313</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>69</v>
+      </c>
+      <c r="R120" s="2">
+        <v>46073</v>
       </c>
       <c r="S120" s="2">
-        <v>47227</v>
-      </c>
-      <c r="T120" s="3">
-        <v>966</v>
-      </c>
-      <c r="U120" s="3"/>
+        <v>45218</v>
+      </c>
+      <c r="T120" s="3"/>
+      <c r="U120" s="3">
+        <v>40</v>
+      </c>
       <c r="V120" s="4">
-        <v>41522909.280000001</v>
+        <v>10934411.34</v>
       </c>
     </row>
     <row r="121" spans="1:22">
       <c r="A121" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B121" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C121" s="2">
-        <v>44238</v>
+        <v>45014</v>
       </c>
       <c r="D121" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E121" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F121" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="G121" t="s">
-        <v>476</v>
+        <v>372</v>
       </c>
       <c r="H121" s="2">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="I121" s="3">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J121" t="s">
         <v>52</v>
       </c>
       <c r="K121" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="L121" s="2">
-        <v>44969</v>
+        <v>45148</v>
       </c>
       <c r="M121" s="3">
-        <v>731</v>
+        <v>134</v>
       </c>
       <c r="O121" t="s">
-        <v>478</v>
+        <v>365</v>
       </c>
       <c r="P121" s="2">
-        <v>46798</v>
+        <v>46609</v>
       </c>
       <c r="S121" s="2">
-        <v>45886</v>
+        <v>45518</v>
       </c>
       <c r="T121" s="3"/>
       <c r="U121" s="3">
-        <v>537</v>
+        <v>336</v>
       </c>
       <c r="V121" s="4">
-        <v>41936400</v>
+        <v>17946403.739999998</v>
       </c>
     </row>
     <row r="122" spans="1:22">
       <c r="A122" t="s">
-        <v>42</v>
+        <v>475</v>
       </c>
       <c r="B122" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C122" s="2">
-        <v>45607</v>
+        <v>45666</v>
       </c>
       <c r="D122" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E122" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F122" t="s">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="G122" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="H122" s="2">
-        <v>45798</v>
+        <v>46174</v>
       </c>
       <c r="I122" s="3">
-        <v>463</v>
+        <v>99</v>
       </c>
       <c r="J122" t="s">
         <v>52</v>
       </c>
-      <c r="K122" t="s">
-        <v>483</v>
-      </c>
-      <c r="L122" s="2">
-        <v>45798</v>
-      </c>
-      <c r="M122" s="3">
-        <v>191</v>
-      </c>
-      <c r="S122" s="2">
-        <v>46712</v>
-      </c>
-      <c r="T122" s="3">
-        <v>451</v>
-      </c>
+      <c r="M122" s="3"/>
+      <c r="T122" s="3"/>
       <c r="U122" s="3"/>
       <c r="V122" s="4">
-        <v>50963796</v>
+        <v>31106553.600000001</v>
       </c>
     </row>
     <row r="123" spans="1:22">
       <c r="A123" t="s">
-        <v>42</v>
+        <v>444</v>
       </c>
       <c r="B123" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C123" s="2">
-        <v>45664</v>
+        <v>45250</v>
       </c>
       <c r="D123" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E123" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F123" t="s">
-        <v>224</v>
+        <v>444</v>
       </c>
       <c r="G123" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="H123" s="2">
-        <v>45958</v>
+        <v>45400</v>
       </c>
       <c r="I123" s="3">
-        <v>303</v>
+        <v>873</v>
       </c>
       <c r="J123" t="s">
-        <v>28</v>
-      </c>
-      <c r="M123" s="3"/>
-      <c r="T123" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="K123" t="s">
+        <v>482</v>
+      </c>
+      <c r="L123" s="2">
+        <v>45401</v>
+      </c>
+      <c r="M123" s="3">
+        <v>151</v>
+      </c>
+      <c r="S123" s="2">
+        <v>47227</v>
+      </c>
+      <c r="T123" s="3">
+        <v>954</v>
+      </c>
       <c r="U123" s="3"/>
       <c r="V123" s="4">
+        <v>41522909.280000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22">
+      <c r="A124" t="s">
+        <v>42</v>
+      </c>
+      <c r="B124" t="s">
+        <v>483</v>
+      </c>
+      <c r="C124" s="2">
+        <v>44238</v>
+      </c>
+      <c r="D124" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124" t="s">
+        <v>484</v>
+      </c>
+      <c r="F124" t="s">
+        <v>66</v>
+      </c>
+      <c r="G124" t="s">
+        <v>485</v>
+      </c>
+      <c r="H124" s="2">
+        <v>46211</v>
+      </c>
+      <c r="I124" s="3">
+        <v>62</v>
+      </c>
+      <c r="J124" t="s">
+        <v>52</v>
+      </c>
+      <c r="K124" t="s">
+        <v>486</v>
+      </c>
+      <c r="L124" s="2">
+        <v>44969</v>
+      </c>
+      <c r="M124" s="3">
+        <v>731</v>
+      </c>
+      <c r="O124" t="s">
+        <v>487</v>
+      </c>
+      <c r="P124" s="2">
+        <v>46798</v>
+      </c>
+      <c r="S124" s="2">
+        <v>45886</v>
+      </c>
+      <c r="T124" s="3"/>
+      <c r="U124" s="3">
+        <v>525</v>
+      </c>
+      <c r="V124" s="4">
+        <v>41936400</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22">
+      <c r="A125" t="s">
+        <v>42</v>
+      </c>
+      <c r="B125" t="s">
+        <v>488</v>
+      </c>
+      <c r="C125" s="2">
+        <v>45607</v>
+      </c>
+      <c r="D125" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125" t="s">
+        <v>489</v>
+      </c>
+      <c r="F125" t="s">
+        <v>490</v>
+      </c>
+      <c r="G125" t="s">
+        <v>491</v>
+      </c>
+      <c r="H125" s="2">
+        <v>45798</v>
+      </c>
+      <c r="I125" s="3">
+        <v>475</v>
+      </c>
+      <c r="J125" t="s">
+        <v>52</v>
+      </c>
+      <c r="K125" t="s">
+        <v>492</v>
+      </c>
+      <c r="L125" s="2">
+        <v>45798</v>
+      </c>
+      <c r="M125" s="3">
+        <v>191</v>
+      </c>
+      <c r="S125" s="2">
+        <v>46712</v>
+      </c>
+      <c r="T125" s="3">
+        <v>439</v>
+      </c>
+      <c r="U125" s="3"/>
+      <c r="V125" s="4">
+        <v>50963796</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22">
+      <c r="A126" t="s">
+        <v>42</v>
+      </c>
+      <c r="B126" t="s">
+        <v>493</v>
+      </c>
+      <c r="C126" s="2">
+        <v>45664</v>
+      </c>
+      <c r="D126" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126" t="s">
+        <v>494</v>
+      </c>
+      <c r="F126" t="s">
+        <v>224</v>
+      </c>
+      <c r="G126" t="s">
+        <v>495</v>
+      </c>
+      <c r="H126" s="2">
+        <v>45958</v>
+      </c>
+      <c r="I126" s="3">
+        <v>315</v>
+      </c>
+      <c r="J126" t="s">
+        <v>28</v>
+      </c>
+      <c r="M126" s="3"/>
+      <c r="T126" s="3"/>
+      <c r="U126" s="3"/>
+      <c r="V126" s="4">
         <v>253382919</v>
       </c>
     </row>

--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maurofilho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6018E3-D313-4BEC-8135-F1BDE64769C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A22586-CD10-4732-80EE-9B660C068DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-825" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="500">
   <si>
     <t>Departamento</t>
   </si>
@@ -152,6 +152,27 @@
   </si>
   <si>
     <t>DOD CRIADO ETP E MAPA DE RISCOS EM DIGITAÇÃO.</t>
+  </si>
+  <si>
+    <t>202600005028452</t>
+  </si>
+  <si>
+    <t>SISLOG  122354 PACS</t>
+  </si>
+  <si>
+    <t>NOVA CONTRATAÇÃO. AGUARDANDO RETORNO GESAD PARA QUANTITATIVOS.</t>
+  </si>
+  <si>
+    <t>Aquisição</t>
+  </si>
+  <si>
+    <t>202600005028892</t>
+  </si>
+  <si>
+    <t>SISLOG 122408 Inscrições - XXI CBIS 2026</t>
+  </si>
+  <si>
+    <t>SOLICITADA ASSINATURAS ETP DIANA E TIBIRIÇA</t>
   </si>
   <si>
     <t>GETEC</t>
@@ -471,7 +492,7 @@
   </si>
   <si>
     <t>DESPACHO 189 GETEC.Considerando a expiração do prazo de publicação de edital no comprasnet, sendo que desde então as licitações se processam apenas no SISLOG;
-Considerando a semelhança do objeto com o contido no Contrato 86 (53173477), assinado em 30/10/2023 e publicado no dia seguinte;Retornem os autos à origem para verificar se ainda persiste a necessidade da licitação, sendo que em caso positivo deverá ser incluída no SISLOG. Em caso negativo, sugere-se a conclusão da tramitação deste processo na unidade.. PROCESSO DEVERÁ SER CANCELADO. CONCLUIDO NA GETEC</t>
+Considerando a semelhança do objeto com o contido no Contrato 86 (53173477), assinado em 30/10/2023 e publicado no dia seguinte;Retornem os autos à origem para verificar se ainda persiste a necessidade da licitação, sendo que em caso positivo deverá ser incluída no SISLOG. Em caso negativo, sugere-se a conclusão da tramitação deste processo na unidade.. PROCESSO DEVERÁ SER CANCELADO. Concluído NA GETEC</t>
   </si>
   <si>
     <t>202300010020827</t>
@@ -843,13 +864,10 @@
     <t>SISLOG 122001 - Aquisição de Workstations</t>
   </si>
   <si>
-    <t>GEFIN CACTIC</t>
-  </si>
-  <si>
-    <t>para conhecimento e providências.</t>
-  </si>
-  <si>
-    <t>Aquisição</t>
+    <t>GELIC  CACTIC</t>
+  </si>
+  <si>
+    <t>PARA CONTINUIDADE</t>
   </si>
   <si>
     <t>202600010023321</t>
@@ -861,9 +879,6 @@
     <t>Doação de 105 desktops para o CISCENO</t>
   </si>
   <si>
-    <t>PARA CONTINUIDADE</t>
-  </si>
-  <si>
     <t>Em Renovação</t>
   </si>
   <si>
@@ -873,93 +888,96 @@
     <t>SISLOG 121437 KIT MOUSE E TECLADO COM FIO</t>
   </si>
   <si>
+    <t>para que realize a análise técnica da minuta de contrato.</t>
+  </si>
+  <si>
+    <t>GEIN</t>
+  </si>
+  <si>
+    <t>202600010030662</t>
+  </si>
+  <si>
+    <t>Sislog 120082 -Ingressos do CONSAD-feito pelo GECG</t>
+  </si>
+  <si>
+    <t>ANEXO II</t>
+  </si>
+  <si>
+    <t>202600005015076</t>
+  </si>
+  <si>
+    <t>119902 Ingresso participação no Simpósio SBCAS 2026</t>
+  </si>
+  <si>
+    <t>Emitida a nota de empenho, encaminhem-se os autos à SUTIS para conhecimento e demais providências cabíveis.</t>
+  </si>
+  <si>
+    <t>202600005015052</t>
+  </si>
+  <si>
+    <t>119899 - Aquisição de ingresso para a participação no Simpósio Brasileiro de Sistemas de Informação (SBSI)</t>
+  </si>
+  <si>
+    <t>202500005019071</t>
+  </si>
+  <si>
+    <t>SISLOG 114940  - Kits Mouse &amp; teclado com fio/sem fio</t>
+  </si>
+  <si>
+    <t>Comunicamos que o julgamento do Pregão Eletrônico 173/2025, objeto em epígrafe, realizar-se-á dia 14/10/2025 (terça-feira) às 09:00 h,</t>
+  </si>
+  <si>
+    <t>202400005028451</t>
+  </si>
+  <si>
+    <t>SISLOG 108212 estabilizador de tensão, potência mínima de 500 va, tensão de 220 v, capacidade mínima para 4 tomada - SEI nº 202500010009280 - Digitalizado e encaminhado a GCC</t>
+  </si>
+  <si>
+    <t>Extrato de Publicação - Contrato 13 (71284812). E-mail 71304720 ao fornecedor.contato@brasillprodutos.com.br. Aguardando a publicação no PNCP para o início da contagem da vigência, conforme a Cláusula Quarta.</t>
+  </si>
+  <si>
+    <t>13/2025</t>
+  </si>
+  <si>
+    <t>202500005000064</t>
+  </si>
+  <si>
+    <t>SISLOG 111806 CERTIFICADOS DIGITAIS PROCESSO PRÉVIO  202400010046932. Processo paralelo da contratação: SEI 202500010039434.</t>
+  </si>
+  <si>
+    <t>CONTRATO EM GESTÃO DA GETEC</t>
+  </si>
+  <si>
+    <t>50/2025</t>
+  </si>
+  <si>
+    <t>202400010051978</t>
+  </si>
+  <si>
+    <t>Aquisição de Suprimentos de Informática diversos, Estabilizador ,Pen drive - 32 GBHeadset (Fone de ouvido) derivado da Ata de Registro de Preços nº 004/2024 - SEAD/GECC resultante do Pregão Eletrônico 'SRP' nº 001/2023 (processo SEI nº 202100005019301). Aditivo ao Contrato nº 113/2024/SES no percentual de 25% (vinte e cinco por cento) – BRASLYNC</t>
+  </si>
+  <si>
+    <t>113/2024</t>
+  </si>
+  <si>
+    <t>202500010034499</t>
+  </si>
+  <si>
+    <t>ADESÃO A ARP PARA AQUISIÇÃO DE WORKSTATION PARA O LACEN</t>
+  </si>
+  <si>
+    <t>Está no LACEN para gestão CONTRATO</t>
+  </si>
+  <si>
+    <t>202500005035836</t>
+  </si>
+  <si>
+    <t>SISLOG 117278 - Aquisição de kits de Mouse e Teclado com e sem fio</t>
+  </si>
+  <si>
     <t>GELIC</t>
   </si>
   <si>
-    <t>GEIN</t>
-  </si>
-  <si>
-    <t>202600010030662</t>
-  </si>
-  <si>
-    <t>Sislog 120082 -Ingressos do CONSAD-feito pelo GECG</t>
-  </si>
-  <si>
-    <t>ANEXO II</t>
-  </si>
-  <si>
-    <t>202600005015076</t>
-  </si>
-  <si>
-    <t>119902 Ingresso participação no Simpósio SBCAS 2026</t>
-  </si>
-  <si>
-    <t>Emitida a nota de empenho, encaminhem-se os autos à SUTIS para conhecimento e demais providências cabíveis.</t>
-  </si>
-  <si>
-    <t>202600005015052</t>
-  </si>
-  <si>
-    <t>119899 - Aquisição de ingresso para a participação no Simpósio Brasileiro de Sistemas de Informação (SBSI)</t>
-  </si>
-  <si>
-    <t>202500005019071</t>
-  </si>
-  <si>
-    <t>SISLOG 114940  - Kits Mouse &amp; teclado com fio/sem fio</t>
-  </si>
-  <si>
-    <t>Comunicamos que o julgamento do Pregão Eletrônico 173/2025, objeto em epígrafe, realizar-se-á dia 14/10/2025 (terça-feira) às 09:00 h,</t>
-  </si>
-  <si>
-    <t>202400005028451</t>
-  </si>
-  <si>
-    <t>SISLOG 108212 estabilizador de tensão, potência mínima de 500 va, tensão de 220 v, capacidade mínima para 4 tomada - SEI nº 202500010009280 - Digitalizado e encaminhado a GCC</t>
-  </si>
-  <si>
-    <t>Extrato de Publicação - Contrato 13 (71284812). E-mail 71304720 ao fornecedor.contato@brasillprodutos.com.br. Aguardando a publicação no PNCP para o início da contagem da vigência, conforme a Cláusula Quarta.</t>
-  </si>
-  <si>
-    <t>13/2025</t>
-  </si>
-  <si>
-    <t>202500005000064</t>
-  </si>
-  <si>
-    <t>SISLOG 111806 CERTIFICADOS DIGITAIS PROCESSO PRÉVIO  202400010046932. Processo paralelo da contratação: SEI 202500010039434.</t>
-  </si>
-  <si>
-    <t>CONTRATO EM GESTÃO DA GETEC</t>
-  </si>
-  <si>
-    <t>50/2025</t>
-  </si>
-  <si>
-    <t>202400010051978</t>
-  </si>
-  <si>
-    <t>Aquisição de Suprimentos de Informática diversos, Estabilizador ,Pen drive - 32 GBHeadset (Fone de ouvido) derivado da Ata de Registro de Preços nº 004/2024 - SEAD/GECC resultante do Pregão Eletrônico 'SRP' nº 001/2023 (processo SEI nº 202100005019301). Aditivo ao Contrato nº 113/2024/SES no percentual de 25% (vinte e cinco por cento) – BRASLYNC</t>
-  </si>
-  <si>
-    <t>113/2024</t>
-  </si>
-  <si>
-    <t>202500010034499</t>
-  </si>
-  <si>
-    <t>ADESÃO A ARP PARA AQUISIÇÃO DE WORKSTATION PARA O LACEN</t>
-  </si>
-  <si>
-    <t>Está no LACEN para gestão CONTRATO</t>
-  </si>
-  <si>
-    <t>202500005035836</t>
-  </si>
-  <si>
-    <t>SISLOG 117278 - Aquisição de kits de Mouse e Teclado com e sem fio</t>
-  </si>
-  <si>
     <t>houve a apresentação de propostas, as quais foram todas desclassificadas e/ou os licitantes inabilitados, inviabilizando a adjudicação do objeto, declaro o certame FRACASSADO.</t>
   </si>
   <si>
@@ -1056,16 +1074,16 @@
     <t>SISLOG 122416 - Adesão À ARP 010/2025 MGI. 300 monitores 24"</t>
   </si>
   <si>
-    <t>AUTORIZADA ADESÃO PELA UNIDADE GERENCIADORA NO SIASG</t>
+    <t>GCC GCC/SEAD</t>
+  </si>
+  <si>
+    <t>GCC PORTA4RIA. AGUARDANDO OFÍCIO AUTORIZAÇÃO SEAD</t>
   </si>
   <si>
     <t>202600005026702</t>
   </si>
   <si>
     <t>SISLOG 121994- Aquisição Webcam e Headset</t>
-  </si>
-  <si>
-    <t>GEFIN</t>
   </si>
   <si>
     <t>202500010044120</t>
@@ -1181,7 +1199,7 @@
     <t xml:space="preserve"> FORNECEDOR  TECNISYS.Contratação Especialista em BigData</t>
   </si>
   <si>
-    <t>GESTÃO DO CONTRATO PELA GESAD</t>
+    <t>AGUARDANDO DEFINIÇÃO DE QUANTITATIVOS PARA NOVO ETP</t>
   </si>
   <si>
     <t>13/2023</t>
@@ -1202,7 +1220,7 @@
     <t>SISLOG 122292 - Adesão À ARP 020/2026. 100 notebooks</t>
   </si>
   <si>
-    <t>DOD E ETP OFÍCIO FORNECEDOR</t>
+    <t>FALTA OFÍCIO FORNECEDOR. GEPO AGUARDANDO CREDITO SUPLEMENTAR</t>
   </si>
   <si>
     <t>202300005025650</t>
@@ -1355,10 +1373,7 @@
     <t>SISLOG 121821 ARP nº 001/2026 do TJ-GO - 500 micromputadores</t>
   </si>
   <si>
-    <t>CACTIC GEPO</t>
-  </si>
-  <si>
-    <t>GEPO NÃO EMITIU ANEXO II</t>
+    <t>CACTIC FAVORÁVEL. AGUARDANDO CREDITO SUPLEMENTAR</t>
   </si>
   <si>
     <t>202600010062463</t>
@@ -1379,7 +1394,7 @@
     <t>PROCSET</t>
   </si>
   <si>
-    <t>Feita a minuta do 1º Termo Aditivo, encaminho o processo à PROCSET para apreciação.</t>
+    <t>Aguardando Parecer Jurídico</t>
   </si>
   <si>
     <t>93/2025</t>
@@ -1524,10 +1539,7 @@
     <t>Sislog: 110233 OMNICHANNELL e CALLCENTER - Processo SEI Paralelo para Contratos- 202500010021689</t>
   </si>
   <si>
-    <t>SUVISA</t>
-  </si>
-  <si>
-    <t>CONTRATO SOB A GESTÃO DA SUVISA</t>
+    <t>AGUARDANDO PARECER PARA ENVIO A PGE</t>
   </si>
   <si>
     <t>32/2025</t>
@@ -1904,7 +1916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V126"/>
+  <dimension ref="A1:V128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -2001,7 +2013,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -2037,7 +2049,7 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J3" t="s">
         <v>28</v>
@@ -2073,7 +2085,7 @@
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="J4" t="s">
         <v>38</v>
@@ -2109,7 +2121,7 @@
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J5" t="s">
         <v>28</v>
@@ -2121,153 +2133,119 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="2">
-        <v>43091</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
         <v>44</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" s="2">
+        <v>46266</v>
+      </c>
+      <c r="I6" s="3">
+        <v>9</v>
+      </c>
+      <c r="J6" t="s">
         <v>45</v>
       </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="2">
-        <v>45141</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1132</v>
-      </c>
-      <c r="J6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" t="s">
-        <v>47</v>
-      </c>
       <c r="M6" s="3"/>
-      <c r="O6" t="s">
-        <v>48</v>
-      </c>
-      <c r="P6" s="2">
-        <v>45336</v>
-      </c>
-      <c r="S6" s="2">
-        <v>43130</v>
-      </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="4"/>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2">
-        <v>43516</v>
+        <v>46267</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H7" s="2">
-        <v>45140</v>
+        <v>46275</v>
       </c>
       <c r="I7" s="3">
-        <v>1133</v>
+        <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="2">
-        <v>44047</v>
-      </c>
-      <c r="M7" s="3">
-        <v>531</v>
-      </c>
-      <c r="O7" t="s">
-        <v>54</v>
-      </c>
-      <c r="P7" s="2">
-        <v>46023</v>
-      </c>
-      <c r="S7" s="2">
-        <v>44259</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="M7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="4"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2">
+        <v>43091</v>
+      </c>
+      <c r="D8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="2">
+        <v>45141</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1134</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="3"/>
+      <c r="O8" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="2">
-        <v>43770</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="2">
-        <v>45198</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1075</v>
-      </c>
-      <c r="J8" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="2">
-        <v>44176</v>
-      </c>
-      <c r="M8" s="3">
-        <v>406</v>
-      </c>
-      <c r="O8" t="s">
-        <v>59</v>
-      </c>
       <c r="P8" s="2">
-        <v>45646</v>
+        <v>45336</v>
       </c>
       <c r="S8" s="2">
-        <v>45282</v>
+        <v>43130</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2275,47 +2253,52 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2">
-        <v>43902</v>
+        <v>43516</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
       </c>
       <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="2">
+        <v>45140</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1135</v>
+      </c>
+      <c r="J9" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="2">
+        <v>44047</v>
+      </c>
+      <c r="M9" s="3">
+        <v>531</v>
+      </c>
+      <c r="O9" t="s">
         <v>61</v>
       </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="2">
-        <v>45702</v>
-      </c>
-      <c r="I9" s="3">
-        <v>571</v>
-      </c>
-      <c r="J9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" s="3"/>
-      <c r="O9" t="s">
-        <v>54</v>
-      </c>
       <c r="P9" s="2">
-        <v>45794</v>
+        <v>46023</v>
       </c>
       <c r="S9" s="2">
-        <v>44917</v>
+        <v>44259</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -2323,47 +2306,52 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
-        <v>44176</v>
+        <v>43770</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H10" s="2">
-        <v>45372</v>
+        <v>45198</v>
       </c>
       <c r="I10" s="3">
-        <v>901</v>
+        <v>1077</v>
       </c>
       <c r="J10" t="s">
         <v>38</v>
       </c>
       <c r="K10" t="s">
-        <v>68</v>
-      </c>
-      <c r="M10" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="L10" s="2">
+        <v>44176</v>
+      </c>
+      <c r="M10" s="3">
+        <v>406</v>
+      </c>
       <c r="O10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P10" s="2">
-        <v>45505</v>
+        <v>45646</v>
       </c>
       <c r="S10" s="2">
-        <v>44431</v>
+        <v>45282</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -2371,47 +2359,47 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C11" s="2">
-        <v>44181</v>
+        <v>43902</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H11" s="2">
-        <v>45453</v>
+        <v>45702</v>
       </c>
       <c r="I11" s="3">
-        <v>820</v>
+        <v>573</v>
       </c>
       <c r="J11" t="s">
         <v>28</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M11" s="3"/>
       <c r="O11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P11" s="2">
-        <v>45499</v>
+        <v>45794</v>
       </c>
       <c r="S11" s="2">
-        <v>45499</v>
+        <v>44917</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -2419,46 +2407,47 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="2">
+        <v>44176</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="2">
-        <v>44448</v>
-      </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="H12" s="2">
+        <v>45372</v>
+      </c>
+      <c r="I12" s="3">
+        <v>903</v>
+      </c>
+      <c r="J12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" t="s">
         <v>75</v>
       </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="2">
-        <v>44980</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1293</v>
-      </c>
-      <c r="J12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="M12" s="3"/>
+      <c r="O12" t="s">
         <v>76</v>
       </c>
-      <c r="L12" s="2">
-        <v>44727</v>
-      </c>
-      <c r="M12" s="3">
-        <v>279</v>
+      <c r="P12" s="2">
+        <v>45505</v>
       </c>
       <c r="S12" s="2">
-        <v>45829</v>
+        <v>44431</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -2466,46 +2455,47 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
         <v>77</v>
       </c>
       <c r="C13" s="2">
-        <v>44628</v>
+        <v>44181</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
         <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>79</v>
       </c>
       <c r="H13" s="2">
-        <v>45107</v>
+        <v>45453</v>
       </c>
       <c r="I13" s="3">
-        <v>1166</v>
+        <v>822</v>
       </c>
       <c r="J13" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="K13" t="s">
         <v>80</v>
       </c>
-      <c r="L13" s="2">
-        <v>45040</v>
-      </c>
-      <c r="M13" s="3">
-        <v>412</v>
+      <c r="M13" s="3"/>
+      <c r="O13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P13" s="2">
+        <v>45499</v>
       </c>
       <c r="S13" s="2">
-        <v>45427</v>
+        <v>45499</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -2513,46 +2503,46 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C14" s="2">
-        <v>44628</v>
+        <v>44448</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="H14" s="2">
-        <v>45154</v>
+        <v>44980</v>
       </c>
       <c r="I14" s="3">
-        <v>1119</v>
+        <v>1295</v>
       </c>
       <c r="J14" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K14" t="s">
         <v>83</v>
       </c>
       <c r="L14" s="2">
-        <v>45040</v>
+        <v>44727</v>
       </c>
       <c r="M14" s="3">
-        <v>412</v>
+        <v>279</v>
       </c>
       <c r="S14" s="2">
-        <v>45427</v>
+        <v>45829</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -2560,10 +2550,10 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C15" s="2">
         <v>44628</v>
@@ -2572,25 +2562,25 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" s="2">
-        <v>45189</v>
+        <v>45107</v>
       </c>
       <c r="I15" s="3">
-        <v>1084</v>
+        <v>1168</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
       </c>
       <c r="K15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L15" s="2">
         <v>45040</v>
@@ -2607,10 +2597,10 @@
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C16" s="2">
         <v>44628</v>
@@ -2619,25 +2609,25 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2">
-        <v>45145</v>
+        <v>45154</v>
       </c>
       <c r="I16" s="3">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="J16" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L16" s="2">
         <v>45040</v>
@@ -2654,10 +2644,10 @@
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C17" s="2">
         <v>44628</v>
@@ -2666,25 +2656,25 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H17" s="2">
-        <v>45107</v>
+        <v>45189</v>
       </c>
       <c r="I17" s="3">
-        <v>1166</v>
+        <v>1086</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
       </c>
       <c r="K17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L17" s="2">
         <v>45040</v>
@@ -2701,10 +2691,10 @@
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C18" s="2">
         <v>44628</v>
@@ -2713,22 +2703,22 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F18" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="G18" t="s">
         <v>95</v>
       </c>
       <c r="H18" s="2">
-        <v>45208</v>
+        <v>45145</v>
       </c>
       <c r="I18" s="3">
-        <v>1065</v>
+        <v>1130</v>
       </c>
       <c r="J18" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K18" t="s">
         <v>96</v>
@@ -2748,10 +2738,10 @@
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C19" s="2">
         <v>44628</v>
@@ -2763,7 +2753,7 @@
         <v>97</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G19" t="s">
         <v>98</v>
@@ -2772,10 +2762,10 @@
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="J19" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K19" t="s">
         <v>99</v>
@@ -2795,82 +2785,93 @@
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C20" s="2">
-        <v>44713</v>
+        <v>44628</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
       </c>
       <c r="E20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s">
         <v>101</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>102</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" s="2">
+        <v>45208</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1067</v>
+      </c>
+      <c r="J20" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" t="s">
         <v>103</v>
       </c>
-      <c r="H20" s="2">
-        <v>45034</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1239</v>
-      </c>
-      <c r="J20" t="s">
-        <v>28</v>
-      </c>
-      <c r="M20" s="3"/>
+      <c r="L20" s="2">
+        <v>45040</v>
+      </c>
+      <c r="M20" s="3">
+        <v>412</v>
+      </c>
+      <c r="S20" s="2">
+        <v>45427</v>
+      </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="4"/>
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C21" s="2">
-        <v>44715</v>
+        <v>44628</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
       </c>
       <c r="E21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" t="s">
         <v>105</v>
       </c>
-      <c r="F21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" t="s">
-        <v>106</v>
-      </c>
       <c r="H21" s="2">
-        <v>45152</v>
+        <v>45107</v>
       </c>
       <c r="I21" s="3">
-        <v>1121</v>
+        <v>1168</v>
       </c>
       <c r="J21" t="s">
         <v>38</v>
       </c>
       <c r="K21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L21" s="2">
-        <v>45112</v>
+        <v>45040</v>
       </c>
       <c r="M21" s="3">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="S21" s="2">
-        <v>45480</v>
+        <v>45427</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
@@ -2878,91 +2879,82 @@
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="2">
+        <v>44713</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
         <v>108</v>
       </c>
-      <c r="C22" s="2">
-        <v>44721</v>
-      </c>
-      <c r="D22" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>109</v>
-      </c>
-      <c r="F22" t="s">
-        <v>42</v>
       </c>
       <c r="G22" t="s">
         <v>110</v>
       </c>
       <c r="H22" s="2">
-        <v>44908</v>
+        <v>45034</v>
       </c>
       <c r="I22" s="3">
-        <v>1365</v>
+        <v>1241</v>
       </c>
       <c r="J22" t="s">
-        <v>52</v>
-      </c>
-      <c r="K22" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="2">
-        <v>44893</v>
-      </c>
-      <c r="M22" s="3">
-        <v>172</v>
-      </c>
-      <c r="S22" s="2">
-        <v>45624</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="4"/>
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="2">
+        <v>44715</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
         <v>112</v>
       </c>
-      <c r="C23" s="2">
-        <v>44741</v>
-      </c>
-      <c r="D23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" t="s">
         <v>113</v>
       </c>
-      <c r="F23" t="s">
-        <v>114</v>
-      </c>
-      <c r="G23" t="s">
-        <v>115</v>
-      </c>
       <c r="H23" s="2">
-        <v>45007</v>
+        <v>45152</v>
       </c>
       <c r="I23" s="3">
-        <v>1266</v>
+        <v>1123</v>
       </c>
       <c r="J23" t="s">
         <v>38</v>
       </c>
       <c r="K23" t="s">
-        <v>116</v>
-      </c>
-      <c r="M23" s="3"/>
-      <c r="N23" t="s">
-        <v>117</v>
+        <v>114</v>
+      </c>
+      <c r="L23" s="2">
+        <v>45112</v>
+      </c>
+      <c r="M23" s="3">
+        <v>397</v>
       </c>
       <c r="S23" s="2">
-        <v>45220</v>
+        <v>45480</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -2970,82 +2962,91 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="2">
+        <v>44721</v>
+      </c>
+      <c r="D24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" s="2">
+        <v>44908</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1367</v>
+      </c>
+      <c r="J24" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="2">
-        <v>44883</v>
-      </c>
-      <c r="D24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="2">
-        <v>45202</v>
-      </c>
-      <c r="I24" s="3">
-        <v>1071</v>
-      </c>
-      <c r="J24" t="s">
-        <v>28</v>
-      </c>
-      <c r="M24" s="3"/>
+      <c r="L24" s="2">
+        <v>44893</v>
+      </c>
+      <c r="M24" s="3">
+        <v>172</v>
+      </c>
+      <c r="S24" s="2">
+        <v>45624</v>
+      </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="4"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="2">
+        <v>44741</v>
+      </c>
+      <c r="D25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="2">
-        <v>44911</v>
-      </c>
-      <c r="D25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>122</v>
       </c>
-      <c r="F25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" t="s">
-        <v>51</v>
-      </c>
       <c r="H25" s="2">
-        <v>45226</v>
+        <v>45007</v>
       </c>
       <c r="I25" s="3">
-        <v>1047</v>
+        <v>1268</v>
       </c>
       <c r="J25" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K25" t="s">
         <v>123</v>
       </c>
-      <c r="L25" s="2">
-        <v>45217</v>
-      </c>
-      <c r="M25" s="3">
-        <v>306</v>
+      <c r="M25" s="3"/>
+      <c r="N25" t="s">
+        <v>124</v>
       </c>
       <c r="S25" s="2">
-        <v>45591</v>
+        <v>45220</v>
       </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -3053,78 +3054,67 @@
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C26" s="2">
-        <v>44911</v>
+        <v>44883</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="H26" s="2">
-        <v>45224</v>
+        <v>45202</v>
       </c>
       <c r="I26" s="3">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="J26" t="s">
-        <v>52</v>
-      </c>
-      <c r="K26" t="s">
-        <v>125</v>
-      </c>
-      <c r="L26" s="2">
-        <v>45217</v>
-      </c>
-      <c r="M26" s="3">
-        <v>306</v>
-      </c>
-      <c r="S26" s="2">
-        <v>45591</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="4"/>
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C27" s="2">
-        <v>45229</v>
+        <v>44911</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F27" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="G27" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="H27" s="2">
-        <v>45481</v>
+        <v>45226</v>
       </c>
       <c r="I27" s="3">
-        <v>792</v>
+        <v>1049</v>
       </c>
       <c r="J27" t="s">
         <v>38</v>
@@ -3132,9 +3122,14 @@
       <c r="K27" t="s">
         <v>130</v>
       </c>
-      <c r="M27" s="3"/>
+      <c r="L27" s="2">
+        <v>45217</v>
+      </c>
+      <c r="M27" s="3">
+        <v>306</v>
+      </c>
       <c r="S27" s="2">
-        <v>45828</v>
+        <v>45591</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -3142,46 +3137,46 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="2">
+        <v>44911</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
         <v>131</v>
       </c>
-      <c r="C28" s="2">
-        <v>44949</v>
-      </c>
-      <c r="D28" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" t="s">
+        <v>58</v>
+      </c>
+      <c r="H28" s="2">
+        <v>45224</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1051</v>
+      </c>
+      <c r="J28" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" t="s">
         <v>132</v>
       </c>
-      <c r="F28" t="s">
-        <v>133</v>
-      </c>
-      <c r="G28" t="s">
-        <v>134</v>
-      </c>
-      <c r="H28" s="2">
-        <v>45134</v>
-      </c>
-      <c r="I28" s="3">
-        <v>1139</v>
-      </c>
-      <c r="J28" t="s">
-        <v>52</v>
-      </c>
-      <c r="K28" t="s">
-        <v>135</v>
-      </c>
       <c r="L28" s="2">
-        <v>45112</v>
+        <v>45217</v>
       </c>
       <c r="M28" s="3">
-        <v>163</v>
+        <v>306</v>
       </c>
       <c r="S28" s="2">
-        <v>46160</v>
+        <v>45591</v>
       </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
@@ -3189,103 +3184,120 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="2">
+        <v>45229</v>
+      </c>
+      <c r="D29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" t="s">
+        <v>135</v>
+      </c>
+      <c r="G29" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="2">
-        <v>44988</v>
-      </c>
-      <c r="D29" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="H29" s="2">
+        <v>45481</v>
+      </c>
+      <c r="I29" s="3">
+        <v>794</v>
+      </c>
+      <c r="J29" t="s">
+        <v>38</v>
+      </c>
+      <c r="K29" t="s">
         <v>137</v>
       </c>
-      <c r="F29" t="s">
-        <v>42</v>
-      </c>
-      <c r="G29" t="s">
-        <v>138</v>
-      </c>
-      <c r="H29" s="2">
-        <v>45043</v>
-      </c>
-      <c r="I29" s="3">
-        <v>1230</v>
-      </c>
-      <c r="J29" t="s">
-        <v>28</v>
-      </c>
       <c r="M29" s="3"/>
+      <c r="S29" s="2">
+        <v>45828</v>
+      </c>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="4"/>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="2">
+        <v>44949</v>
+      </c>
+      <c r="D30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" t="s">
         <v>139</v>
       </c>
-      <c r="C30" s="2">
-        <v>45015</v>
-      </c>
-      <c r="D30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>140</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>141</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" s="2">
+        <v>45134</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1141</v>
+      </c>
+      <c r="J30" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" t="s">
         <v>142</v>
       </c>
-      <c r="H30" s="2">
-        <v>45395</v>
-      </c>
-      <c r="I30" s="3">
-        <v>878</v>
-      </c>
-      <c r="J30" t="s">
-        <v>28</v>
-      </c>
-      <c r="M30" s="3"/>
+      <c r="L30" s="2">
+        <v>45112</v>
+      </c>
+      <c r="M30" s="3">
+        <v>163</v>
+      </c>
+      <c r="S30" s="2">
+        <v>46160</v>
+      </c>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="4"/>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
         <v>143</v>
       </c>
       <c r="C31" s="2">
-        <v>45027</v>
+        <v>44988</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
         <v>144</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G31" t="s">
         <v>145</v>
       </c>
       <c r="H31" s="2">
-        <v>45251</v>
+        <v>45043</v>
       </c>
       <c r="I31" s="3">
-        <v>1022</v>
+        <v>1232</v>
       </c>
       <c r="J31" t="s">
         <v>28</v>
@@ -3297,60 +3309,49 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
         <v>146</v>
       </c>
       <c r="C32" s="2">
-        <v>45030</v>
+        <v>45015</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
         <v>147</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="G32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H32" s="2">
-        <v>45175</v>
+        <v>45395</v>
       </c>
       <c r="I32" s="3">
-        <v>1098</v>
+        <v>880</v>
       </c>
       <c r="J32" t="s">
-        <v>38</v>
-      </c>
-      <c r="K32" t="s">
-        <v>149</v>
-      </c>
-      <c r="L32" s="2">
-        <v>45161</v>
-      </c>
-      <c r="M32" s="3">
-        <v>131</v>
-      </c>
-      <c r="S32" s="2">
-        <v>45563</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="4"/>
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
         <v>150</v>
       </c>
       <c r="C33" s="2">
-        <v>45056</v>
+        <v>45027</v>
       </c>
       <c r="D33" t="s">
         <v>24</v>
@@ -3359,138 +3360,149 @@
         <v>151</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="G33" t="s">
         <v>152</v>
       </c>
       <c r="H33" s="2">
-        <v>45400</v>
+        <v>45251</v>
       </c>
       <c r="I33" s="3">
-        <v>873</v>
+        <v>1024</v>
       </c>
       <c r="J33" t="s">
-        <v>38</v>
-      </c>
-      <c r="K33" t="s">
-        <v>153</v>
-      </c>
-      <c r="L33" s="2">
-        <v>45400</v>
-      </c>
-      <c r="M33" s="3">
-        <v>344</v>
-      </c>
-      <c r="S33" s="2">
-        <v>45765</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="4"/>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="2">
+        <v>45030</v>
+      </c>
+      <c r="D34" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" t="s">
         <v>154</v>
       </c>
-      <c r="C34" s="2">
-        <v>45056</v>
-      </c>
-      <c r="D34" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>49</v>
+      </c>
+      <c r="G34" t="s">
         <v>155</v>
       </c>
-      <c r="F34" t="s">
-        <v>156</v>
-      </c>
-      <c r="G34" t="s">
-        <v>157</v>
-      </c>
       <c r="H34" s="2">
-        <v>45252</v>
+        <v>45175</v>
       </c>
       <c r="I34" s="3">
-        <v>1021</v>
+        <v>1100</v>
       </c>
       <c r="J34" t="s">
         <v>38</v>
       </c>
-      <c r="M34" s="3"/>
+      <c r="K34" t="s">
+        <v>156</v>
+      </c>
+      <c r="L34" s="2">
+        <v>45161</v>
+      </c>
+      <c r="M34" s="3">
+        <v>131</v>
+      </c>
+      <c r="S34" s="2">
+        <v>45563</v>
+      </c>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="4"/>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C35" s="2">
-        <v>45069</v>
+        <v>45056</v>
       </c>
       <c r="D35" t="s">
         <v>24</v>
       </c>
       <c r="E35" t="s">
+        <v>158</v>
+      </c>
+      <c r="F35" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" t="s">
         <v>159</v>
       </c>
-      <c r="F35" t="s">
-        <v>42</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="H35" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I35" s="3">
+        <v>875</v>
+      </c>
+      <c r="J35" t="s">
+        <v>38</v>
+      </c>
+      <c r="K35" t="s">
         <v>160</v>
       </c>
-      <c r="H35" s="2">
-        <v>45267</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1006</v>
-      </c>
-      <c r="J35" t="s">
-        <v>28</v>
-      </c>
-      <c r="M35" s="3"/>
+      <c r="L35" s="2">
+        <v>45400</v>
+      </c>
+      <c r="M35" s="3">
+        <v>344</v>
+      </c>
+      <c r="S35" s="2">
+        <v>45765</v>
+      </c>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="4"/>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B36" t="s">
         <v>161</v>
       </c>
       <c r="C36" s="2">
-        <v>45063</v>
+        <v>45056</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
         <v>162</v>
       </c>
       <c r="F36" t="s">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="G36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H36" s="2">
-        <v>45404</v>
+        <v>45252</v>
       </c>
       <c r="I36" s="3">
-        <v>869</v>
+        <v>1023</v>
       </c>
       <c r="J36" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="M36" s="3"/>
       <c r="T36" s="3"/>
@@ -3499,78 +3511,67 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C37" s="2">
-        <v>45063</v>
+        <v>45069</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F37" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G37" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="H37" s="2">
-        <v>45236</v>
+        <v>45267</v>
       </c>
       <c r="I37" s="3">
-        <v>1037</v>
+        <v>1008</v>
       </c>
       <c r="J37" t="s">
-        <v>38</v>
-      </c>
-      <c r="K37" t="s">
-        <v>166</v>
-      </c>
-      <c r="L37" s="2">
-        <v>45236</v>
-      </c>
-      <c r="M37" s="3">
-        <v>173</v>
-      </c>
-      <c r="S37" s="2">
-        <v>45603</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="4"/>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C38" s="2">
-        <v>45065</v>
+        <v>45063</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F38" t="s">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="G38" t="s">
         <v>170</v>
       </c>
       <c r="H38" s="2">
-        <v>45209</v>
+        <v>45404</v>
       </c>
       <c r="I38" s="3">
-        <v>1064</v>
+        <v>871</v>
       </c>
       <c r="J38" t="s">
         <v>28</v>
@@ -3582,49 +3583,46 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
         <v>171</v>
       </c>
       <c r="C39" s="2">
-        <v>45092</v>
+        <v>45063</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
         <v>172</v>
       </c>
       <c r="F39" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="G39" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H39" s="2">
-        <v>45573</v>
+        <v>45236</v>
       </c>
       <c r="I39" s="3">
-        <v>700</v>
+        <v>1039</v>
       </c>
       <c r="J39" t="s">
         <v>38</v>
       </c>
       <c r="K39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L39" s="2">
-        <v>45569</v>
+        <v>45236</v>
       </c>
       <c r="M39" s="3">
-        <v>477</v>
-      </c>
-      <c r="O39" t="s">
-        <v>59</v>
+        <v>173</v>
       </c>
       <c r="S39" s="2">
-        <v>45805</v>
+        <v>45603</v>
       </c>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
@@ -3632,31 +3630,31 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C40" s="2">
-        <v>45106</v>
+        <v>45065</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
       </c>
       <c r="E40" t="s">
+        <v>175</v>
+      </c>
+      <c r="F40" t="s">
         <v>176</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>177</v>
       </c>
-      <c r="G40" t="s">
-        <v>178</v>
-      </c>
       <c r="H40" s="2">
-        <v>45306</v>
+        <v>45209</v>
       </c>
       <c r="I40" s="3">
-        <v>967</v>
+        <v>1066</v>
       </c>
       <c r="J40" t="s">
         <v>28</v>
@@ -3668,31 +3666,31 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" s="2">
+        <v>45092</v>
+      </c>
+      <c r="D41" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" t="s">
         <v>179</v>
       </c>
-      <c r="C41" s="2">
-        <v>45128</v>
-      </c>
-      <c r="D41" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
+        <v>121</v>
+      </c>
+      <c r="G41" t="s">
         <v>180</v>
       </c>
-      <c r="F41" t="s">
-        <v>42</v>
-      </c>
-      <c r="G41" t="s">
-        <v>148</v>
-      </c>
       <c r="H41" s="2">
-        <v>45264</v>
+        <v>45573</v>
       </c>
       <c r="I41" s="3">
-        <v>1009</v>
+        <v>702</v>
       </c>
       <c r="J41" t="s">
         <v>38</v>
@@ -3701,13 +3699,16 @@
         <v>181</v>
       </c>
       <c r="L41" s="2">
-        <v>45229</v>
+        <v>45569</v>
       </c>
       <c r="M41" s="3">
-        <v>101</v>
+        <v>477</v>
+      </c>
+      <c r="O41" t="s">
+        <v>66</v>
       </c>
       <c r="S41" s="2">
-        <v>45591</v>
+        <v>45805</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -3715,13 +3716,13 @@
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
         <v>182</v>
       </c>
       <c r="C42" s="2">
-        <v>45307</v>
+        <v>45106</v>
       </c>
       <c r="D42" t="s">
         <v>24</v>
@@ -3730,16 +3731,16 @@
         <v>183</v>
       </c>
       <c r="F42" t="s">
-        <v>42</v>
+        <v>184</v>
       </c>
       <c r="G42" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H42" s="2">
-        <v>45426</v>
+        <v>45306</v>
       </c>
       <c r="I42" s="3">
-        <v>847</v>
+        <v>969</v>
       </c>
       <c r="J42" t="s">
         <v>28</v>
@@ -3751,163 +3752,162 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C43" s="2">
-        <v>45359</v>
+        <v>45128</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F43" t="s">
-        <v>177</v>
+        <v>49</v>
       </c>
       <c r="G43" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="H43" s="2">
-        <v>45359</v>
+        <v>45264</v>
       </c>
       <c r="I43" s="3">
-        <v>914</v>
+        <v>1011</v>
       </c>
       <c r="J43" t="s">
-        <v>28</v>
-      </c>
-      <c r="M43" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="K43" t="s">
+        <v>188</v>
+      </c>
+      <c r="L43" s="2">
+        <v>45229</v>
+      </c>
+      <c r="M43" s="3">
+        <v>101</v>
+      </c>
+      <c r="S43" s="2">
+        <v>45591</v>
+      </c>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="4"/>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C44" s="2">
-        <v>45408</v>
+        <v>45307</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F44" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G44" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H44" s="2">
-        <v>45595</v>
+        <v>45426</v>
       </c>
       <c r="I44" s="3">
-        <v>678</v>
+        <v>849</v>
       </c>
       <c r="J44" t="s">
-        <v>38</v>
-      </c>
-      <c r="K44" t="s">
-        <v>191</v>
-      </c>
-      <c r="L44" s="2">
-        <v>45624</v>
-      </c>
-      <c r="M44" s="3">
-        <v>216</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="4"/>
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
         <v>192</v>
       </c>
       <c r="C45" s="2">
-        <v>45394</v>
+        <v>45359</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
         <v>193</v>
       </c>
       <c r="F45" t="s">
-        <v>42</v>
+        <v>184</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="H45" s="2">
-        <v>45562</v>
+        <v>45359</v>
       </c>
       <c r="I45" s="3">
-        <v>711</v>
+        <v>916</v>
       </c>
       <c r="J45" t="s">
-        <v>38</v>
-      </c>
-      <c r="K45" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
       <c r="M45" s="3"/>
-      <c r="S45" s="2">
-        <v>45927</v>
-      </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
       <c r="V45" s="4"/>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
         <v>195</v>
       </c>
       <c r="C46" s="2">
-        <v>45456</v>
+        <v>45408</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E46" t="s">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="F46" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G46" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H46" s="2">
-        <v>45488</v>
+        <v>45595</v>
       </c>
       <c r="I46" s="3">
-        <v>785</v>
+        <v>680</v>
       </c>
       <c r="J46" t="s">
         <v>38</v>
       </c>
       <c r="K46" t="s">
-        <v>197</v>
-      </c>
-      <c r="M46" s="3"/>
-      <c r="S46" s="2">
-        <v>45832</v>
+        <v>198</v>
+      </c>
+      <c r="L46" s="2">
+        <v>45624</v>
+      </c>
+      <c r="M46" s="3">
+        <v>216</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
@@ -3915,31 +3915,31 @@
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C47" s="2">
-        <v>45395</v>
+        <v>45394</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E47" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G47" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="H47" s="2">
-        <v>45552</v>
+        <v>45562</v>
       </c>
       <c r="I47" s="3">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="J47" t="s">
         <v>38</v>
@@ -3947,48 +3947,41 @@
       <c r="K47" t="s">
         <v>201</v>
       </c>
-      <c r="L47" s="2">
-        <v>45548</v>
-      </c>
-      <c r="M47" s="3">
-        <v>153</v>
-      </c>
+      <c r="M47" s="3"/>
       <c r="S47" s="2">
-        <v>47378</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1105</v>
-      </c>
+        <v>45927</v>
+      </c>
+      <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
         <v>202</v>
       </c>
       <c r="C48" s="2">
-        <v>45395</v>
+        <v>45456</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
+        <v>134</v>
+      </c>
+      <c r="F48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" t="s">
         <v>203</v>
       </c>
-      <c r="F48" t="s">
-        <v>42</v>
-      </c>
-      <c r="G48" t="s">
-        <v>200</v>
-      </c>
       <c r="H48" s="2">
-        <v>45540</v>
+        <v>45488</v>
       </c>
       <c r="I48" s="3">
-        <v>733</v>
+        <v>787</v>
       </c>
       <c r="J48" t="s">
         <v>38</v>
@@ -3996,17 +3989,9 @@
       <c r="K48" t="s">
         <v>204</v>
       </c>
-      <c r="L48" s="2">
-        <v>45530</v>
-      </c>
-      <c r="M48" s="3">
-        <v>135</v>
-      </c>
-      <c r="N48" t="s">
-        <v>205</v>
-      </c>
+      <c r="M48" s="3"/>
       <c r="S48" s="2">
-        <v>45720</v>
+        <v>45832</v>
       </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
@@ -4014,31 +3999,31 @@
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C49" s="2">
         <v>45395</v>
       </c>
       <c r="D49" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E49" t="s">
+        <v>206</v>
+      </c>
+      <c r="F49" t="s">
+        <v>49</v>
+      </c>
+      <c r="G49" t="s">
         <v>207</v>
       </c>
-      <c r="F49" t="s">
-        <v>42</v>
-      </c>
-      <c r="G49" t="s">
-        <v>148</v>
-      </c>
       <c r="H49" s="2">
-        <v>45566</v>
+        <v>45552</v>
       </c>
       <c r="I49" s="3">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="J49" t="s">
         <v>38</v>
@@ -4047,59 +4032,65 @@
         <v>208</v>
       </c>
       <c r="L49" s="2">
-        <v>45517</v>
+        <v>45548</v>
       </c>
       <c r="M49" s="3">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="S49" s="2">
-        <v>47343</v>
+        <v>47378</v>
       </c>
       <c r="T49" s="3">
-        <v>1070</v>
+        <v>1103</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
         <v>209</v>
       </c>
       <c r="C50" s="2">
-        <v>45400</v>
+        <v>45395</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E50" t="s">
         <v>210</v>
       </c>
       <c r="F50" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G50" t="s">
+        <v>207</v>
+      </c>
+      <c r="H50" s="2">
+        <v>45540</v>
+      </c>
+      <c r="I50" s="3">
+        <v>735</v>
+      </c>
+      <c r="J50" t="s">
+        <v>38</v>
+      </c>
+      <c r="K50" t="s">
         <v>211</v>
       </c>
-      <c r="H50" s="2">
-        <v>45790</v>
-      </c>
-      <c r="I50" s="3">
-        <v>483</v>
-      </c>
-      <c r="J50" t="s">
-        <v>28</v>
-      </c>
-      <c r="K50" t="s">
+      <c r="L50" s="2">
+        <v>45530</v>
+      </c>
+      <c r="M50" s="3">
+        <v>135</v>
+      </c>
+      <c r="N50" t="s">
         <v>212</v>
       </c>
-      <c r="L50" s="2">
-        <v>45580</v>
-      </c>
-      <c r="M50" s="3">
-        <v>180</v>
+      <c r="S50" s="2">
+        <v>45720</v>
       </c>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
@@ -4107,88 +4098,109 @@
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
         <v>213</v>
       </c>
       <c r="C51" s="2">
-        <v>45553</v>
+        <v>45395</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E51" t="s">
         <v>214</v>
       </c>
       <c r="F51" t="s">
+        <v>49</v>
+      </c>
+      <c r="G51" t="s">
+        <v>155</v>
+      </c>
+      <c r="H51" s="2">
+        <v>45566</v>
+      </c>
+      <c r="I51" s="3">
+        <v>709</v>
+      </c>
+      <c r="J51" t="s">
+        <v>38</v>
+      </c>
+      <c r="K51" t="s">
         <v>215</v>
       </c>
-      <c r="G51" t="s">
-        <v>216</v>
-      </c>
-      <c r="H51" s="2">
-        <v>45567</v>
-      </c>
-      <c r="I51" s="3">
-        <v>706</v>
-      </c>
-      <c r="J51" t="s">
-        <v>28</v>
-      </c>
-      <c r="M51" s="3"/>
-      <c r="T51" s="3"/>
+      <c r="L51" s="2">
+        <v>45517</v>
+      </c>
+      <c r="M51" s="3">
+        <v>122</v>
+      </c>
+      <c r="S51" s="2">
+        <v>47343</v>
+      </c>
+      <c r="T51" s="3">
+        <v>1068</v>
+      </c>
       <c r="U51" s="3"/>
       <c r="V51" s="4"/>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
+        <v>216</v>
+      </c>
+      <c r="C52" s="2">
+        <v>45400</v>
+      </c>
+      <c r="D52" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" t="s">
         <v>217</v>
       </c>
-      <c r="C52" s="2">
-        <v>45516</v>
-      </c>
-      <c r="D52" t="s">
-        <v>44</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" t="s">
         <v>218</v>
       </c>
-      <c r="F52" t="s">
-        <v>42</v>
-      </c>
-      <c r="G52" t="s">
-        <v>219</v>
-      </c>
       <c r="H52" s="2">
-        <v>45590</v>
+        <v>45790</v>
       </c>
       <c r="I52" s="3">
-        <v>683</v>
+        <v>485</v>
       </c>
       <c r="J52" t="s">
         <v>28</v>
       </c>
-      <c r="M52" s="3"/>
+      <c r="K52" t="s">
+        <v>219</v>
+      </c>
+      <c r="L52" s="2">
+        <v>45580</v>
+      </c>
+      <c r="M52" s="3">
+        <v>180</v>
+      </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="4"/>
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
         <v>220</v>
       </c>
       <c r="C53" s="2">
-        <v>45701</v>
+        <v>45553</v>
       </c>
       <c r="D53" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
         <v>221</v>
@@ -4200,10 +4212,10 @@
         <v>223</v>
       </c>
       <c r="H53" s="2">
-        <v>45758</v>
+        <v>45567</v>
       </c>
       <c r="I53" s="3">
-        <v>515</v>
+        <v>708</v>
       </c>
       <c r="J53" t="s">
         <v>28</v>
@@ -4215,81 +4227,70 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" t="s">
         <v>224</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" s="2">
+        <v>45516</v>
+      </c>
+      <c r="D54" t="s">
+        <v>51</v>
+      </c>
+      <c r="E54" t="s">
         <v>225</v>
       </c>
-      <c r="C54" s="2">
-        <v>45308</v>
-      </c>
-      <c r="D54" t="s">
-        <v>35</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
+        <v>49</v>
+      </c>
+      <c r="G54" t="s">
         <v>226</v>
       </c>
-      <c r="F54" t="s">
-        <v>224</v>
-      </c>
-      <c r="G54" t="s">
-        <v>227</v>
-      </c>
       <c r="H54" s="2">
-        <v>45454</v>
+        <v>45590</v>
       </c>
       <c r="I54" s="3">
-        <v>819</v>
+        <v>685</v>
       </c>
       <c r="J54" t="s">
-        <v>52</v>
-      </c>
-      <c r="K54" t="s">
-        <v>228</v>
-      </c>
-      <c r="L54" s="2">
-        <v>45408</v>
-      </c>
-      <c r="M54" s="3">
-        <v>100</v>
-      </c>
-      <c r="S54" s="2">
-        <v>46138</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="4"/>
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
+        <v>227</v>
+      </c>
+      <c r="C55" s="2">
+        <v>45701</v>
+      </c>
+      <c r="D55" t="s">
+        <v>51</v>
+      </c>
+      <c r="E55" t="s">
+        <v>228</v>
+      </c>
+      <c r="F55" t="s">
         <v>229</v>
       </c>
-      <c r="C55" s="2">
-        <v>45051</v>
-      </c>
-      <c r="D55" t="s">
-        <v>44</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>230</v>
       </c>
-      <c r="F55" t="s">
-        <v>231</v>
-      </c>
-      <c r="G55" t="s">
-        <v>232</v>
-      </c>
       <c r="H55" s="2">
-        <v>45573</v>
+        <v>45758</v>
       </c>
       <c r="I55" s="3">
-        <v>700</v>
+        <v>517</v>
       </c>
       <c r="J55" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M55" s="3"/>
       <c r="T55" s="3"/>
@@ -4298,36 +4299,47 @@
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>26</v>
+        <v>231</v>
       </c>
       <c r="B56" t="s">
+        <v>232</v>
+      </c>
+      <c r="C56" s="2">
+        <v>45308</v>
+      </c>
+      <c r="D56" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" t="s">
         <v>233</v>
       </c>
-      <c r="C56" s="2">
-        <v>45016</v>
-      </c>
-      <c r="D56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
+        <v>231</v>
+      </c>
+      <c r="G56" t="s">
         <v>234</v>
       </c>
-      <c r="F56" t="s">
+      <c r="H56" s="2">
+        <v>45454</v>
+      </c>
+      <c r="I56" s="3">
+        <v>821</v>
+      </c>
+      <c r="J56" t="s">
+        <v>38</v>
+      </c>
+      <c r="K56" t="s">
         <v>235</v>
       </c>
-      <c r="G56" t="s">
-        <v>236</v>
-      </c>
-      <c r="H56" s="2">
-        <v>45219</v>
-      </c>
-      <c r="I56" s="3">
-        <v>1054</v>
-      </c>
-      <c r="J56" t="s">
-        <v>28</v>
-      </c>
-      <c r="M56" s="3"/>
+      <c r="L56" s="2">
+        <v>45408</v>
+      </c>
+      <c r="M56" s="3">
+        <v>100</v>
+      </c>
+      <c r="S56" s="2">
+        <v>46138</v>
+      </c>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="4"/>
@@ -4337,28 +4349,28 @@
         <v>26</v>
       </c>
       <c r="B57" t="s">
+        <v>236</v>
+      </c>
+      <c r="C57" s="2">
+        <v>45051</v>
+      </c>
+      <c r="D57" t="s">
+        <v>51</v>
+      </c>
+      <c r="E57" t="s">
         <v>237</v>
       </c>
-      <c r="C57" s="2">
-        <v>45016</v>
-      </c>
-      <c r="D57" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>238</v>
-      </c>
-      <c r="F57" t="s">
-        <v>133</v>
       </c>
       <c r="G57" t="s">
         <v>239</v>
       </c>
       <c r="H57" s="2">
-        <v>45315</v>
+        <v>45573</v>
       </c>
       <c r="I57" s="3">
-        <v>958</v>
+        <v>702</v>
       </c>
       <c r="J57" t="s">
         <v>38</v>
@@ -4376,25 +4388,25 @@
         <v>240</v>
       </c>
       <c r="C58" s="2">
-        <v>45251</v>
+        <v>45016</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
         <v>241</v>
       </c>
       <c r="F58" t="s">
-        <v>26</v>
+        <v>242</v>
       </c>
       <c r="G58" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H58" s="2">
-        <v>45299</v>
+        <v>45219</v>
       </c>
       <c r="I58" s="3">
-        <v>974</v>
+        <v>1056</v>
       </c>
       <c r="J58" t="s">
         <v>28</v>
@@ -4409,28 +4421,28 @@
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C59" s="2">
-        <v>45314</v>
+        <v>45016</v>
       </c>
       <c r="D59" t="s">
-        <v>244</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
         <v>245</v>
       </c>
       <c r="F59" t="s">
+        <v>140</v>
+      </c>
+      <c r="G59" t="s">
         <v>246</v>
       </c>
-      <c r="G59" t="s">
-        <v>247</v>
-      </c>
       <c r="H59" s="2">
-        <v>45462</v>
+        <v>45315</v>
       </c>
       <c r="I59" s="3">
-        <v>811</v>
+        <v>960</v>
       </c>
       <c r="J59" t="s">
         <v>38</v>
@@ -4445,47 +4457,34 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
+        <v>247</v>
+      </c>
+      <c r="C60" s="2">
+        <v>45251</v>
+      </c>
+      <c r="D60" t="s">
+        <v>51</v>
+      </c>
+      <c r="E60" t="s">
         <v>248</v>
       </c>
-      <c r="C60" s="2">
-        <v>45216</v>
-      </c>
-      <c r="D60" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" t="s">
         <v>249</v>
       </c>
-      <c r="F60" t="s">
-        <v>42</v>
-      </c>
-      <c r="G60" t="s">
-        <v>250</v>
-      </c>
       <c r="H60" s="2">
-        <v>45538</v>
+        <v>45299</v>
       </c>
       <c r="I60" s="3">
-        <v>735</v>
+        <v>976</v>
       </c>
       <c r="J60" t="s">
-        <v>52</v>
-      </c>
-      <c r="K60" t="s">
-        <v>251</v>
-      </c>
-      <c r="L60" s="2">
-        <v>45475</v>
-      </c>
-      <c r="M60" s="3">
-        <v>259</v>
-      </c>
-      <c r="S60" s="2">
-        <v>47301</v>
-      </c>
-      <c r="T60" s="3">
-        <v>1028</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M60" s="3"/>
+      <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
     </row>
@@ -4494,31 +4493,31 @@
         <v>26</v>
       </c>
       <c r="B61" t="s">
+        <v>250</v>
+      </c>
+      <c r="C61" s="2">
+        <v>45314</v>
+      </c>
+      <c r="D61" t="s">
+        <v>251</v>
+      </c>
+      <c r="E61" t="s">
         <v>252</v>
       </c>
-      <c r="C61" s="2">
-        <v>45742</v>
-      </c>
-      <c r="D61" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>253</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>254</v>
       </c>
-      <c r="G61" t="s">
-        <v>255</v>
-      </c>
       <c r="H61" s="2">
-        <v>45847</v>
+        <v>45462</v>
       </c>
       <c r="I61" s="3">
-        <v>426</v>
+        <v>813</v>
       </c>
       <c r="J61" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="M61" s="3"/>
       <c r="T61" s="3"/>
@@ -4530,34 +4529,47 @@
         <v>26</v>
       </c>
       <c r="B62" t="s">
+        <v>255</v>
+      </c>
+      <c r="C62" s="2">
+        <v>45216</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" t="s">
         <v>256</v>
       </c>
-      <c r="C62" s="2">
-        <v>45734</v>
-      </c>
-      <c r="D62" t="s">
-        <v>44</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
+        <v>49</v>
+      </c>
+      <c r="G62" t="s">
         <v>257</v>
       </c>
-      <c r="F62" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" t="s">
+      <c r="H62" s="2">
+        <v>45538</v>
+      </c>
+      <c r="I62" s="3">
+        <v>737</v>
+      </c>
+      <c r="J62" t="s">
+        <v>59</v>
+      </c>
+      <c r="K62" t="s">
         <v>258</v>
       </c>
-      <c r="H62" s="2">
-        <v>45839</v>
-      </c>
-      <c r="I62" s="3">
-        <v>434</v>
-      </c>
-      <c r="J62" t="s">
-        <v>28</v>
-      </c>
-      <c r="M62" s="3"/>
-      <c r="T62" s="3"/>
+      <c r="L62" s="2">
+        <v>45475</v>
+      </c>
+      <c r="M62" s="3">
+        <v>259</v>
+      </c>
+      <c r="S62" s="2">
+        <v>47301</v>
+      </c>
+      <c r="T62" s="3">
+        <v>1026</v>
+      </c>
       <c r="U62" s="3"/>
       <c r="V62" s="4"/>
     </row>
@@ -4569,7 +4581,7 @@
         <v>259</v>
       </c>
       <c r="C63" s="2">
-        <v>46162</v>
+        <v>45742</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
@@ -4578,16 +4590,16 @@
         <v>260</v>
       </c>
       <c r="F63" t="s">
-        <v>26</v>
+        <v>261</v>
       </c>
       <c r="G63" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H63" s="2">
-        <v>46246</v>
+        <v>45847</v>
       </c>
       <c r="I63" s="3">
-        <v>27</v>
+        <v>428</v>
       </c>
       <c r="J63" t="s">
         <v>28</v>
@@ -4602,31 +4614,31 @@
         <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C64" s="2">
-        <v>46245</v>
+        <v>45734</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E64" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F64" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="G64" t="s">
         <v>265</v>
       </c>
       <c r="H64" s="2">
-        <v>46259</v>
+        <v>45839</v>
       </c>
       <c r="I64" s="3">
-        <v>14</v>
+        <v>436</v>
       </c>
       <c r="J64" t="s">
-        <v>266</v>
+        <v>28</v>
       </c>
       <c r="M64" s="3"/>
       <c r="T64" s="3"/>
@@ -4638,31 +4650,31 @@
         <v>26</v>
       </c>
       <c r="B65" t="s">
+        <v>266</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46162</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" t="s">
         <v>267</v>
       </c>
-      <c r="C65" s="2">
-        <v>46126</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" t="s">
         <v>268</v>
       </c>
-      <c r="E65" t="s">
-        <v>269</v>
-      </c>
-      <c r="F65" t="s">
-        <v>66</v>
-      </c>
-      <c r="G65" t="s">
-        <v>270</v>
-      </c>
       <c r="H65" s="2">
-        <v>46182</v>
+        <v>46246</v>
       </c>
       <c r="I65" s="3">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="J65" t="s">
-        <v>271</v>
+        <v>28</v>
       </c>
       <c r="M65" s="3"/>
       <c r="T65" s="3"/>
@@ -4674,121 +4686,117 @@
         <v>26</v>
       </c>
       <c r="B66" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C66" s="2">
-        <v>46211</v>
+        <v>46245</v>
       </c>
       <c r="D66" t="s">
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F66" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G66" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H66" s="2">
-        <v>46267</v>
+        <v>46259</v>
       </c>
       <c r="I66" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J66" t="s">
-        <v>266</v>
+        <v>45</v>
       </c>
       <c r="M66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
-      <c r="V66" s="4">
-        <v>0</v>
-      </c>
+      <c r="V66" s="4"/>
     </row>
     <row r="67" spans="1:22">
       <c r="A67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B67" t="s">
+        <v>273</v>
+      </c>
+      <c r="C67" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D67" t="s">
+        <v>274</v>
+      </c>
+      <c r="E67" t="s">
         <v>275</v>
       </c>
-      <c r="B67" t="s">
+      <c r="F67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G67" t="s">
+        <v>272</v>
+      </c>
+      <c r="H67" s="2">
+        <v>46182</v>
+      </c>
+      <c r="I67" s="3">
+        <v>93</v>
+      </c>
+      <c r="J67" t="s">
         <v>276</v>
-      </c>
-      <c r="C67" s="2">
-        <v>46136</v>
-      </c>
-      <c r="D67" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" t="s">
-        <v>277</v>
-      </c>
-      <c r="F67" t="s">
-        <v>169</v>
-      </c>
-      <c r="G67" t="s">
-        <v>278</v>
-      </c>
-      <c r="H67" s="2">
-        <v>46156</v>
-      </c>
-      <c r="I67" s="3">
-        <v>117</v>
-      </c>
-      <c r="J67" t="s">
-        <v>38</v>
       </c>
       <c r="M67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-      <c r="V67" s="4">
-        <v>400</v>
-      </c>
+      <c r="V67" s="4"/>
     </row>
     <row r="68" spans="1:22">
       <c r="A68" t="s">
-        <v>275</v>
+        <v>26</v>
       </c>
       <c r="B68" t="s">
+        <v>277</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46211</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" t="s">
+        <v>278</v>
+      </c>
+      <c r="F68" t="s">
+        <v>135</v>
+      </c>
+      <c r="G68" t="s">
         <v>279</v>
       </c>
-      <c r="C68" s="2">
-        <v>46135</v>
-      </c>
-      <c r="D68" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" t="s">
-        <v>280</v>
-      </c>
-      <c r="F68" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" t="s">
-        <v>281</v>
-      </c>
       <c r="H68" s="2">
-        <v>46155</v>
+        <v>46267</v>
       </c>
       <c r="I68" s="3">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="J68" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M68" s="3"/>
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="4">
-        <v>504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:22">
       <c r="A69" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C69" s="2">
         <v>46136</v>
@@ -4797,19 +4805,19 @@
         <v>35</v>
       </c>
       <c r="E69" t="s">
+        <v>282</v>
+      </c>
+      <c r="F69" t="s">
+        <v>176</v>
+      </c>
+      <c r="G69" t="s">
         <v>283</v>
       </c>
-      <c r="F69" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" t="s">
-        <v>281</v>
-      </c>
       <c r="H69" s="2">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="I69" s="3">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J69" t="s">
         <v>38</v>
@@ -4818,21 +4826,21 @@
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
       <c r="V69" s="4">
-        <v>856</v>
+        <v>400</v>
       </c>
     </row>
     <row r="70" spans="1:22">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="B70" t="s">
         <v>284</v>
       </c>
       <c r="C70" s="2">
-        <v>45804</v>
+        <v>46135</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E70" t="s">
         <v>285</v>
@@ -4844,408 +4852,391 @@
         <v>286</v>
       </c>
       <c r="H70" s="2">
-        <v>45943</v>
+        <v>46155</v>
       </c>
       <c r="I70" s="3">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="J70" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="M70" s="3"/>
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
       <c r="V70" s="4">
-        <v>9808.2000000000007</v>
+        <v>504</v>
       </c>
     </row>
     <row r="71" spans="1:22">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="B71" t="s">
         <v>287</v>
       </c>
       <c r="C71" s="2">
-        <v>45513</v>
+        <v>46136</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E71" t="s">
         <v>288</v>
       </c>
       <c r="F71" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H71" s="2">
-        <v>45715</v>
+        <v>46157</v>
       </c>
       <c r="I71" s="3">
-        <v>558</v>
+        <v>118</v>
       </c>
       <c r="J71" t="s">
-        <v>52</v>
-      </c>
-      <c r="K71" t="s">
-        <v>290</v>
-      </c>
-      <c r="L71" s="2">
-        <v>45712</v>
-      </c>
-      <c r="M71" s="3">
-        <v>199</v>
-      </c>
-      <c r="S71" s="2">
-        <v>46077</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M71" s="3"/>
       <c r="T71" s="3"/>
       <c r="U71" s="3"/>
       <c r="V71" s="4">
-        <v>18900</v>
+        <v>856</v>
       </c>
     </row>
     <row r="72" spans="1:22">
       <c r="A72" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B72" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C72" s="2">
-        <v>45659</v>
+        <v>45804</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F72" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H72" s="2">
-        <v>45817</v>
+        <v>45943</v>
       </c>
       <c r="I72" s="3">
-        <v>456</v>
+        <v>332</v>
       </c>
       <c r="J72" t="s">
-        <v>52</v>
-      </c>
-      <c r="K72" t="s">
-        <v>294</v>
-      </c>
-      <c r="L72" s="2">
-        <v>45812</v>
-      </c>
-      <c r="M72" s="3">
-        <v>153</v>
-      </c>
-      <c r="S72" s="2">
-        <v>46909</v>
-      </c>
-      <c r="T72" s="3">
-        <v>636</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M72" s="3"/>
+      <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="4">
-        <v>23850</v>
+        <v>9808.2000000000007</v>
       </c>
     </row>
     <row r="73" spans="1:22">
       <c r="A73" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B73" t="s">
+        <v>292</v>
+      </c>
+      <c r="C73" s="2">
+        <v>45513</v>
+      </c>
+      <c r="D73" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73" t="s">
+        <v>293</v>
+      </c>
+      <c r="F73" t="s">
+        <v>135</v>
+      </c>
+      <c r="G73" t="s">
+        <v>294</v>
+      </c>
+      <c r="H73" s="2">
+        <v>45715</v>
+      </c>
+      <c r="I73" s="3">
+        <v>560</v>
+      </c>
+      <c r="J73" t="s">
+        <v>38</v>
+      </c>
+      <c r="K73" t="s">
         <v>295</v>
       </c>
-      <c r="C73" s="2">
-        <v>45492</v>
-      </c>
-      <c r="D73" t="s">
-        <v>44</v>
-      </c>
-      <c r="E73" t="s">
-        <v>296</v>
-      </c>
-      <c r="F73" t="s">
-        <v>42</v>
-      </c>
-      <c r="G73" t="s">
-        <v>51</v>
-      </c>
-      <c r="H73" s="2">
-        <v>45911</v>
-      </c>
-      <c r="I73" s="3">
-        <v>362</v>
-      </c>
-      <c r="J73" t="s">
-        <v>52</v>
-      </c>
-      <c r="K73" t="s">
-        <v>297</v>
-      </c>
       <c r="L73" s="2">
-        <v>45546</v>
+        <v>45712</v>
       </c>
       <c r="M73" s="3">
-        <v>54</v>
-      </c>
-      <c r="O73" t="s">
-        <v>59</v>
-      </c>
-      <c r="P73" s="2">
-        <v>45966</v>
+        <v>199</v>
+      </c>
+      <c r="S73" s="2">
+        <v>46077</v>
       </c>
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
       <c r="V73" s="4">
-        <v>25173.75</v>
+        <v>18900</v>
       </c>
     </row>
     <row r="74" spans="1:22">
       <c r="A74" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B74" t="s">
+        <v>296</v>
+      </c>
+      <c r="C74" s="2">
+        <v>45659</v>
+      </c>
+      <c r="D74" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" t="s">
+        <v>297</v>
+      </c>
+      <c r="F74" t="s">
+        <v>73</v>
+      </c>
+      <c r="G74" t="s">
         <v>298</v>
       </c>
-      <c r="C74" s="2">
-        <v>45786</v>
-      </c>
-      <c r="D74" t="s">
-        <v>44</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="H74" s="2">
+        <v>45817</v>
+      </c>
+      <c r="I74" s="3">
+        <v>458</v>
+      </c>
+      <c r="J74" t="s">
+        <v>59</v>
+      </c>
+      <c r="K74" t="s">
         <v>299</v>
       </c>
-      <c r="F74" t="s">
-        <v>141</v>
-      </c>
-      <c r="G74" t="s">
-        <v>300</v>
-      </c>
-      <c r="H74" s="2">
-        <v>45895</v>
-      </c>
-      <c r="I74" s="3">
-        <v>378</v>
-      </c>
-      <c r="J74" t="s">
-        <v>38</v>
-      </c>
-      <c r="M74" s="3"/>
-      <c r="T74" s="3"/>
+      <c r="L74" s="2">
+        <v>45812</v>
+      </c>
+      <c r="M74" s="3">
+        <v>153</v>
+      </c>
+      <c r="S74" s="2">
+        <v>46909</v>
+      </c>
+      <c r="T74" s="3">
+        <v>634</v>
+      </c>
       <c r="U74" s="3"/>
       <c r="V74" s="4">
-        <v>31300</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="75" spans="1:22">
       <c r="A75" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B75" t="s">
+        <v>300</v>
+      </c>
+      <c r="C75" s="2">
+        <v>45492</v>
+      </c>
+      <c r="D75" t="s">
+        <v>51</v>
+      </c>
+      <c r="E75" t="s">
         <v>301</v>
       </c>
-      <c r="C75" s="2">
-        <v>45946</v>
-      </c>
-      <c r="D75" t="s">
-        <v>24</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
+        <v>49</v>
+      </c>
+      <c r="G75" t="s">
+        <v>58</v>
+      </c>
+      <c r="H75" s="2">
+        <v>45911</v>
+      </c>
+      <c r="I75" s="3">
+        <v>364</v>
+      </c>
+      <c r="J75" t="s">
+        <v>38</v>
+      </c>
+      <c r="K75" t="s">
         <v>302</v>
       </c>
-      <c r="F75" t="s">
-        <v>274</v>
-      </c>
-      <c r="G75" t="s">
-        <v>303</v>
-      </c>
-      <c r="H75" s="2">
-        <v>46196</v>
-      </c>
-      <c r="I75" s="3">
-        <v>77</v>
-      </c>
-      <c r="J75" t="s">
-        <v>28</v>
-      </c>
-      <c r="M75" s="3"/>
+      <c r="L75" s="2">
+        <v>45546</v>
+      </c>
+      <c r="M75" s="3">
+        <v>54</v>
+      </c>
+      <c r="O75" t="s">
+        <v>66</v>
+      </c>
+      <c r="P75" s="2">
+        <v>45966</v>
+      </c>
       <c r="T75" s="3"/>
       <c r="U75" s="3"/>
       <c r="V75" s="4">
-        <v>32983.599999999999</v>
+        <v>25173.75</v>
       </c>
     </row>
     <row r="76" spans="1:22">
       <c r="A76" t="s">
+        <v>26</v>
+      </c>
+      <c r="B76" t="s">
+        <v>303</v>
+      </c>
+      <c r="C76" s="2">
+        <v>45786</v>
+      </c>
+      <c r="D76" t="s">
+        <v>51</v>
+      </c>
+      <c r="E76" t="s">
         <v>304</v>
       </c>
-      <c r="B76" t="s">
+      <c r="F76" t="s">
+        <v>148</v>
+      </c>
+      <c r="G76" t="s">
         <v>305</v>
       </c>
-      <c r="C76" s="2">
-        <v>45665</v>
-      </c>
-      <c r="D76" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" t="s">
-        <v>306</v>
-      </c>
-      <c r="F76" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" t="s">
-        <v>307</v>
-      </c>
       <c r="H76" s="2">
-        <v>46198</v>
+        <v>45895</v>
       </c>
       <c r="I76" s="3">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="J76" t="s">
         <v>38</v>
       </c>
-      <c r="K76" t="s">
-        <v>308</v>
-      </c>
-      <c r="L76" s="2">
-        <v>46071</v>
-      </c>
-      <c r="M76" s="3">
-        <v>406</v>
-      </c>
-      <c r="O76" t="s">
-        <v>309</v>
-      </c>
-      <c r="P76" s="2">
-        <v>46294</v>
-      </c>
-      <c r="S76" s="2">
-        <v>46202</v>
-      </c>
+      <c r="M76" s="3"/>
       <c r="T76" s="3"/>
-      <c r="U76" s="3">
-        <v>21</v>
-      </c>
+      <c r="U76" s="3"/>
       <c r="V76" s="4">
-        <v>51071</v>
+        <v>31300</v>
       </c>
     </row>
     <row r="77" spans="1:22">
       <c r="A77" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B77" t="s">
-        <v>60</v>
+        <v>306</v>
       </c>
       <c r="C77" s="2">
-        <v>43902</v>
+        <v>45946</v>
       </c>
       <c r="D77" t="s">
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F77" t="s">
-        <v>42</v>
+        <v>308</v>
       </c>
       <c r="G77" t="s">
-        <v>148</v>
+        <v>309</v>
       </c>
       <c r="H77" s="2">
-        <v>45790</v>
+        <v>46196</v>
       </c>
       <c r="I77" s="3">
-        <v>483</v>
+        <v>79</v>
       </c>
       <c r="J77" t="s">
-        <v>52</v>
-      </c>
-      <c r="K77" t="s">
-        <v>311</v>
-      </c>
-      <c r="L77" s="2">
-        <v>43964</v>
-      </c>
-      <c r="M77" s="3">
-        <v>62</v>
-      </c>
-      <c r="O77" t="s">
-        <v>69</v>
-      </c>
-      <c r="P77" s="2">
-        <v>46160</v>
-      </c>
-      <c r="S77" s="2">
-        <v>44917</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M77" s="3"/>
       <c r="T77" s="3"/>
       <c r="U77" s="3"/>
       <c r="V77" s="4">
-        <v>61200</v>
+        <v>32983.599999999999</v>
       </c>
     </row>
     <row r="78" spans="1:22">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>310</v>
       </c>
       <c r="B78" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C78" s="2">
-        <v>46210</v>
+        <v>45665</v>
       </c>
       <c r="D78" t="s">
         <v>35</v>
       </c>
       <c r="E78" t="s">
+        <v>312</v>
+      </c>
+      <c r="F78" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" t="s">
         <v>313</v>
       </c>
-      <c r="F78" t="s">
-        <v>177</v>
-      </c>
-      <c r="G78" t="s">
+      <c r="H78" s="2">
+        <v>46198</v>
+      </c>
+      <c r="I78" s="3">
+        <v>77</v>
+      </c>
+      <c r="J78" t="s">
+        <v>38</v>
+      </c>
+      <c r="K78" t="s">
         <v>314</v>
       </c>
-      <c r="H78" s="2">
-        <v>46259</v>
-      </c>
-      <c r="I78" s="3">
-        <v>14</v>
-      </c>
-      <c r="J78" t="s">
-        <v>266</v>
-      </c>
-      <c r="M78" s="3"/>
+      <c r="L78" s="2">
+        <v>46071</v>
+      </c>
+      <c r="M78" s="3">
+        <v>406</v>
+      </c>
+      <c r="O78" t="s">
+        <v>315</v>
+      </c>
+      <c r="P78" s="2">
+        <v>46294</v>
+      </c>
+      <c r="S78" s="2">
+        <v>46202</v>
+      </c>
       <c r="T78" s="3"/>
-      <c r="U78" s="3"/>
+      <c r="U78" s="3">
+        <v>19</v>
+      </c>
       <c r="V78" s="4">
-        <v>67057.570000000007</v>
+        <v>51071</v>
       </c>
     </row>
     <row r="79" spans="1:22">
       <c r="A79" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B79" t="s">
-        <v>315</v>
+        <v>67</v>
       </c>
       <c r="C79" s="2">
-        <v>45915</v>
+        <v>43902</v>
       </c>
       <c r="D79" t="s">
         <v>24</v>
@@ -5254,101 +5245,88 @@
         <v>316</v>
       </c>
       <c r="F79" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="G79" t="s">
-        <v>317</v>
+        <v>155</v>
       </c>
       <c r="H79" s="2">
-        <v>46094</v>
+        <v>45790</v>
       </c>
       <c r="I79" s="3">
-        <v>179</v>
+        <v>485</v>
       </c>
       <c r="J79" t="s">
         <v>38</v>
       </c>
       <c r="K79" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L79" s="2">
-        <v>46086</v>
+        <v>43964</v>
       </c>
       <c r="M79" s="3">
-        <v>171</v>
+        <v>62</v>
+      </c>
+      <c r="O79" t="s">
+        <v>76</v>
+      </c>
+      <c r="P79" s="2">
+        <v>46160</v>
       </c>
       <c r="S79" s="2">
-        <v>47181</v>
-      </c>
-      <c r="T79" s="3">
-        <v>908</v>
-      </c>
+        <v>44917</v>
+      </c>
+      <c r="T79" s="3"/>
       <c r="U79" s="3"/>
       <c r="V79" s="4">
-        <v>71265.600000000006</v>
+        <v>61200</v>
       </c>
     </row>
     <row r="80" spans="1:22">
       <c r="A80" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B80" t="s">
+        <v>318</v>
+      </c>
+      <c r="C80" s="2">
+        <v>46210</v>
+      </c>
+      <c r="D80" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" t="s">
         <v>319</v>
       </c>
-      <c r="C80" s="2">
-        <v>45950</v>
-      </c>
-      <c r="D80" t="s">
-        <v>44</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
+        <v>184</v>
+      </c>
+      <c r="G80" t="s">
         <v>320</v>
       </c>
-      <c r="F80" t="s">
-        <v>42</v>
-      </c>
-      <c r="G80" t="s">
-        <v>321</v>
-      </c>
       <c r="H80" s="2">
-        <v>45975</v>
+        <v>46259</v>
       </c>
       <c r="I80" s="3">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="J80" t="s">
-        <v>38</v>
-      </c>
-      <c r="K80" t="s">
-        <v>322</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45978</v>
-      </c>
-      <c r="M80" s="3">
-        <v>28</v>
-      </c>
-      <c r="O80" t="s">
-        <v>59</v>
-      </c>
-      <c r="P80" s="2">
-        <v>46220</v>
-      </c>
-      <c r="S80" s="2">
-        <v>46220</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="M80" s="3"/>
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
       <c r="V80" s="4">
-        <v>71722</v>
+        <v>67057.570000000007</v>
       </c>
     </row>
     <row r="81" spans="1:22">
       <c r="A81" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B81" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C81" s="2">
         <v>45915</v>
@@ -5357,25 +5335,25 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
+        <v>322</v>
+      </c>
+      <c r="F81" t="s">
+        <v>148</v>
+      </c>
+      <c r="G81" t="s">
         <v>323</v>
       </c>
-      <c r="F81" t="s">
+      <c r="H81" s="2">
+        <v>46094</v>
+      </c>
+      <c r="I81" s="3">
+        <v>181</v>
+      </c>
+      <c r="J81" t="s">
+        <v>38</v>
+      </c>
+      <c r="K81" t="s">
         <v>324</v>
-      </c>
-      <c r="G81" t="s">
-        <v>325</v>
-      </c>
-      <c r="H81" s="2">
-        <v>46241</v>
-      </c>
-      <c r="I81" s="3">
-        <v>32</v>
-      </c>
-      <c r="J81" t="s">
-        <v>271</v>
-      </c>
-      <c r="K81" t="s">
-        <v>326</v>
       </c>
       <c r="L81" s="2">
         <v>46086</v>
@@ -5387,40 +5365,40 @@
         <v>47181</v>
       </c>
       <c r="T81" s="3">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
-        <v>73620</v>
+        <v>71265.600000000006</v>
       </c>
     </row>
     <row r="82" spans="1:22">
       <c r="A82" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B82" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C82" s="2">
-        <v>45915</v>
+        <v>45950</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E82" t="s">
+        <v>326</v>
+      </c>
+      <c r="F82" t="s">
+        <v>49</v>
+      </c>
+      <c r="G82" t="s">
         <v>327</v>
       </c>
-      <c r="F82" t="s">
-        <v>141</v>
-      </c>
-      <c r="G82" t="s">
-        <v>317</v>
-      </c>
       <c r="H82" s="2">
-        <v>46094</v>
+        <v>45975</v>
       </c>
       <c r="I82" s="3">
-        <v>179</v>
+        <v>300</v>
       </c>
       <c r="J82" t="s">
         <v>38</v>
@@ -5429,352 +5407,358 @@
         <v>328</v>
       </c>
       <c r="L82" s="2">
-        <v>46086</v>
+        <v>45978</v>
       </c>
       <c r="M82" s="3">
-        <v>171</v>
+        <v>28</v>
+      </c>
+      <c r="O82" t="s">
+        <v>66</v>
+      </c>
+      <c r="P82" s="2">
+        <v>46220</v>
       </c>
       <c r="S82" s="2">
-        <v>47181</v>
-      </c>
-      <c r="T82" s="3">
-        <v>908</v>
-      </c>
+        <v>46220</v>
+      </c>
+      <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="4">
-        <v>104220</v>
+        <v>71722</v>
       </c>
     </row>
     <row r="83" spans="1:22">
       <c r="A83" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B83" t="s">
-        <v>60</v>
+        <v>321</v>
       </c>
       <c r="C83" s="2">
-        <v>43902</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="s">
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>61</v>
+        <v>329</v>
       </c>
       <c r="F83" t="s">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="G83" t="s">
-        <v>148</v>
+        <v>331</v>
       </c>
       <c r="H83" s="2">
-        <v>45790</v>
+        <v>46241</v>
       </c>
       <c r="I83" s="3">
-        <v>483</v>
+        <v>34</v>
       </c>
       <c r="J83" t="s">
-        <v>52</v>
+        <v>276</v>
       </c>
       <c r="K83" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L83" s="2">
-        <v>43964</v>
+        <v>46086</v>
       </c>
       <c r="M83" s="3">
-        <v>62</v>
-      </c>
-      <c r="O83" t="s">
-        <v>69</v>
-      </c>
-      <c r="P83" s="2">
-        <v>46160</v>
+        <v>171</v>
       </c>
       <c r="S83" s="2">
-        <v>44917</v>
-      </c>
-      <c r="T83" s="3"/>
+        <v>47181</v>
+      </c>
+      <c r="T83" s="3">
+        <v>906</v>
+      </c>
       <c r="U83" s="3"/>
       <c r="V83" s="4">
-        <v>139755.72</v>
+        <v>73620</v>
       </c>
     </row>
     <row r="84" spans="1:22">
       <c r="A84" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B84" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C84" s="2">
-        <v>46260</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F84" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="G84" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="H84" s="2">
-        <v>46261</v>
+        <v>46094</v>
       </c>
       <c r="I84" s="3">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="J84" t="s">
-        <v>28</v>
-      </c>
-      <c r="M84" s="3"/>
-      <c r="T84" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="K84" t="s">
+        <v>334</v>
+      </c>
+      <c r="L84" s="2">
+        <v>46086</v>
+      </c>
+      <c r="M84" s="3">
+        <v>171</v>
+      </c>
+      <c r="S84" s="2">
+        <v>47181</v>
+      </c>
+      <c r="T84" s="3">
+        <v>906</v>
+      </c>
       <c r="U84" s="3"/>
       <c r="V84" s="4">
-        <v>171000</v>
+        <v>104220</v>
       </c>
     </row>
     <row r="85" spans="1:22">
       <c r="A85" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B85" t="s">
-        <v>333</v>
+        <v>67</v>
       </c>
       <c r="C85" s="2">
-        <v>46266</v>
+        <v>43902</v>
       </c>
       <c r="D85" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>334</v>
+        <v>68</v>
       </c>
       <c r="F85" t="s">
-        <v>274</v>
+        <v>49</v>
       </c>
       <c r="G85" t="s">
+        <v>155</v>
+      </c>
+      <c r="H85" s="2">
+        <v>45790</v>
+      </c>
+      <c r="I85" s="3">
+        <v>485</v>
+      </c>
+      <c r="J85" t="s">
+        <v>38</v>
+      </c>
+      <c r="K85" t="s">
         <v>335</v>
       </c>
-      <c r="H85" s="2">
-        <v>46269</v>
-      </c>
-      <c r="I85" s="3">
-        <v>4</v>
-      </c>
-      <c r="J85" t="s">
-        <v>266</v>
-      </c>
-      <c r="M85" s="3"/>
+      <c r="L85" s="2">
+        <v>43964</v>
+      </c>
+      <c r="M85" s="3">
+        <v>62</v>
+      </c>
+      <c r="O85" t="s">
+        <v>76</v>
+      </c>
+      <c r="P85" s="2">
+        <v>46160</v>
+      </c>
+      <c r="S85" s="2">
+        <v>44917</v>
+      </c>
       <c r="T85" s="3"/>
       <c r="U85" s="3"/>
       <c r="V85" s="4">
-        <v>171000</v>
+        <v>139755.72</v>
       </c>
     </row>
     <row r="86" spans="1:22">
       <c r="A86" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B86" t="s">
         <v>336</v>
       </c>
       <c r="C86" s="2">
-        <v>46245</v>
+        <v>46260</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E86" t="s">
         <v>337</v>
       </c>
       <c r="F86" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" t="s">
         <v>338</v>
       </c>
-      <c r="G86" t="s">
-        <v>265</v>
-      </c>
       <c r="H86" s="2">
-        <v>46267</v>
+        <v>46261</v>
       </c>
       <c r="I86" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J86" t="s">
-        <v>266</v>
+        <v>28</v>
       </c>
       <c r="M86" s="3"/>
       <c r="T86" s="3"/>
       <c r="U86" s="3"/>
       <c r="V86" s="4">
-        <v>180600</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="87" spans="1:22">
       <c r="A87" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B87" t="s">
         <v>339</v>
       </c>
       <c r="C87" s="2">
-        <v>45819</v>
+        <v>46266</v>
       </c>
       <c r="D87" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E87" t="s">
         <v>340</v>
       </c>
       <c r="F87" t="s">
-        <v>42</v>
+        <v>341</v>
       </c>
       <c r="G87" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H87" s="2">
-        <v>46170</v>
+        <v>46274</v>
       </c>
       <c r="I87" s="3">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>52</v>
-      </c>
-      <c r="K87" t="s">
-        <v>342</v>
-      </c>
-      <c r="L87" s="2">
-        <v>45904</v>
-      </c>
-      <c r="M87" s="3">
-        <v>85</v>
-      </c>
-      <c r="S87" s="2">
-        <v>46273</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="M87" s="3"/>
       <c r="T87" s="3"/>
       <c r="U87" s="3"/>
       <c r="V87" s="4">
-        <v>230000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="88" spans="1:22">
       <c r="A88" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B88" t="s">
         <v>343</v>
       </c>
       <c r="C88" s="2">
-        <v>45952</v>
+        <v>46245</v>
       </c>
       <c r="D88" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E88" t="s">
         <v>344</v>
       </c>
       <c r="F88" t="s">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="G88" t="s">
-        <v>346</v>
+        <v>272</v>
       </c>
       <c r="H88" s="2">
-        <v>46087</v>
+        <v>46273</v>
       </c>
       <c r="I88" s="3">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="J88" t="s">
-        <v>52</v>
-      </c>
-      <c r="K88" t="s">
-        <v>347</v>
-      </c>
-      <c r="L88" s="2">
-        <v>46086</v>
-      </c>
-      <c r="M88" s="3">
-        <v>134</v>
-      </c>
-      <c r="S88" s="2">
-        <v>47910</v>
-      </c>
-      <c r="T88" s="3">
-        <v>1637</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="M88" s="3"/>
+      <c r="T88" s="3"/>
       <c r="U88" s="3"/>
       <c r="V88" s="4">
-        <v>250977.6</v>
+        <v>180600</v>
       </c>
     </row>
     <row r="89" spans="1:22">
       <c r="A89" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B89" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="C89" s="2">
-        <v>45775</v>
+        <v>45819</v>
       </c>
       <c r="D89" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E89" t="s">
+        <v>346</v>
+      </c>
+      <c r="F89" t="s">
+        <v>49</v>
+      </c>
+      <c r="G89" t="s">
+        <v>347</v>
+      </c>
+      <c r="H89" s="2">
+        <v>46170</v>
+      </c>
+      <c r="I89" s="3">
+        <v>105</v>
+      </c>
+      <c r="J89" t="s">
+        <v>59</v>
+      </c>
+      <c r="K89" t="s">
         <v>348</v>
       </c>
-      <c r="F89" t="s">
-        <v>42</v>
-      </c>
-      <c r="G89" t="s">
-        <v>51</v>
-      </c>
-      <c r="H89" s="2">
-        <v>45861</v>
-      </c>
-      <c r="I89" s="3">
-        <v>412</v>
-      </c>
-      <c r="J89" t="s">
-        <v>38</v>
-      </c>
-      <c r="K89" t="s">
-        <v>322</v>
-      </c>
       <c r="L89" s="2">
-        <v>45856</v>
+        <v>45904</v>
       </c>
       <c r="M89" s="3">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="S89" s="2">
-        <v>46225</v>
+        <v>46273</v>
       </c>
       <c r="T89" s="3"/>
       <c r="U89" s="3"/>
       <c r="V89" s="4">
-        <v>288862</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="90" spans="1:22">
       <c r="A90" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B90" t="s">
         <v>349</v>
       </c>
       <c r="C90" s="2">
-        <v>45539</v>
+        <v>45952</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E90" t="s">
         <v>350</v>
@@ -5786,417 +5770,433 @@
         <v>352</v>
       </c>
       <c r="H90" s="2">
-        <v>45607</v>
+        <v>46087</v>
       </c>
       <c r="I90" s="3">
-        <v>666</v>
+        <v>188</v>
       </c>
       <c r="J90" t="s">
-        <v>52</v>
-      </c>
-      <c r="M90" s="3"/>
-      <c r="T90" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="K90" t="s">
+        <v>353</v>
+      </c>
+      <c r="L90" s="2">
+        <v>46086</v>
+      </c>
+      <c r="M90" s="3">
+        <v>134</v>
+      </c>
+      <c r="S90" s="2">
+        <v>47910</v>
+      </c>
+      <c r="T90" s="3">
+        <v>1635</v>
+      </c>
       <c r="U90" s="3"/>
       <c r="V90" s="4">
-        <v>297600</v>
+        <v>250977.6</v>
       </c>
     </row>
     <row r="91" spans="1:22">
       <c r="A91" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B91" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="C91" s="2">
-        <v>45840</v>
+        <v>45775</v>
       </c>
       <c r="D91" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E91" t="s">
         <v>354</v>
       </c>
       <c r="F91" t="s">
-        <v>355</v>
+        <v>49</v>
       </c>
       <c r="G91" t="s">
-        <v>356</v>
+        <v>58</v>
       </c>
       <c r="H91" s="2">
-        <v>46002</v>
+        <v>45861</v>
       </c>
       <c r="I91" s="3">
-        <v>271</v>
+        <v>414</v>
       </c>
       <c r="J91" t="s">
         <v>38</v>
       </c>
       <c r="K91" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="L91" s="2">
-        <v>46001</v>
+        <v>45856</v>
       </c>
       <c r="M91" s="3">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="S91" s="2">
-        <v>47097</v>
-      </c>
-      <c r="T91" s="3">
-        <v>824</v>
-      </c>
+        <v>46225</v>
+      </c>
+      <c r="T91" s="3"/>
       <c r="U91" s="3"/>
       <c r="V91" s="4">
-        <v>299821.5</v>
+        <v>288862</v>
       </c>
     </row>
     <row r="92" spans="1:22">
       <c r="A92" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B92" t="s">
+        <v>355</v>
+      </c>
+      <c r="C92" s="2">
+        <v>45539</v>
+      </c>
+      <c r="D92" t="s">
+        <v>51</v>
+      </c>
+      <c r="E92" t="s">
+        <v>356</v>
+      </c>
+      <c r="F92" t="s">
+        <v>357</v>
+      </c>
+      <c r="G92" t="s">
         <v>358</v>
       </c>
-      <c r="C92" s="2">
-        <v>45868</v>
-      </c>
-      <c r="D92" t="s">
-        <v>24</v>
-      </c>
-      <c r="E92" t="s">
-        <v>359</v>
-      </c>
-      <c r="F92" t="s">
-        <v>66</v>
-      </c>
-      <c r="G92" t="s">
-        <v>360</v>
-      </c>
       <c r="H92" s="2">
-        <v>46146</v>
+        <v>45607</v>
       </c>
       <c r="I92" s="3">
-        <v>127</v>
+        <v>668</v>
       </c>
       <c r="J92" t="s">
-        <v>52</v>
-      </c>
-      <c r="K92" t="s">
-        <v>361</v>
-      </c>
-      <c r="L92" s="2">
-        <v>46077</v>
-      </c>
-      <c r="M92" s="3">
-        <v>209</v>
-      </c>
-      <c r="S92" s="2">
-        <v>47905</v>
-      </c>
-      <c r="T92" s="3">
-        <v>1632</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M92" s="3"/>
+      <c r="T92" s="3"/>
       <c r="U92" s="3"/>
       <c r="V92" s="4">
-        <v>338580</v>
+        <v>297600</v>
       </c>
     </row>
     <row r="93" spans="1:22">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B93" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C93" s="2">
-        <v>44370</v>
+        <v>45840</v>
       </c>
       <c r="D93" t="s">
         <v>24</v>
       </c>
       <c r="E93" t="s">
+        <v>360</v>
+      </c>
+      <c r="F93" t="s">
+        <v>361</v>
+      </c>
+      <c r="G93" t="s">
+        <v>362</v>
+      </c>
+      <c r="H93" s="2">
+        <v>46002</v>
+      </c>
+      <c r="I93" s="3">
+        <v>273</v>
+      </c>
+      <c r="J93" t="s">
+        <v>38</v>
+      </c>
+      <c r="K93" t="s">
         <v>363</v>
       </c>
-      <c r="F93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G93" t="s">
-        <v>148</v>
-      </c>
-      <c r="H93" s="2">
-        <v>45881</v>
-      </c>
-      <c r="I93" s="3">
-        <v>392</v>
-      </c>
-      <c r="J93" t="s">
-        <v>52</v>
-      </c>
-      <c r="K93" t="s">
-        <v>364</v>
-      </c>
       <c r="L93" s="2">
-        <v>44589</v>
+        <v>46001</v>
       </c>
       <c r="M93" s="3">
-        <v>219</v>
-      </c>
-      <c r="O93" t="s">
-        <v>365</v>
-      </c>
-      <c r="P93" s="2">
-        <v>46419</v>
+        <v>161</v>
       </c>
       <c r="S93" s="2">
-        <v>44593</v>
-      </c>
-      <c r="T93" s="3"/>
-      <c r="U93" s="3">
-        <v>146</v>
-      </c>
+        <v>47097</v>
+      </c>
+      <c r="T93" s="3">
+        <v>822</v>
+      </c>
+      <c r="U93" s="3"/>
       <c r="V93" s="4">
-        <v>374899.96</v>
+        <v>299821.5</v>
       </c>
     </row>
     <row r="94" spans="1:22">
       <c r="A94" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B94" t="s">
+        <v>364</v>
+      </c>
+      <c r="C94" s="2">
+        <v>45868</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94" t="s">
+        <v>365</v>
+      </c>
+      <c r="F94" t="s">
+        <v>73</v>
+      </c>
+      <c r="G94" t="s">
         <v>366</v>
       </c>
-      <c r="C94" s="2">
-        <v>45422</v>
-      </c>
-      <c r="D94" t="s">
-        <v>44</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="H94" s="2">
+        <v>46146</v>
+      </c>
+      <c r="I94" s="3">
+        <v>129</v>
+      </c>
+      <c r="J94" t="s">
+        <v>59</v>
+      </c>
+      <c r="K94" t="s">
         <v>367</v>
       </c>
-      <c r="F94" t="s">
-        <v>42</v>
-      </c>
-      <c r="G94" t="s">
-        <v>368</v>
-      </c>
-      <c r="H94" s="2">
-        <v>45624</v>
-      </c>
-      <c r="I94" s="3">
-        <v>649</v>
-      </c>
-      <c r="J94" t="s">
-        <v>38</v>
-      </c>
-      <c r="K94" t="s">
-        <v>369</v>
-      </c>
       <c r="L94" s="2">
-        <v>45544</v>
+        <v>46077</v>
       </c>
       <c r="M94" s="3">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="S94" s="2">
-        <v>45911</v>
-      </c>
-      <c r="T94" s="3"/>
+        <v>47905</v>
+      </c>
+      <c r="T94" s="3">
+        <v>1630</v>
+      </c>
       <c r="U94" s="3"/>
       <c r="V94" s="4">
-        <v>457600</v>
+        <v>338580</v>
       </c>
     </row>
     <row r="95" spans="1:22">
       <c r="A95" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B95" t="s">
+        <v>368</v>
+      </c>
+      <c r="C95" s="2">
+        <v>44370</v>
+      </c>
+      <c r="D95" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" t="s">
+        <v>369</v>
+      </c>
+      <c r="F95" t="s">
+        <v>49</v>
+      </c>
+      <c r="G95" t="s">
+        <v>155</v>
+      </c>
+      <c r="H95" s="2">
+        <v>45881</v>
+      </c>
+      <c r="I95" s="3">
+        <v>394</v>
+      </c>
+      <c r="J95" t="s">
+        <v>59</v>
+      </c>
+      <c r="K95" t="s">
         <v>370</v>
       </c>
-      <c r="C95" s="2">
-        <v>46038</v>
-      </c>
-      <c r="D95" t="s">
-        <v>44</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="L95" s="2">
+        <v>44589</v>
+      </c>
+      <c r="M95" s="3">
+        <v>219</v>
+      </c>
+      <c r="O95" t="s">
         <v>371</v>
       </c>
-      <c r="F95" t="s">
-        <v>42</v>
-      </c>
-      <c r="G95" t="s">
-        <v>372</v>
-      </c>
-      <c r="H95" s="2">
-        <v>46237</v>
-      </c>
-      <c r="I95" s="3">
-        <v>36</v>
-      </c>
-      <c r="J95" t="s">
-        <v>52</v>
-      </c>
-      <c r="M95" s="3"/>
+      <c r="P95" s="2">
+        <v>46419</v>
+      </c>
+      <c r="S95" s="2">
+        <v>44593</v>
+      </c>
       <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
+      <c r="U95" s="3">
+        <v>144</v>
+      </c>
       <c r="V95" s="4">
-        <v>687500</v>
+        <v>374899.96</v>
       </c>
     </row>
     <row r="96" spans="1:22">
       <c r="A96" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B96" t="s">
+        <v>372</v>
+      </c>
+      <c r="C96" s="2">
+        <v>45422</v>
+      </c>
+      <c r="D96" t="s">
+        <v>51</v>
+      </c>
+      <c r="E96" t="s">
         <v>373</v>
       </c>
-      <c r="C96" s="2">
-        <v>44939</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
+        <v>49</v>
+      </c>
+      <c r="G96" t="s">
         <v>374</v>
       </c>
-      <c r="E96" t="s">
+      <c r="H96" s="2">
+        <v>45624</v>
+      </c>
+      <c r="I96" s="3">
+        <v>651</v>
+      </c>
+      <c r="J96" t="s">
+        <v>38</v>
+      </c>
+      <c r="K96" t="s">
         <v>375</v>
       </c>
-      <c r="F96" t="s">
-        <v>29</v>
-      </c>
-      <c r="G96" t="s">
-        <v>376</v>
-      </c>
-      <c r="H96" s="2">
-        <v>45979</v>
-      </c>
-      <c r="I96" s="3">
-        <v>294</v>
-      </c>
-      <c r="J96" t="s">
-        <v>52</v>
-      </c>
-      <c r="K96" t="s">
-        <v>377</v>
-      </c>
       <c r="L96" s="2">
-        <v>45968</v>
+        <v>45544</v>
       </c>
       <c r="M96" s="3">
-        <v>1029</v>
-      </c>
-      <c r="O96" t="s">
-        <v>365</v>
-      </c>
-      <c r="P96" s="2">
-        <v>46426</v>
+        <v>122</v>
       </c>
       <c r="S96" s="2">
-        <v>45334</v>
+        <v>45911</v>
       </c>
       <c r="T96" s="3"/>
-      <c r="U96" s="3">
-        <v>153</v>
-      </c>
+      <c r="U96" s="3"/>
       <c r="V96" s="4">
-        <v>706431.6</v>
+        <v>457600</v>
       </c>
     </row>
     <row r="97" spans="1:22">
       <c r="A97" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B97" t="s">
+        <v>376</v>
+      </c>
+      <c r="C97" s="2">
+        <v>46038</v>
+      </c>
+      <c r="D97" t="s">
+        <v>51</v>
+      </c>
+      <c r="E97" t="s">
+        <v>377</v>
+      </c>
+      <c r="F97" t="s">
+        <v>49</v>
+      </c>
+      <c r="G97" t="s">
         <v>378</v>
       </c>
-      <c r="C97" s="2">
-        <v>45673</v>
-      </c>
-      <c r="D97" t="s">
-        <v>24</v>
-      </c>
-      <c r="E97" t="s">
-        <v>379</v>
-      </c>
-      <c r="F97" t="s">
-        <v>42</v>
-      </c>
-      <c r="G97" t="s">
-        <v>51</v>
-      </c>
       <c r="H97" s="2">
-        <v>46140</v>
+        <v>46237</v>
       </c>
       <c r="I97" s="3">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="J97" t="s">
-        <v>52</v>
-      </c>
-      <c r="K97" t="s">
-        <v>380</v>
+        <v>59</v>
       </c>
       <c r="M97" s="3"/>
-      <c r="S97" s="2">
-        <v>46598</v>
-      </c>
-      <c r="T97" s="3">
-        <v>325</v>
-      </c>
+      <c r="T97" s="3"/>
       <c r="U97" s="3"/>
       <c r="V97" s="4">
-        <v>890000</v>
+        <v>687500</v>
       </c>
     </row>
     <row r="98" spans="1:22">
       <c r="A98" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B98" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="2">
+        <v>44939</v>
+      </c>
+      <c r="D98" t="s">
+        <v>380</v>
+      </c>
+      <c r="E98" t="s">
         <v>381</v>
       </c>
-      <c r="C98" s="2">
-        <v>46260</v>
-      </c>
-      <c r="D98" t="s">
-        <v>44</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
+        <v>29</v>
+      </c>
+      <c r="G98" t="s">
         <v>382</v>
       </c>
-      <c r="F98" t="s">
-        <v>26</v>
-      </c>
-      <c r="G98" t="s">
+      <c r="H98" s="2">
+        <v>46274</v>
+      </c>
+      <c r="I98" s="3">
+        <v>1</v>
+      </c>
+      <c r="J98" t="s">
+        <v>276</v>
+      </c>
+      <c r="K98" t="s">
         <v>383</v>
       </c>
-      <c r="H98" s="2">
-        <v>46266</v>
-      </c>
-      <c r="I98" s="3">
-        <v>7</v>
-      </c>
-      <c r="J98" t="s">
-        <v>266</v>
-      </c>
-      <c r="M98" s="3"/>
+      <c r="L98" s="2">
+        <v>45968</v>
+      </c>
+      <c r="M98" s="3">
+        <v>1029</v>
+      </c>
+      <c r="O98" t="s">
+        <v>371</v>
+      </c>
+      <c r="P98" s="2">
+        <v>46426</v>
+      </c>
+      <c r="S98" s="2">
+        <v>45334</v>
+      </c>
       <c r="T98" s="3"/>
-      <c r="U98" s="3"/>
+      <c r="U98" s="3">
+        <v>151</v>
+      </c>
       <c r="V98" s="4">
-        <v>1170000</v>
+        <v>706431.6</v>
       </c>
     </row>
     <row r="99" spans="1:22">
       <c r="A99" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B99" t="s">
         <v>384</v>
       </c>
       <c r="C99" s="2">
-        <v>45215</v>
+        <v>45673</v>
       </c>
       <c r="D99" t="s">
         <v>24</v>
@@ -6205,568 +6205,563 @@
         <v>385</v>
       </c>
       <c r="F99" t="s">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="G99" t="s">
+        <v>58</v>
+      </c>
+      <c r="H99" s="2">
+        <v>46140</v>
+      </c>
+      <c r="I99" s="3">
+        <v>135</v>
+      </c>
+      <c r="J99" t="s">
+        <v>59</v>
+      </c>
+      <c r="K99" t="s">
         <v>386</v>
       </c>
-      <c r="H99" s="2">
-        <v>45687</v>
-      </c>
-      <c r="I99" s="3">
-        <v>586</v>
-      </c>
-      <c r="J99" t="s">
-        <v>38</v>
-      </c>
-      <c r="K99" t="s">
-        <v>387</v>
-      </c>
-      <c r="L99" s="2">
-        <v>45685</v>
-      </c>
-      <c r="M99" s="3">
-        <v>470</v>
-      </c>
+      <c r="M99" s="3"/>
       <c r="S99" s="2">
-        <v>46780</v>
+        <v>46598</v>
       </c>
       <c r="T99" s="3">
-        <v>507</v>
+        <v>323</v>
       </c>
       <c r="U99" s="3"/>
       <c r="V99" s="4">
-        <v>1220266.1399999999</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="100" spans="1:22">
       <c r="A100" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B100" t="s">
+        <v>387</v>
+      </c>
+      <c r="C100" s="2">
+        <v>46260</v>
+      </c>
+      <c r="D100" t="s">
+        <v>51</v>
+      </c>
+      <c r="E100" t="s">
         <v>388</v>
       </c>
-      <c r="C100" s="2">
-        <v>45366</v>
-      </c>
-      <c r="D100" t="s">
-        <v>44</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
+        <v>176</v>
+      </c>
+      <c r="G100" t="s">
         <v>389</v>
       </c>
-      <c r="F100" t="s">
-        <v>42</v>
-      </c>
-      <c r="G100" t="s">
-        <v>390</v>
-      </c>
       <c r="H100" s="2">
-        <v>45481</v>
+        <v>46274</v>
       </c>
       <c r="I100" s="3">
-        <v>792</v>
+        <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>52</v>
-      </c>
-      <c r="K100" t="s">
-        <v>391</v>
-      </c>
-      <c r="L100" s="2">
-        <v>45471</v>
-      </c>
-      <c r="M100" s="3">
-        <v>105</v>
-      </c>
-      <c r="S100" s="2">
-        <v>47301</v>
-      </c>
-      <c r="T100" s="3">
-        <v>1028</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="M100" s="3"/>
+      <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="4">
-        <v>1245414.49</v>
+        <v>1170000</v>
       </c>
     </row>
     <row r="101" spans="1:22">
       <c r="A101" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B101" t="s">
+        <v>390</v>
+      </c>
+      <c r="C101" s="2">
+        <v>45215</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" t="s">
+        <v>391</v>
+      </c>
+      <c r="F101" t="s">
+        <v>176</v>
+      </c>
+      <c r="G101" t="s">
         <v>392</v>
       </c>
-      <c r="C101" s="2">
-        <v>45152</v>
-      </c>
-      <c r="D101" t="s">
-        <v>268</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="H101" s="2">
+        <v>45687</v>
+      </c>
+      <c r="I101" s="3">
+        <v>588</v>
+      </c>
+      <c r="J101" t="s">
+        <v>38</v>
+      </c>
+      <c r="K101" t="s">
         <v>393</v>
       </c>
-      <c r="F101" t="s">
-        <v>29</v>
-      </c>
-      <c r="G101" t="s">
-        <v>394</v>
-      </c>
-      <c r="H101" s="2">
-        <v>45440</v>
-      </c>
-      <c r="I101" s="3">
-        <v>833</v>
-      </c>
-      <c r="J101" t="s">
-        <v>52</v>
-      </c>
-      <c r="K101" t="s">
-        <v>395</v>
-      </c>
       <c r="L101" s="2">
-        <v>45303</v>
+        <v>45685</v>
       </c>
       <c r="M101" s="3">
-        <v>151</v>
+        <v>470</v>
       </c>
       <c r="S101" s="2">
-        <v>45992</v>
-      </c>
-      <c r="T101" s="3"/>
+        <v>46780</v>
+      </c>
+      <c r="T101" s="3">
+        <v>505</v>
+      </c>
       <c r="U101" s="3"/>
       <c r="V101" s="4">
-        <v>1298031.3600000001</v>
+        <v>1220266.1399999999</v>
       </c>
     </row>
     <row r="102" spans="1:22">
       <c r="A102" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B102" t="s">
+        <v>394</v>
+      </c>
+      <c r="C102" s="2">
+        <v>45366</v>
+      </c>
+      <c r="D102" t="s">
+        <v>51</v>
+      </c>
+      <c r="E102" t="s">
+        <v>395</v>
+      </c>
+      <c r="F102" t="s">
+        <v>49</v>
+      </c>
+      <c r="G102" t="s">
         <v>396</v>
       </c>
-      <c r="C102" s="2">
-        <v>45373</v>
-      </c>
-      <c r="D102" t="s">
-        <v>44</v>
-      </c>
-      <c r="E102" t="s">
+      <c r="H102" s="2">
+        <v>45481</v>
+      </c>
+      <c r="I102" s="3">
+        <v>794</v>
+      </c>
+      <c r="J102" t="s">
+        <v>59</v>
+      </c>
+      <c r="K102" t="s">
         <v>397</v>
       </c>
-      <c r="F102" t="s">
-        <v>42</v>
-      </c>
-      <c r="G102" t="s">
-        <v>390</v>
-      </c>
-      <c r="H102" s="2">
-        <v>45492</v>
-      </c>
-      <c r="I102" s="3">
-        <v>781</v>
-      </c>
-      <c r="J102" t="s">
-        <v>52</v>
-      </c>
-      <c r="K102" t="s">
-        <v>398</v>
-      </c>
       <c r="L102" s="2">
-        <v>45492</v>
+        <v>45471</v>
       </c>
       <c r="M102" s="3">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="S102" s="2">
-        <v>46587</v>
+        <v>47301</v>
       </c>
       <c r="T102" s="3">
-        <v>314</v>
+        <v>1026</v>
       </c>
       <c r="U102" s="3"/>
       <c r="V102" s="4">
-        <v>1320176.8799999999</v>
+        <v>1245414.49</v>
       </c>
     </row>
     <row r="103" spans="1:22">
       <c r="A103" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B103" t="s">
+        <v>398</v>
+      </c>
+      <c r="C103" s="2">
+        <v>45152</v>
+      </c>
+      <c r="D103" t="s">
+        <v>274</v>
+      </c>
+      <c r="E103" t="s">
         <v>399</v>
       </c>
-      <c r="C103" s="2">
-        <v>44663</v>
-      </c>
-      <c r="D103" t="s">
-        <v>24</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
+        <v>29</v>
+      </c>
+      <c r="G103" t="s">
         <v>400</v>
       </c>
-      <c r="F103" t="s">
-        <v>128</v>
-      </c>
-      <c r="G103" t="s">
-        <v>200</v>
-      </c>
       <c r="H103" s="2">
-        <v>45588</v>
+        <v>45440</v>
       </c>
       <c r="I103" s="3">
-        <v>685</v>
+        <v>835</v>
       </c>
       <c r="J103" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K103" t="s">
         <v>401</v>
       </c>
       <c r="L103" s="2">
-        <v>44893</v>
+        <v>45303</v>
       </c>
       <c r="M103" s="3">
-        <v>230</v>
-      </c>
-      <c r="O103" t="s">
-        <v>59</v>
-      </c>
-      <c r="P103" s="2">
-        <v>45996</v>
+        <v>151</v>
       </c>
       <c r="S103" s="2">
-        <v>45624</v>
+        <v>45992</v>
       </c>
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
       <c r="V103" s="4">
-        <v>1416380</v>
+        <v>1298031.3600000001</v>
       </c>
     </row>
     <row r="104" spans="1:22">
       <c r="A104" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B104" t="s">
         <v>402</v>
       </c>
       <c r="C104" s="2">
-        <v>45826</v>
+        <v>45373</v>
       </c>
       <c r="D104" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E104" t="s">
         <v>403</v>
       </c>
       <c r="F104" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="G104" t="s">
+        <v>396</v>
+      </c>
+      <c r="H104" s="2">
+        <v>45492</v>
+      </c>
+      <c r="I104" s="3">
+        <v>783</v>
+      </c>
+      <c r="J104" t="s">
+        <v>59</v>
+      </c>
+      <c r="K104" t="s">
         <v>404</v>
       </c>
-      <c r="H104" s="2">
-        <v>46079</v>
-      </c>
-      <c r="I104" s="3">
-        <v>194</v>
-      </c>
-      <c r="J104" t="s">
-        <v>52</v>
-      </c>
-      <c r="K104" t="s">
-        <v>405</v>
-      </c>
       <c r="L104" s="2">
-        <v>46076</v>
+        <v>45492</v>
       </c>
       <c r="M104" s="3">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="S104" s="2">
-        <v>47903</v>
+        <v>46587</v>
       </c>
       <c r="T104" s="3">
-        <v>1630</v>
+        <v>312</v>
       </c>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
-        <v>1435000</v>
+        <v>1320176.8799999999</v>
       </c>
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
+        <v>49</v>
+      </c>
+      <c r="B105" t="s">
+        <v>405</v>
+      </c>
+      <c r="C105" s="2">
+        <v>44663</v>
+      </c>
+      <c r="D105" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" t="s">
         <v>406</v>
       </c>
-      <c r="B105" t="s">
+      <c r="F105" t="s">
+        <v>135</v>
+      </c>
+      <c r="G105" t="s">
+        <v>207</v>
+      </c>
+      <c r="H105" s="2">
+        <v>45588</v>
+      </c>
+      <c r="I105" s="3">
+        <v>687</v>
+      </c>
+      <c r="J105" t="s">
+        <v>38</v>
+      </c>
+      <c r="K105" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="2">
-        <v>46150</v>
-      </c>
-      <c r="D105" t="s">
-        <v>44</v>
-      </c>
-      <c r="E105" t="s">
-        <v>408</v>
-      </c>
-      <c r="F105" t="s">
-        <v>406</v>
-      </c>
-      <c r="G105" t="s">
-        <v>372</v>
-      </c>
-      <c r="H105" s="2">
-        <v>46206</v>
-      </c>
-      <c r="I105" s="3">
-        <v>67</v>
-      </c>
-      <c r="J105" t="s">
-        <v>52</v>
-      </c>
-      <c r="M105" s="3"/>
+      <c r="L105" s="2">
+        <v>44893</v>
+      </c>
+      <c r="M105" s="3">
+        <v>230</v>
+      </c>
+      <c r="O105" t="s">
+        <v>66</v>
+      </c>
+      <c r="P105" s="2">
+        <v>45996</v>
+      </c>
+      <c r="S105" s="2">
+        <v>45624</v>
+      </c>
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
       <c r="V105" s="4">
-        <v>1719174</v>
+        <v>1416380</v>
       </c>
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B106" t="s">
+        <v>408</v>
+      </c>
+      <c r="C106" s="2">
+        <v>45826</v>
+      </c>
+      <c r="D106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" t="s">
         <v>409</v>
       </c>
-      <c r="C106" s="2">
-        <v>46094</v>
-      </c>
-      <c r="D106" t="s">
-        <v>44</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
+        <v>73</v>
+      </c>
+      <c r="G106" t="s">
         <v>410</v>
       </c>
-      <c r="F106" t="s">
+      <c r="H106" s="2">
+        <v>46079</v>
+      </c>
+      <c r="I106" s="3">
+        <v>196</v>
+      </c>
+      <c r="J106" t="s">
+        <v>59</v>
+      </c>
+      <c r="K106" t="s">
         <v>411</v>
       </c>
-      <c r="G106" t="s">
-        <v>412</v>
-      </c>
-      <c r="H106" s="2">
-        <v>46211</v>
-      </c>
-      <c r="I106" s="3">
-        <v>62</v>
-      </c>
-      <c r="J106" t="s">
-        <v>52</v>
-      </c>
-      <c r="M106" s="3"/>
-      <c r="T106" s="3"/>
+      <c r="L106" s="2">
+        <v>46076</v>
+      </c>
+      <c r="M106" s="3">
+        <v>250</v>
+      </c>
+      <c r="S106" s="2">
+        <v>47903</v>
+      </c>
+      <c r="T106" s="3">
+        <v>1628</v>
+      </c>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
-        <v>1828126.08</v>
+        <v>1435000</v>
       </c>
     </row>
     <row r="107" spans="1:22">
       <c r="A107" t="s">
-        <v>42</v>
+        <v>412</v>
       </c>
       <c r="B107" t="s">
         <v>413</v>
       </c>
       <c r="C107" s="2">
-        <v>45950</v>
+        <v>46150</v>
       </c>
       <c r="D107" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E107" t="s">
         <v>414</v>
       </c>
       <c r="F107" t="s">
-        <v>42</v>
+        <v>412</v>
       </c>
       <c r="G107" t="s">
-        <v>415</v>
+        <v>378</v>
       </c>
       <c r="H107" s="2">
-        <v>45988</v>
+        <v>46206</v>
       </c>
       <c r="I107" s="3">
-        <v>285</v>
+        <v>69</v>
       </c>
       <c r="J107" t="s">
-        <v>38</v>
-      </c>
-      <c r="K107" t="s">
-        <v>416</v>
-      </c>
-      <c r="L107" s="2">
-        <v>45979</v>
-      </c>
-      <c r="M107" s="3">
-        <v>29</v>
-      </c>
-      <c r="S107" s="2">
-        <v>46343</v>
-      </c>
-      <c r="T107" s="3">
-        <v>70</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="M107" s="3"/>
+      <c r="T107" s="3"/>
       <c r="U107" s="3"/>
       <c r="V107" s="4">
-        <v>2075682</v>
+        <v>1719174</v>
       </c>
     </row>
     <row r="108" spans="1:22">
       <c r="A108" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B108" t="s">
+        <v>415</v>
+      </c>
+      <c r="C108" s="2">
+        <v>46094</v>
+      </c>
+      <c r="D108" t="s">
+        <v>51</v>
+      </c>
+      <c r="E108" t="s">
+        <v>416</v>
+      </c>
+      <c r="F108" t="s">
         <v>417</v>
       </c>
-      <c r="C108" s="2">
-        <v>45511</v>
-      </c>
-      <c r="D108" t="s">
-        <v>24</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="G108" t="s">
         <v>418</v>
       </c>
-      <c r="F108" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" t="s">
-        <v>419</v>
-      </c>
       <c r="H108" s="2">
-        <v>45786</v>
+        <v>46211</v>
       </c>
       <c r="I108" s="3">
-        <v>487</v>
+        <v>64</v>
       </c>
       <c r="J108" t="s">
-        <v>38</v>
-      </c>
-      <c r="K108" t="s">
-        <v>420</v>
-      </c>
-      <c r="L108" s="2">
-        <v>45794</v>
-      </c>
-      <c r="M108" s="3">
-        <v>283</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="M108" s="3"/>
       <c r="T108" s="3"/>
       <c r="U108" s="3"/>
       <c r="V108" s="4">
-        <v>2594055</v>
+        <v>1828126.08</v>
       </c>
     </row>
     <row r="109" spans="1:22">
       <c r="A109" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B109" t="s">
+        <v>419</v>
+      </c>
+      <c r="C109" s="2">
+        <v>45950</v>
+      </c>
+      <c r="D109" t="s">
+        <v>51</v>
+      </c>
+      <c r="E109" t="s">
+        <v>420</v>
+      </c>
+      <c r="F109" t="s">
+        <v>49</v>
+      </c>
+      <c r="G109" t="s">
         <v>421</v>
       </c>
-      <c r="C109" s="2">
-        <v>45848</v>
-      </c>
-      <c r="D109" t="s">
-        <v>35</v>
-      </c>
-      <c r="E109" t="s">
-        <v>422</v>
-      </c>
-      <c r="F109" t="s">
-        <v>224</v>
-      </c>
-      <c r="G109" t="s">
-        <v>423</v>
-      </c>
       <c r="H109" s="2">
-        <v>46014</v>
+        <v>45988</v>
       </c>
       <c r="I109" s="3">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="J109" t="s">
         <v>38</v>
       </c>
       <c r="K109" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L109" s="2">
-        <v>46008</v>
+        <v>45979</v>
       </c>
       <c r="M109" s="3">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="S109" s="2">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="T109" s="3">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="U109" s="3"/>
       <c r="V109" s="4">
-        <v>2641069.35</v>
+        <v>2075682</v>
       </c>
     </row>
     <row r="110" spans="1:22">
       <c r="A110" t="s">
+        <v>49</v>
+      </c>
+      <c r="B110" t="s">
+        <v>423</v>
+      </c>
+      <c r="C110" s="2">
+        <v>45511</v>
+      </c>
+      <c r="D110" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110" t="s">
+        <v>424</v>
+      </c>
+      <c r="F110" t="s">
         <v>26</v>
       </c>
-      <c r="B110" t="s">
+      <c r="G110" t="s">
         <v>425</v>
       </c>
-      <c r="C110" s="2">
-        <v>46030</v>
-      </c>
-      <c r="D110" t="s">
-        <v>268</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="H110" s="2">
+        <v>45786</v>
+      </c>
+      <c r="I110" s="3">
+        <v>489</v>
+      </c>
+      <c r="J110" t="s">
+        <v>38</v>
+      </c>
+      <c r="K110" t="s">
         <v>426</v>
       </c>
-      <c r="F110" t="s">
-        <v>29</v>
-      </c>
-      <c r="G110" t="s">
-        <v>372</v>
-      </c>
-      <c r="H110" s="2">
-        <v>46237</v>
-      </c>
-      <c r="I110" s="3">
-        <v>36</v>
-      </c>
-      <c r="J110" t="s">
-        <v>52</v>
-      </c>
-      <c r="M110" s="3"/>
+      <c r="L110" s="2">
+        <v>45794</v>
+      </c>
+      <c r="M110" s="3">
+        <v>283</v>
+      </c>
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
       <c r="V110" s="4">
-        <v>2652975.2799999998</v>
+        <v>2594055</v>
       </c>
     </row>
     <row r="111" spans="1:22">
       <c r="A111" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B111" t="s">
         <v>427</v>
       </c>
       <c r="C111" s="2">
-        <v>45365</v>
+        <v>45848</v>
       </c>
       <c r="D111" t="s">
         <v>35</v>
@@ -6775,214 +6770,203 @@
         <v>428</v>
       </c>
       <c r="F111" t="s">
+        <v>231</v>
+      </c>
+      <c r="G111" t="s">
         <v>429</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" s="2">
+        <v>46014</v>
+      </c>
+      <c r="I111" s="3">
+        <v>261</v>
+      </c>
+      <c r="J111" t="s">
+        <v>38</v>
+      </c>
+      <c r="K111" t="s">
         <v>430</v>
       </c>
-      <c r="H111" s="2">
-        <v>45568</v>
-      </c>
-      <c r="I111" s="3">
-        <v>705</v>
-      </c>
-      <c r="J111" t="s">
-        <v>52</v>
-      </c>
-      <c r="K111" t="s">
-        <v>431</v>
-      </c>
       <c r="L111" s="2">
-        <v>45567</v>
+        <v>46008</v>
       </c>
       <c r="M111" s="3">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="S111" s="2">
-        <v>46479</v>
+        <v>46373</v>
       </c>
       <c r="T111" s="3">
-        <v>206</v>
+        <v>98</v>
       </c>
       <c r="U111" s="3"/>
       <c r="V111" s="4">
-        <v>2780400.6</v>
+        <v>2641069.35</v>
       </c>
     </row>
     <row r="112" spans="1:22">
       <c r="A112" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B112" t="s">
+        <v>431</v>
+      </c>
+      <c r="C112" s="2">
+        <v>46030</v>
+      </c>
+      <c r="D112" t="s">
+        <v>274</v>
+      </c>
+      <c r="E112" t="s">
         <v>432</v>
       </c>
-      <c r="C112" s="2">
-        <v>46245</v>
-      </c>
-      <c r="D112" t="s">
-        <v>44</v>
-      </c>
-      <c r="E112" t="s">
-        <v>433</v>
-      </c>
       <c r="F112" t="s">
-        <v>434</v>
+        <v>29</v>
       </c>
       <c r="G112" t="s">
-        <v>435</v>
+        <v>378</v>
       </c>
       <c r="H112" s="2">
-        <v>46268</v>
+        <v>46237</v>
       </c>
       <c r="I112" s="3">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="J112" t="s">
-        <v>266</v>
+        <v>59</v>
       </c>
       <c r="M112" s="3"/>
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
       <c r="V112" s="4">
-        <v>3446560</v>
+        <v>2652975.2799999998</v>
       </c>
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B113" t="s">
+        <v>433</v>
+      </c>
+      <c r="C113" s="2">
+        <v>45365</v>
+      </c>
+      <c r="D113" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" t="s">
+        <v>434</v>
+      </c>
+      <c r="F113" t="s">
+        <v>435</v>
+      </c>
+      <c r="G113" t="s">
         <v>436</v>
       </c>
-      <c r="C113" s="2">
-        <v>46232</v>
-      </c>
-      <c r="D113" t="s">
-        <v>44</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="H113" s="2">
+        <v>45568</v>
+      </c>
+      <c r="I113" s="3">
+        <v>707</v>
+      </c>
+      <c r="J113" t="s">
+        <v>59</v>
+      </c>
+      <c r="K113" t="s">
         <v>437</v>
       </c>
-      <c r="F113" t="s">
-        <v>26</v>
-      </c>
-      <c r="G113" t="s">
-        <v>438</v>
-      </c>
-      <c r="H113" s="2">
-        <v>46237</v>
-      </c>
-      <c r="I113" s="3">
-        <v>36</v>
-      </c>
-      <c r="J113" t="s">
-        <v>28</v>
-      </c>
-      <c r="M113" s="3"/>
-      <c r="T113" s="3"/>
+      <c r="L113" s="2">
+        <v>45567</v>
+      </c>
+      <c r="M113" s="3">
+        <v>202</v>
+      </c>
+      <c r="S113" s="2">
+        <v>46479</v>
+      </c>
+      <c r="T113" s="3">
+        <v>204</v>
+      </c>
       <c r="U113" s="3"/>
       <c r="V113" s="4">
-        <v>3446570</v>
+        <v>2780400.6</v>
       </c>
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B114" t="s">
+        <v>438</v>
+      </c>
+      <c r="C114" s="2">
+        <v>46245</v>
+      </c>
+      <c r="D114" t="s">
+        <v>51</v>
+      </c>
+      <c r="E114" t="s">
         <v>439</v>
       </c>
-      <c r="C114" s="2">
-        <v>45824</v>
-      </c>
-      <c r="D114" t="s">
-        <v>24</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
+        <v>176</v>
+      </c>
+      <c r="G114" t="s">
         <v>440</v>
       </c>
-      <c r="F114" t="s">
-        <v>441</v>
-      </c>
-      <c r="G114" t="s">
-        <v>442</v>
-      </c>
       <c r="H114" s="2">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="I114" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J114" t="s">
-        <v>271</v>
-      </c>
-      <c r="K114" t="s">
-        <v>443</v>
-      </c>
-      <c r="L114" s="2">
-        <v>45951</v>
-      </c>
-      <c r="M114" s="3">
-        <v>127</v>
-      </c>
-      <c r="O114" t="s">
-        <v>59</v>
-      </c>
-      <c r="S114" s="2">
-        <v>46316</v>
-      </c>
-      <c r="T114" s="3">
-        <v>43</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="M114" s="3"/>
+      <c r="T114" s="3"/>
       <c r="U114" s="3"/>
       <c r="V114" s="4">
-        <v>4130258.58</v>
+        <v>3446560</v>
       </c>
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
-        <v>444</v>
+        <v>49</v>
       </c>
       <c r="B115" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C115" s="2">
-        <v>45526</v>
+        <v>46232</v>
       </c>
       <c r="D115" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E115" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F115" t="s">
-        <v>444</v>
+        <v>26</v>
       </c>
       <c r="G115" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H115" s="2">
-        <v>45932</v>
+        <v>46237</v>
       </c>
       <c r="I115" s="3">
-        <v>341</v>
+        <v>38</v>
       </c>
       <c r="J115" t="s">
-        <v>52</v>
-      </c>
-      <c r="K115" t="s">
-        <v>448</v>
+        <v>28</v>
       </c>
       <c r="M115" s="3"/>
-      <c r="S115" s="2">
-        <v>47748</v>
-      </c>
-      <c r="T115" s="3">
-        <v>1475</v>
-      </c>
+      <c r="T115" s="3"/>
       <c r="U115" s="3"/>
       <c r="V115" s="4">
-        <v>4440928.34</v>
+        <v>3446570</v>
       </c>
     </row>
     <row r="116" spans="1:22">
@@ -6990,558 +6974,658 @@
         <v>26</v>
       </c>
       <c r="B116" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C116" s="2">
-        <v>45560</v>
+        <v>45824</v>
       </c>
       <c r="D116" t="s">
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F116" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="G116" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="H116" s="2">
-        <v>45930</v>
+        <v>46274</v>
       </c>
       <c r="I116" s="3">
-        <v>343</v>
+        <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>38</v>
+        <v>276</v>
       </c>
       <c r="K116" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="L116" s="2">
-        <v>45854</v>
+        <v>45951</v>
       </c>
       <c r="M116" s="3">
-        <v>294</v>
+        <v>127</v>
+      </c>
+      <c r="O116" t="s">
+        <v>66</v>
       </c>
       <c r="S116" s="2">
-        <v>46950</v>
+        <v>46316</v>
       </c>
       <c r="T116" s="3">
-        <v>677</v>
+        <v>41</v>
       </c>
       <c r="U116" s="3"/>
       <c r="V116" s="4">
-        <v>6210000</v>
+        <v>4130258.58</v>
       </c>
     </row>
     <row r="117" spans="1:22">
       <c r="A117" t="s">
-        <v>275</v>
+        <v>449</v>
       </c>
       <c r="B117" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C117" s="2">
-        <v>44607</v>
+        <v>45526</v>
       </c>
       <c r="D117" t="s">
-        <v>374</v>
+        <v>35</v>
       </c>
       <c r="E117" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F117" t="s">
-        <v>275</v>
+        <v>449</v>
       </c>
       <c r="G117" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H117" s="2">
-        <v>46196</v>
+        <v>45932</v>
       </c>
       <c r="I117" s="3">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="J117" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K117" t="s">
-        <v>457</v>
-      </c>
-      <c r="L117" s="2">
-        <v>44747</v>
-      </c>
-      <c r="M117" s="3">
-        <v>140</v>
-      </c>
-      <c r="O117" t="s">
-        <v>458</v>
-      </c>
-      <c r="P117" s="2">
-        <v>46573</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="M117" s="3"/>
       <c r="S117" s="2">
-        <v>45111</v>
-      </c>
-      <c r="T117" s="3"/>
-      <c r="U117" s="3">
-        <v>300</v>
-      </c>
+        <v>47748</v>
+      </c>
+      <c r="T117" s="3">
+        <v>1473</v>
+      </c>
+      <c r="U117" s="3"/>
       <c r="V117" s="4">
-        <v>6571898.25</v>
+        <v>4440928.34</v>
       </c>
     </row>
     <row r="118" spans="1:22">
       <c r="A118" t="s">
-        <v>459</v>
+        <v>26</v>
       </c>
       <c r="B118" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C118" s="2">
-        <v>38661</v>
+        <v>45560</v>
       </c>
       <c r="D118" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="F118" t="s">
-        <v>26</v>
+        <v>456</v>
       </c>
       <c r="G118" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="H118" s="2">
-        <v>45993</v>
+        <v>45930</v>
       </c>
       <c r="I118" s="3">
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="J118" t="s">
         <v>38</v>
       </c>
       <c r="K118" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="L118" s="2">
-        <v>45993</v>
+        <v>45854</v>
       </c>
       <c r="M118" s="3">
-        <v>7332</v>
+        <v>294</v>
       </c>
       <c r="S118" s="2">
-        <v>46540</v>
+        <v>46950</v>
       </c>
       <c r="T118" s="3">
-        <v>267</v>
+        <v>675</v>
       </c>
       <c r="U118" s="3"/>
       <c r="V118" s="4">
-        <v>9032000</v>
+        <v>6210000</v>
       </c>
     </row>
     <row r="119" spans="1:22">
       <c r="A119" t="s">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="B119" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C119" s="2">
-        <v>45560</v>
+        <v>44607</v>
       </c>
       <c r="D119" t="s">
-        <v>24</v>
+        <v>380</v>
       </c>
       <c r="E119" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F119" t="s">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="G119" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="H119" s="2">
-        <v>45797</v>
+        <v>46196</v>
       </c>
       <c r="I119" s="3">
-        <v>476</v>
+        <v>79</v>
       </c>
       <c r="J119" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K119" t="s">
-        <v>467</v>
-      </c>
-      <c r="M119" s="3"/>
+        <v>462</v>
+      </c>
+      <c r="L119" s="2">
+        <v>44747</v>
+      </c>
+      <c r="M119" s="3">
+        <v>140</v>
+      </c>
+      <c r="O119" t="s">
+        <v>463</v>
+      </c>
+      <c r="P119" s="2">
+        <v>46573</v>
+      </c>
       <c r="S119" s="2">
-        <v>46523</v>
-      </c>
-      <c r="T119" s="3">
-        <v>250</v>
-      </c>
-      <c r="U119" s="3"/>
+        <v>45111</v>
+      </c>
+      <c r="T119" s="3"/>
+      <c r="U119" s="3">
+        <v>298</v>
+      </c>
       <c r="V119" s="4">
-        <v>9152353</v>
+        <v>6571898.25</v>
       </c>
     </row>
     <row r="120" spans="1:22">
       <c r="A120" t="s">
-        <v>42</v>
+        <v>464</v>
       </c>
       <c r="B120" t="s">
+        <v>465</v>
+      </c>
+      <c r="C120" s="2">
+        <v>38661</v>
+      </c>
+      <c r="D120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" t="s">
+        <v>466</v>
+      </c>
+      <c r="F120" t="s">
+        <v>26</v>
+      </c>
+      <c r="G120" t="s">
+        <v>467</v>
+      </c>
+      <c r="H120" s="2">
+        <v>45993</v>
+      </c>
+      <c r="I120" s="3">
+        <v>282</v>
+      </c>
+      <c r="J120" t="s">
+        <v>38</v>
+      </c>
+      <c r="K120" t="s">
         <v>468</v>
       </c>
-      <c r="C120" s="2">
-        <v>44763</v>
-      </c>
-      <c r="D120" t="s">
-        <v>24</v>
-      </c>
-      <c r="E120" t="s">
-        <v>469</v>
-      </c>
-      <c r="F120" t="s">
-        <v>441</v>
-      </c>
-      <c r="G120" t="s">
-        <v>470</v>
-      </c>
-      <c r="H120" s="2">
-        <v>46266</v>
-      </c>
-      <c r="I120" s="3">
-        <v>7</v>
-      </c>
-      <c r="J120" t="s">
-        <v>271</v>
-      </c>
-      <c r="K120" t="s">
-        <v>471</v>
-      </c>
       <c r="L120" s="2">
-        <v>45574</v>
+        <v>45993</v>
       </c>
       <c r="M120" s="3">
-        <v>811</v>
-      </c>
-      <c r="O120" t="s">
-        <v>365</v>
-      </c>
-      <c r="P120" s="2">
-        <v>46313</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>69</v>
-      </c>
-      <c r="R120" s="2">
-        <v>46073</v>
+        <v>7332</v>
       </c>
       <c r="S120" s="2">
-        <v>45218</v>
-      </c>
-      <c r="T120" s="3"/>
-      <c r="U120" s="3">
-        <v>40</v>
-      </c>
+        <v>46540</v>
+      </c>
+      <c r="T120" s="3">
+        <v>265</v>
+      </c>
+      <c r="U120" s="3"/>
       <c r="V120" s="4">
-        <v>10934411.34</v>
+        <v>9032000</v>
       </c>
     </row>
     <row r="121" spans="1:22">
       <c r="A121" t="s">
-        <v>26</v>
+        <v>231</v>
       </c>
       <c r="B121" t="s">
+        <v>469</v>
+      </c>
+      <c r="C121" s="2">
+        <v>45560</v>
+      </c>
+      <c r="D121" t="s">
+        <v>24</v>
+      </c>
+      <c r="E121" t="s">
+        <v>470</v>
+      </c>
+      <c r="F121" t="s">
+        <v>231</v>
+      </c>
+      <c r="G121" t="s">
+        <v>471</v>
+      </c>
+      <c r="H121" s="2">
+        <v>45797</v>
+      </c>
+      <c r="I121" s="3">
+        <v>478</v>
+      </c>
+      <c r="J121" t="s">
+        <v>59</v>
+      </c>
+      <c r="K121" t="s">
         <v>472</v>
       </c>
-      <c r="C121" s="2">
-        <v>45014</v>
-      </c>
-      <c r="D121" t="s">
-        <v>44</v>
-      </c>
-      <c r="E121" t="s">
-        <v>473</v>
-      </c>
-      <c r="F121" t="s">
-        <v>26</v>
-      </c>
-      <c r="G121" t="s">
-        <v>372</v>
-      </c>
-      <c r="H121" s="2">
-        <v>46219</v>
-      </c>
-      <c r="I121" s="3">
-        <v>54</v>
-      </c>
-      <c r="J121" t="s">
-        <v>52</v>
-      </c>
-      <c r="K121" t="s">
-        <v>474</v>
-      </c>
-      <c r="L121" s="2">
-        <v>45148</v>
-      </c>
-      <c r="M121" s="3">
-        <v>134</v>
-      </c>
-      <c r="O121" t="s">
-        <v>365</v>
-      </c>
-      <c r="P121" s="2">
-        <v>46609</v>
-      </c>
+      <c r="M121" s="3"/>
       <c r="S121" s="2">
-        <v>45518</v>
-      </c>
-      <c r="T121" s="3"/>
-      <c r="U121" s="3">
-        <v>336</v>
-      </c>
+        <v>46523</v>
+      </c>
+      <c r="T121" s="3">
+        <v>248</v>
+      </c>
+      <c r="U121" s="3"/>
       <c r="V121" s="4">
-        <v>17946403.739999998</v>
+        <v>9152353</v>
       </c>
     </row>
     <row r="122" spans="1:22">
       <c r="A122" t="s">
+        <v>49</v>
+      </c>
+      <c r="B122" t="s">
+        <v>473</v>
+      </c>
+      <c r="C122" s="2">
+        <v>44763</v>
+      </c>
+      <c r="D122" t="s">
+        <v>24</v>
+      </c>
+      <c r="E122" t="s">
+        <v>474</v>
+      </c>
+      <c r="F122" t="s">
+        <v>446</v>
+      </c>
+      <c r="G122" t="s">
         <v>475</v>
       </c>
-      <c r="B122" t="s">
+      <c r="H122" s="2">
+        <v>46266</v>
+      </c>
+      <c r="I122" s="3">
+        <v>9</v>
+      </c>
+      <c r="J122" t="s">
+        <v>276</v>
+      </c>
+      <c r="K122" t="s">
         <v>476</v>
       </c>
-      <c r="C122" s="2">
-        <v>45666</v>
-      </c>
-      <c r="D122" t="s">
-        <v>44</v>
-      </c>
-      <c r="E122" t="s">
-        <v>477</v>
-      </c>
-      <c r="F122" t="s">
-        <v>444</v>
-      </c>
-      <c r="G122" t="s">
-        <v>478</v>
-      </c>
-      <c r="H122" s="2">
-        <v>46174</v>
-      </c>
-      <c r="I122" s="3">
-        <v>99</v>
-      </c>
-      <c r="J122" t="s">
-        <v>52</v>
-      </c>
-      <c r="M122" s="3"/>
+      <c r="L122" s="2">
+        <v>45574</v>
+      </c>
+      <c r="M122" s="3">
+        <v>811</v>
+      </c>
+      <c r="O122" t="s">
+        <v>371</v>
+      </c>
+      <c r="P122" s="2">
+        <v>46313</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>76</v>
+      </c>
+      <c r="R122" s="2">
+        <v>46073</v>
+      </c>
+      <c r="S122" s="2">
+        <v>45218</v>
+      </c>
       <c r="T122" s="3"/>
-      <c r="U122" s="3"/>
+      <c r="U122" s="3">
+        <v>38</v>
+      </c>
       <c r="V122" s="4">
-        <v>31106553.600000001</v>
+        <v>10934411.34</v>
       </c>
     </row>
     <row r="123" spans="1:22">
       <c r="A123" t="s">
-        <v>444</v>
+        <v>26</v>
       </c>
       <c r="B123" t="s">
+        <v>477</v>
+      </c>
+      <c r="C123" s="2">
+        <v>45014</v>
+      </c>
+      <c r="D123" t="s">
+        <v>51</v>
+      </c>
+      <c r="E123" t="s">
+        <v>478</v>
+      </c>
+      <c r="F123" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" t="s">
+        <v>378</v>
+      </c>
+      <c r="H123" s="2">
+        <v>46219</v>
+      </c>
+      <c r="I123" s="3">
+        <v>56</v>
+      </c>
+      <c r="J123" t="s">
+        <v>59</v>
+      </c>
+      <c r="K123" t="s">
         <v>479</v>
       </c>
-      <c r="C123" s="2">
-        <v>45250</v>
-      </c>
-      <c r="D123" t="s">
-        <v>35</v>
-      </c>
-      <c r="E123" t="s">
-        <v>480</v>
-      </c>
-      <c r="F123" t="s">
-        <v>444</v>
-      </c>
-      <c r="G123" t="s">
-        <v>481</v>
-      </c>
-      <c r="H123" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I123" s="3">
-        <v>873</v>
-      </c>
-      <c r="J123" t="s">
-        <v>52</v>
-      </c>
-      <c r="K123" t="s">
-        <v>482</v>
-      </c>
       <c r="L123" s="2">
-        <v>45401</v>
+        <v>45148</v>
       </c>
       <c r="M123" s="3">
-        <v>151</v>
+        <v>134</v>
+      </c>
+      <c r="O123" t="s">
+        <v>371</v>
+      </c>
+      <c r="P123" s="2">
+        <v>46609</v>
       </c>
       <c r="S123" s="2">
-        <v>47227</v>
-      </c>
-      <c r="T123" s="3">
-        <v>954</v>
-      </c>
-      <c r="U123" s="3"/>
+        <v>45518</v>
+      </c>
+      <c r="T123" s="3"/>
+      <c r="U123" s="3">
+        <v>334</v>
+      </c>
       <c r="V123" s="4">
-        <v>41522909.280000001</v>
+        <v>17946403.739999998</v>
       </c>
     </row>
     <row r="124" spans="1:22">
       <c r="A124" t="s">
-        <v>42</v>
+        <v>480</v>
       </c>
       <c r="B124" t="s">
+        <v>481</v>
+      </c>
+      <c r="C124" s="2">
+        <v>45666</v>
+      </c>
+      <c r="D124" t="s">
+        <v>51</v>
+      </c>
+      <c r="E124" t="s">
+        <v>482</v>
+      </c>
+      <c r="F124" t="s">
+        <v>449</v>
+      </c>
+      <c r="G124" t="s">
         <v>483</v>
       </c>
-      <c r="C124" s="2">
-        <v>44238</v>
-      </c>
-      <c r="D124" t="s">
-        <v>24</v>
-      </c>
-      <c r="E124" t="s">
-        <v>484</v>
-      </c>
-      <c r="F124" t="s">
-        <v>66</v>
-      </c>
-      <c r="G124" t="s">
-        <v>485</v>
-      </c>
       <c r="H124" s="2">
-        <v>46211</v>
+        <v>46174</v>
       </c>
       <c r="I124" s="3">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="J124" t="s">
-        <v>52</v>
-      </c>
-      <c r="K124" t="s">
-        <v>486</v>
-      </c>
-      <c r="L124" s="2">
-        <v>44969</v>
-      </c>
-      <c r="M124" s="3">
-        <v>731</v>
-      </c>
-      <c r="O124" t="s">
-        <v>487</v>
-      </c>
-      <c r="P124" s="2">
-        <v>46798</v>
-      </c>
-      <c r="S124" s="2">
-        <v>45886</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="M124" s="3"/>
       <c r="T124" s="3"/>
-      <c r="U124" s="3">
-        <v>525</v>
-      </c>
+      <c r="U124" s="3"/>
       <c r="V124" s="4">
-        <v>41936400</v>
+        <v>31106553.600000001</v>
       </c>
     </row>
     <row r="125" spans="1:22">
       <c r="A125" t="s">
-        <v>42</v>
+        <v>449</v>
       </c>
       <c r="B125" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C125" s="2">
-        <v>45607</v>
+        <v>45250</v>
       </c>
       <c r="D125" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F125" t="s">
-        <v>490</v>
+        <v>449</v>
       </c>
       <c r="G125" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="H125" s="2">
-        <v>45798</v>
+        <v>45400</v>
       </c>
       <c r="I125" s="3">
-        <v>475</v>
+        <v>875</v>
       </c>
       <c r="J125" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K125" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="L125" s="2">
-        <v>45798</v>
+        <v>45401</v>
       </c>
       <c r="M125" s="3">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="S125" s="2">
-        <v>46712</v>
+        <v>47227</v>
       </c>
       <c r="T125" s="3">
-        <v>439</v>
+        <v>952</v>
       </c>
       <c r="U125" s="3"/>
       <c r="V125" s="4">
-        <v>50963796</v>
+        <v>41522909.280000001</v>
       </c>
     </row>
     <row r="126" spans="1:22">
       <c r="A126" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B126" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C126" s="2">
-        <v>45664</v>
+        <v>44238</v>
       </c>
       <c r="D126" t="s">
         <v>24</v>
       </c>
       <c r="E126" t="s">
+        <v>489</v>
+      </c>
+      <c r="F126" t="s">
+        <v>73</v>
+      </c>
+      <c r="G126" t="s">
+        <v>490</v>
+      </c>
+      <c r="H126" s="2">
+        <v>46211</v>
+      </c>
+      <c r="I126" s="3">
+        <v>64</v>
+      </c>
+      <c r="J126" t="s">
+        <v>59</v>
+      </c>
+      <c r="K126" t="s">
+        <v>491</v>
+      </c>
+      <c r="L126" s="2">
+        <v>44969</v>
+      </c>
+      <c r="M126" s="3">
+        <v>731</v>
+      </c>
+      <c r="O126" t="s">
+        <v>492</v>
+      </c>
+      <c r="P126" s="2">
+        <v>46798</v>
+      </c>
+      <c r="S126" s="2">
+        <v>45886</v>
+      </c>
+      <c r="T126" s="3"/>
+      <c r="U126" s="3">
+        <v>523</v>
+      </c>
+      <c r="V126" s="4">
+        <v>41936400</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22">
+      <c r="A127" t="s">
+        <v>49</v>
+      </c>
+      <c r="B127" t="s">
+        <v>493</v>
+      </c>
+      <c r="C127" s="2">
+        <v>45607</v>
+      </c>
+      <c r="D127" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127" t="s">
         <v>494</v>
       </c>
-      <c r="F126" t="s">
-        <v>224</v>
-      </c>
-      <c r="G126" t="s">
+      <c r="F127" t="s">
+        <v>446</v>
+      </c>
+      <c r="G127" t="s">
         <v>495</v>
       </c>
-      <c r="H126" s="2">
+      <c r="H127" s="2">
+        <v>46274</v>
+      </c>
+      <c r="I127" s="3">
+        <v>1</v>
+      </c>
+      <c r="J127" t="s">
+        <v>276</v>
+      </c>
+      <c r="K127" t="s">
+        <v>496</v>
+      </c>
+      <c r="L127" s="2">
+        <v>45798</v>
+      </c>
+      <c r="M127" s="3">
+        <v>191</v>
+      </c>
+      <c r="S127" s="2">
+        <v>46712</v>
+      </c>
+      <c r="T127" s="3">
+        <v>437</v>
+      </c>
+      <c r="U127" s="3"/>
+      <c r="V127" s="4">
+        <v>50963796</v>
+      </c>
+    </row>
+    <row r="128" spans="1:22">
+      <c r="A128" t="s">
+        <v>49</v>
+      </c>
+      <c r="B128" t="s">
+        <v>497</v>
+      </c>
+      <c r="C128" s="2">
+        <v>45664</v>
+      </c>
+      <c r="D128" t="s">
+        <v>24</v>
+      </c>
+      <c r="E128" t="s">
+        <v>498</v>
+      </c>
+      <c r="F128" t="s">
+        <v>231</v>
+      </c>
+      <c r="G128" t="s">
+        <v>499</v>
+      </c>
+      <c r="H128" s="2">
         <v>45958</v>
       </c>
-      <c r="I126" s="3">
-        <v>315</v>
-      </c>
-      <c r="J126" t="s">
+      <c r="I128" s="3">
+        <v>317</v>
+      </c>
+      <c r="J128" t="s">
         <v>28</v>
       </c>
-      <c r="M126" s="3"/>
-      <c r="T126" s="3"/>
-      <c r="U126" s="3"/>
-      <c r="V126" s="4">
+      <c r="M128" s="3"/>
+      <c r="T128" s="3"/>
+      <c r="U128" s="3"/>
+      <c r="V128" s="4">
         <v>253382919</v>
       </c>
     </row>

--- a/datagrid.xlsx
+++ b/datagrid.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maurofilho\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A22586-CD10-4732-80EE-9B660C068DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20FD4C1-5078-459B-8E5F-C7DA8B21711F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="504">
   <si>
     <t>Departamento</t>
   </si>
@@ -160,7 +160,10 @@
     <t>SISLOG  122354 PACS</t>
   </si>
   <si>
-    <t>NOVA CONTRATAÇÃO. AGUARDANDO RETORNO GESAD PARA QUANTITATIVOS.</t>
+    <t>GESAD SUTIS</t>
+  </si>
+  <si>
+    <t>PEDIMOS ORÇAMENTOS À DIANA. ETP EM ELABORAÇÃO.</t>
   </si>
   <si>
     <t>Aquisição</t>
@@ -172,7 +175,10 @@
     <t>SISLOG 122408 Inscrições - XXI CBIS 2026</t>
   </si>
   <si>
-    <t>SOLICITADA ASSINATURAS ETP DIANA E TIBIRIÇA</t>
+    <t>GEFIN</t>
+  </si>
+  <si>
+    <t>Ato que autoriza a Contratação Direta. Mais um inscrito terá que desistir</t>
   </si>
   <si>
     <t>GETEC</t>
@@ -861,10 +867,10 @@
     <t>202600005026802</t>
   </si>
   <si>
-    <t>SISLOG 122001 - Aquisição de Workstations</t>
-  </si>
-  <si>
-    <t>GELIC  CACTIC</t>
+    <t>SISLOG 122001 - Aquisição de Workstations PROCESSO COMSET 202600010028095</t>
+  </si>
+  <si>
+    <t>GELIC</t>
   </si>
   <si>
     <t>PARA CONTINUIDADE</t>
@@ -879,6 +885,9 @@
     <t>Doação de 105 desktops para o CISCENO</t>
   </si>
   <si>
+    <t>PARA CONTINUIDADE. PARADO POR PERIODO ELEITORAL</t>
+  </si>
+  <si>
     <t>Em Renovação</t>
   </si>
   <si>
@@ -888,7 +897,7 @@
     <t>SISLOG 121437 KIT MOUSE E TECLADO COM FIO</t>
   </si>
   <si>
-    <t>para que realize a análise técnica da minuta de contrato.</t>
+    <t>Parecer Técnico</t>
   </si>
   <si>
     <t>GEIN</t>
@@ -975,9 +984,6 @@
     <t>SISLOG 117278 - Aquisição de kits de Mouse e Teclado com e sem fio</t>
   </si>
   <si>
-    <t>GELIC</t>
-  </si>
-  <si>
     <t>houve a apresentação de propostas, as quais foram todas desclassificadas e/ou os licitantes inabilitados, inviabilizando a adjudicação do objeto, declaro o certame FRACASSADO.</t>
   </si>
   <si>
@@ -1011,7 +1017,7 @@
     <t>SISLOG 121388 GALERA APP</t>
   </si>
   <si>
-    <t>Envio para elaboração da Portaria e do Termo de Referência</t>
+    <t>PARECER FAVORÁVEL</t>
   </si>
   <si>
     <t>202500005030582</t>
@@ -1074,16 +1080,19 @@
     <t>SISLOG 122416 - Adesão À ARP 010/2025 MGI. 300 monitores 24"</t>
   </si>
   <si>
-    <t>GCC GCC/SEAD</t>
-  </si>
-  <si>
-    <t>GCC PORTA4RIA. AGUARDANDO OFÍCIO AUTORIZAÇÃO SEAD</t>
+    <t>PROCSET</t>
+  </si>
+  <si>
+    <t>PARECER</t>
   </si>
   <si>
     <t>202600005026702</t>
   </si>
   <si>
     <t>SISLOG 121994- Aquisição Webcam e Headset</t>
+  </si>
+  <si>
+    <t>Para atendimento da Recomendação de Diligência (540324)</t>
   </si>
   <si>
     <t>202500010044120</t>
@@ -1199,7 +1208,10 @@
     <t xml:space="preserve"> FORNECEDOR  TECNISYS.Contratação Especialista em BigData</t>
   </si>
   <si>
-    <t>AGUARDANDO DEFINIÇÃO DE QUANTITATIVOS PARA NOVO ETP</t>
+    <t>GESAD DEOF</t>
+  </si>
+  <si>
+    <t>Encaminhado ofício ao fornecedor. Ajuste conforme Anulação revisão de saldo (96879517)valor R$ 24.108,38</t>
   </si>
   <si>
     <t>13/2023</t>
@@ -1220,7 +1232,7 @@
     <t>SISLOG 122292 - Adesão À ARP 020/2026. 100 notebooks</t>
   </si>
   <si>
-    <t>FALTA OFÍCIO FORNECEDOR. GEPO AGUARDANDO CREDITO SUPLEMENTAR</t>
+    <t>PARA PROVIDÊNCIAS</t>
   </si>
   <si>
     <t>202300005025650</t>
@@ -1373,7 +1385,12 @@
     <t>SISLOG 121821 ARP nº 001/2026 do TJ-GO - 500 micromputadores</t>
   </si>
   <si>
-    <t>CACTIC FAVORÁVEL. AGUARDANDO CREDITO SUPLEMENTAR</t>
+    <t>GELIC SUTIS</t>
+  </si>
+  <si>
+    <t>a) obtenção e juntada aos autos de documento formal de ratificação/revalidação da anuência da empresa fornecedora registrada (Positivo Tecnologia S.A.), tendo em vista que a anuência constante dos autos teve validade restrita a 30 dias e expirou em 05/09/2026 (subitem 3.2);
+b) juntada do comprovante de publicação da Ata de Registro de Preços nº 001/2026 – TJ-GO, para confirmação do termo inicial e do prazo de vigência, considerando que a Cláusula Quarta prevê sua contagem a partir da publicação (subitem 3.3);
+c) juntada dos documentos faltantes, atualização e regularização prévia de todas as certidões habilitatórias vencidas (item 11);</t>
   </si>
   <si>
     <t>202600010062463</t>
@@ -1391,10 +1408,7 @@
     <t>SISLOG 113930 -GLOBAL TI Contratação de solução de Inteligência Artificial (IA). Processo 202500010079078 paralelo CCONT</t>
   </si>
   <si>
-    <t>PROCSET</t>
-  </si>
-  <si>
-    <t>Aguardando Parecer Jurídico</t>
+    <t>Aditivo formalizado e publicado. Encaminhem-se o autos à GETEC/SUTIS, via SUBIPEI, para conhecimento e providências a seu cargo.</t>
   </si>
   <si>
     <t>93/2025</t>
@@ -1479,7 +1493,7 @@
     <t>FORNECEDOR MEMORA. Contratação de mão de obra de infra e banco.</t>
   </si>
   <si>
-    <t>para análise e manifestação, bem como para posterior remessa à Procuradoria-Geral do Estado para apreciação conclusiva, haja vista que o valor supera R$ 10.000.000,00</t>
+    <t>Liberada assinatura externa para o usuário JAIRO MARTINS DE CARVALHO (jairo@memora.com.br) no documento 96997338 (Aditivo) até 20/10/2026</t>
   </si>
   <si>
     <t>83/2023</t>
@@ -1539,7 +1553,7 @@
     <t>Sislog: 110233 OMNICHANNELL e CALLCENTER - Processo SEI Paralelo para Contratos- 202500010021689</t>
   </si>
   <si>
-    <t>AGUARDANDO PARECER PARA ENVIO A PGE</t>
+    <t>para continuidade do feito</t>
   </si>
   <si>
     <t>32/2025</t>
@@ -1918,6 +1932,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V128"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
@@ -2013,7 +2035,7 @@
         <v>46112</v>
       </c>
       <c r="I2" s="3">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -2049,7 +2071,7 @@
         <v>45621</v>
       </c>
       <c r="I3" s="3">
-        <v>654</v>
+        <v>688</v>
       </c>
       <c r="J3" t="s">
         <v>28</v>
@@ -2085,7 +2107,7 @@
         <v>45407</v>
       </c>
       <c r="I4" s="3">
-        <v>868</v>
+        <v>902</v>
       </c>
       <c r="J4" t="s">
         <v>38</v>
@@ -2121,7 +2143,7 @@
         <v>45806</v>
       </c>
       <c r="I5" s="3">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="J5" t="s">
         <v>28</v>
@@ -2148,19 +2170,19 @@
         <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H6" s="2">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="I6" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M6" s="3"/>
       <c r="T6" s="3"/>
@@ -2172,7 +2194,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2">
         <v>46267</v>
@@ -2181,22 +2203,22 @@
         <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="I7" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M7" s="3"/>
       <c r="T7" s="3"/>
@@ -2205,41 +2227,41 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2">
         <v>43091</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H8" s="2">
         <v>45141</v>
       </c>
       <c r="I8" s="3">
-        <v>1134</v>
+        <v>1168</v>
       </c>
       <c r="J8" t="s">
         <v>38</v>
       </c>
       <c r="K8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M8" s="3"/>
       <c r="O8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P8" s="2">
         <v>45336</v>
@@ -2253,10 +2275,10 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" s="2">
         <v>43516</v>
@@ -2265,25 +2287,25 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H9" s="2">
         <v>45140</v>
       </c>
       <c r="I9" s="3">
-        <v>1135</v>
+        <v>1169</v>
       </c>
       <c r="J9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L9" s="2">
         <v>44047</v>
@@ -2292,7 +2314,7 @@
         <v>531</v>
       </c>
       <c r="O9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P9" s="2">
         <v>46023</v>
@@ -2306,10 +2328,10 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2">
         <v>43770</v>
@@ -2318,25 +2340,25 @@
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H10" s="2">
         <v>45198</v>
       </c>
       <c r="I10" s="3">
-        <v>1077</v>
+        <v>1111</v>
       </c>
       <c r="J10" t="s">
         <v>38</v>
       </c>
       <c r="K10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L10" s="2">
         <v>44176</v>
@@ -2345,7 +2367,7 @@
         <v>406</v>
       </c>
       <c r="O10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P10" s="2">
         <v>45646</v>
@@ -2359,10 +2381,10 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11" s="2">
         <v>43902</v>
@@ -2371,29 +2393,29 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2">
         <v>45702</v>
       </c>
       <c r="I11" s="3">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="J11" t="s">
         <v>28</v>
       </c>
       <c r="K11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M11" s="3"/>
       <c r="O11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P11" s="2">
         <v>45794</v>
@@ -2407,10 +2429,10 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C12" s="2">
         <v>44176</v>
@@ -2419,29 +2441,29 @@
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2">
         <v>45372</v>
       </c>
       <c r="I12" s="3">
-        <v>903</v>
+        <v>937</v>
       </c>
       <c r="J12" t="s">
         <v>38</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M12" s="3"/>
       <c r="O12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P12" s="2">
         <v>45505</v>
@@ -2455,41 +2477,41 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2">
         <v>44181</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H13" s="2">
         <v>45453</v>
       </c>
       <c r="I13" s="3">
-        <v>822</v>
+        <v>856</v>
       </c>
       <c r="J13" t="s">
         <v>28</v>
       </c>
       <c r="K13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M13" s="3"/>
       <c r="O13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P13" s="2">
         <v>45499</v>
@@ -2503,37 +2525,37 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" s="2">
         <v>44448</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H14" s="2">
         <v>44980</v>
       </c>
       <c r="I14" s="3">
-        <v>1295</v>
+        <v>1329</v>
       </c>
       <c r="J14" t="s">
         <v>38</v>
       </c>
       <c r="K14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L14" s="2">
         <v>44727</v>
@@ -2550,10 +2572,10 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C15" s="2">
         <v>44628</v>
@@ -2562,25 +2584,25 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H15" s="2">
         <v>45107</v>
       </c>
       <c r="I15" s="3">
-        <v>1168</v>
+        <v>1202</v>
       </c>
       <c r="J15" t="s">
         <v>38</v>
       </c>
       <c r="K15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L15" s="2">
         <v>45040</v>
@@ -2597,10 +2619,10 @@
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C16" s="2">
         <v>44628</v>
@@ -2609,25 +2631,25 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2">
         <v>45154</v>
       </c>
       <c r="I16" s="3">
-        <v>1121</v>
+        <v>1155</v>
       </c>
       <c r="J16" t="s">
         <v>38</v>
       </c>
       <c r="K16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L16" s="2">
         <v>45040</v>
@@ -2644,10 +2666,10 @@
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C17" s="2">
         <v>44628</v>
@@ -2656,25 +2678,25 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2">
         <v>45189</v>
       </c>
       <c r="I17" s="3">
-        <v>1086</v>
+        <v>1120</v>
       </c>
       <c r="J17" t="s">
         <v>38</v>
       </c>
       <c r="K17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L17" s="2">
         <v>45040</v>
@@ -2691,10 +2713,10 @@
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C18" s="2">
         <v>44628</v>
@@ -2703,25 +2725,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H18" s="2">
         <v>45145</v>
       </c>
       <c r="I18" s="3">
-        <v>1130</v>
+        <v>1164</v>
       </c>
       <c r="J18" t="s">
         <v>38</v>
       </c>
       <c r="K18" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L18" s="2">
         <v>45040</v>
@@ -2738,10 +2760,10 @@
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19" s="2">
         <v>44628</v>
@@ -2750,25 +2772,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2">
         <v>45107</v>
       </c>
       <c r="I19" s="3">
-        <v>1168</v>
+        <v>1202</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
       </c>
       <c r="K19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L19" s="2">
         <v>45040</v>
@@ -2785,10 +2807,10 @@
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C20" s="2">
         <v>44628</v>
@@ -2797,25 +2819,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H20" s="2">
         <v>45208</v>
       </c>
       <c r="I20" s="3">
-        <v>1067</v>
+        <v>1101</v>
       </c>
       <c r="J20" t="s">
         <v>38</v>
       </c>
       <c r="K20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L20" s="2">
         <v>45040</v>
@@ -2832,10 +2854,10 @@
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C21" s="2">
         <v>44628</v>
@@ -2844,25 +2866,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H21" s="2">
         <v>45107</v>
       </c>
       <c r="I21" s="3">
-        <v>1168</v>
+        <v>1202</v>
       </c>
       <c r="J21" t="s">
         <v>38</v>
       </c>
       <c r="K21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L21" s="2">
         <v>45040</v>
@@ -2879,10 +2901,10 @@
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C22" s="2">
         <v>44713</v>
@@ -2891,19 +2913,19 @@
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H22" s="2">
         <v>45034</v>
       </c>
       <c r="I22" s="3">
-        <v>1241</v>
+        <v>1275</v>
       </c>
       <c r="J22" t="s">
         <v>28</v>
@@ -2915,10 +2937,10 @@
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C23" s="2">
         <v>44715</v>
@@ -2927,25 +2949,25 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H23" s="2">
         <v>45152</v>
       </c>
       <c r="I23" s="3">
-        <v>1123</v>
+        <v>1157</v>
       </c>
       <c r="J23" t="s">
         <v>38</v>
       </c>
       <c r="K23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L23" s="2">
         <v>45112</v>
@@ -2962,37 +2984,37 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C24" s="2">
         <v>44721</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E24" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H24" s="2">
         <v>44908</v>
       </c>
       <c r="I24" s="3">
-        <v>1367</v>
+        <v>1401</v>
       </c>
       <c r="J24" t="s">
         <v>38</v>
       </c>
       <c r="K24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L24" s="2">
         <v>44893</v>
@@ -3009,41 +3031,41 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C25" s="2">
         <v>44741</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H25" s="2">
         <v>45007</v>
       </c>
       <c r="I25" s="3">
-        <v>1268</v>
+        <v>1302</v>
       </c>
       <c r="J25" t="s">
         <v>38</v>
       </c>
       <c r="K25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S25" s="2">
         <v>45220</v>
@@ -3054,10 +3076,10 @@
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C26" s="2">
         <v>44883</v>
@@ -3066,19 +3088,19 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H26" s="2">
         <v>45202</v>
       </c>
       <c r="I26" s="3">
-        <v>1073</v>
+        <v>1107</v>
       </c>
       <c r="J26" t="s">
         <v>28</v>
@@ -3090,10 +3112,10 @@
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C27" s="2">
         <v>44911</v>
@@ -3102,25 +3124,25 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H27" s="2">
         <v>45226</v>
       </c>
       <c r="I27" s="3">
-        <v>1049</v>
+        <v>1083</v>
       </c>
       <c r="J27" t="s">
         <v>38</v>
       </c>
       <c r="K27" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L27" s="2">
         <v>45217</v>
@@ -3137,10 +3159,10 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C28" s="2">
         <v>44911</v>
@@ -3149,25 +3171,25 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H28" s="2">
         <v>45224</v>
       </c>
       <c r="I28" s="3">
-        <v>1051</v>
+        <v>1085</v>
       </c>
       <c r="J28" t="s">
         <v>38</v>
       </c>
       <c r="K28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L28" s="2">
         <v>45217</v>
@@ -3184,10 +3206,10 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C29" s="2">
         <v>45229</v>
@@ -3196,25 +3218,25 @@
         <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H29" s="2">
         <v>45481</v>
       </c>
       <c r="I29" s="3">
-        <v>794</v>
+        <v>828</v>
       </c>
       <c r="J29" t="s">
         <v>38</v>
       </c>
       <c r="K29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M29" s="3"/>
       <c r="S29" s="2">
@@ -3226,37 +3248,37 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C30" s="2">
         <v>44949</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H30" s="2">
         <v>45134</v>
       </c>
       <c r="I30" s="3">
-        <v>1141</v>
+        <v>1175</v>
       </c>
       <c r="J30" t="s">
         <v>38</v>
       </c>
       <c r="K30" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L30" s="2">
         <v>45112</v>
@@ -3273,31 +3295,31 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C31" s="2">
         <v>44988</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H31" s="2">
         <v>45043</v>
       </c>
       <c r="I31" s="3">
-        <v>1232</v>
+        <v>1266</v>
       </c>
       <c r="J31" t="s">
         <v>28</v>
@@ -3309,10 +3331,10 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C32" s="2">
         <v>45015</v>
@@ -3321,19 +3343,19 @@
         <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G32" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H32" s="2">
         <v>45395</v>
       </c>
       <c r="I32" s="3">
-        <v>880</v>
+        <v>914</v>
       </c>
       <c r="J32" t="s">
         <v>28</v>
@@ -3345,10 +3367,10 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C33" s="2">
         <v>45027</v>
@@ -3357,19 +3379,19 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H33" s="2">
         <v>45251</v>
       </c>
       <c r="I33" s="3">
-        <v>1024</v>
+        <v>1058</v>
       </c>
       <c r="J33" t="s">
         <v>28</v>
@@ -3381,37 +3403,37 @@
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C34" s="2">
         <v>45030</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G34" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H34" s="2">
         <v>45175</v>
       </c>
       <c r="I34" s="3">
-        <v>1100</v>
+        <v>1134</v>
       </c>
       <c r="J34" t="s">
         <v>38</v>
       </c>
       <c r="K34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L34" s="2">
         <v>45161</v>
@@ -3428,10 +3450,10 @@
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C35" s="2">
         <v>45056</v>
@@ -3440,25 +3462,25 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H35" s="2">
         <v>45400</v>
       </c>
       <c r="I35" s="3">
-        <v>875</v>
+        <v>909</v>
       </c>
       <c r="J35" t="s">
         <v>38</v>
       </c>
       <c r="K35" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L35" s="2">
         <v>45400</v>
@@ -3475,31 +3497,31 @@
     </row>
     <row r="36" spans="1:22">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C36" s="2">
         <v>45056</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F36" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G36" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H36" s="2">
         <v>45252</v>
       </c>
       <c r="I36" s="3">
-        <v>1023</v>
+        <v>1057</v>
       </c>
       <c r="J36" t="s">
         <v>38</v>
@@ -3511,10 +3533,10 @@
     </row>
     <row r="37" spans="1:22">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C37" s="2">
         <v>45069</v>
@@ -3523,19 +3545,19 @@
         <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H37" s="2">
         <v>45267</v>
       </c>
       <c r="I37" s="3">
-        <v>1008</v>
+        <v>1042</v>
       </c>
       <c r="J37" t="s">
         <v>28</v>
@@ -3547,10 +3569,10 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C38" s="2">
         <v>45063</v>
@@ -3559,19 +3581,19 @@
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H38" s="2">
         <v>45404</v>
       </c>
       <c r="I38" s="3">
-        <v>871</v>
+        <v>905</v>
       </c>
       <c r="J38" t="s">
         <v>28</v>
@@ -3583,37 +3605,37 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C39" s="2">
         <v>45063</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G39" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H39" s="2">
         <v>45236</v>
       </c>
       <c r="I39" s="3">
-        <v>1039</v>
+        <v>1073</v>
       </c>
       <c r="J39" t="s">
         <v>38</v>
       </c>
       <c r="K39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L39" s="2">
         <v>45236</v>
@@ -3630,10 +3652,10 @@
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C40" s="2">
         <v>45065</v>
@@ -3642,19 +3664,19 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F40" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G40" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H40" s="2">
         <v>45209</v>
       </c>
       <c r="I40" s="3">
-        <v>1066</v>
+        <v>1100</v>
       </c>
       <c r="J40" t="s">
         <v>28</v>
@@ -3666,10 +3688,10 @@
     </row>
     <row r="41" spans="1:22">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C41" s="2">
         <v>45092</v>
@@ -3678,25 +3700,25 @@
         <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F41" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G41" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H41" s="2">
         <v>45573</v>
       </c>
       <c r="I41" s="3">
-        <v>702</v>
+        <v>736</v>
       </c>
       <c r="J41" t="s">
         <v>38</v>
       </c>
       <c r="K41" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L41" s="2">
         <v>45569</v>
@@ -3705,7 +3727,7 @@
         <v>477</v>
       </c>
       <c r="O41" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S41" s="2">
         <v>45805</v>
@@ -3716,10 +3738,10 @@
     </row>
     <row r="42" spans="1:22">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C42" s="2">
         <v>45106</v>
@@ -3728,19 +3750,19 @@
         <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G42" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H42" s="2">
         <v>45306</v>
       </c>
       <c r="I42" s="3">
-        <v>969</v>
+        <v>1003</v>
       </c>
       <c r="J42" t="s">
         <v>28</v>
@@ -3752,37 +3774,37 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C43" s="2">
         <v>45128</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H43" s="2">
         <v>45264</v>
       </c>
       <c r="I43" s="3">
-        <v>1011</v>
+        <v>1045</v>
       </c>
       <c r="J43" t="s">
         <v>38</v>
       </c>
       <c r="K43" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L43" s="2">
         <v>45229</v>
@@ -3799,10 +3821,10 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C44" s="2">
         <v>45307</v>
@@ -3811,19 +3833,19 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G44" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H44" s="2">
         <v>45426</v>
       </c>
       <c r="I44" s="3">
-        <v>849</v>
+        <v>883</v>
       </c>
       <c r="J44" t="s">
         <v>28</v>
@@ -3835,10 +3857,10 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C45" s="2">
         <v>45359</v>
@@ -3847,19 +3869,19 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F45" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G45" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H45" s="2">
         <v>45359</v>
       </c>
       <c r="I45" s="3">
-        <v>916</v>
+        <v>950</v>
       </c>
       <c r="J45" t="s">
         <v>28</v>
@@ -3871,37 +3893,37 @@
     </row>
     <row r="46" spans="1:22">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C46" s="2">
         <v>45408</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H46" s="2">
         <v>45595</v>
       </c>
       <c r="I46" s="3">
-        <v>680</v>
+        <v>714</v>
       </c>
       <c r="J46" t="s">
         <v>38</v>
       </c>
       <c r="K46" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L46" s="2">
         <v>45624</v>
@@ -3915,37 +3937,37 @@
     </row>
     <row r="47" spans="1:22">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C47" s="2">
         <v>45394</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E47" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G47" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H47" s="2">
         <v>45562</v>
       </c>
       <c r="I47" s="3">
-        <v>713</v>
+        <v>747</v>
       </c>
       <c r="J47" t="s">
         <v>38</v>
       </c>
       <c r="K47" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M47" s="3"/>
       <c r="S47" s="2">
@@ -3957,10 +3979,10 @@
     </row>
     <row r="48" spans="1:22">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C48" s="2">
         <v>45456</v>
@@ -3969,25 +3991,25 @@
         <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G48" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H48" s="2">
         <v>45488</v>
       </c>
       <c r="I48" s="3">
-        <v>787</v>
+        <v>821</v>
       </c>
       <c r="J48" t="s">
         <v>38</v>
       </c>
       <c r="K48" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M48" s="3"/>
       <c r="S48" s="2">
@@ -3999,37 +4021,37 @@
     </row>
     <row r="49" spans="1:22">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C49" s="2">
         <v>45395</v>
       </c>
       <c r="D49" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F49" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G49" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H49" s="2">
         <v>45552</v>
       </c>
       <c r="I49" s="3">
-        <v>723</v>
+        <v>757</v>
       </c>
       <c r="J49" t="s">
         <v>38</v>
       </c>
       <c r="K49" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L49" s="2">
         <v>45548</v>
@@ -4041,44 +4063,44 @@
         <v>47378</v>
       </c>
       <c r="T49" s="3">
-        <v>1103</v>
+        <v>1069</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C50" s="2">
         <v>45395</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G50" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H50" s="2">
         <v>45540</v>
       </c>
       <c r="I50" s="3">
-        <v>735</v>
+        <v>769</v>
       </c>
       <c r="J50" t="s">
         <v>38</v>
       </c>
       <c r="K50" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L50" s="2">
         <v>45530</v>
@@ -4087,7 +4109,7 @@
         <v>135</v>
       </c>
       <c r="N50" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="S50" s="2">
         <v>45720</v>
@@ -4098,37 +4120,37 @@
     </row>
     <row r="51" spans="1:22">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C51" s="2">
         <v>45395</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F51" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G51" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H51" s="2">
         <v>45566</v>
       </c>
       <c r="I51" s="3">
-        <v>709</v>
+        <v>743</v>
       </c>
       <c r="J51" t="s">
         <v>38</v>
       </c>
       <c r="K51" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L51" s="2">
         <v>45517</v>
@@ -4140,44 +4162,44 @@
         <v>47343</v>
       </c>
       <c r="T51" s="3">
-        <v>1068</v>
+        <v>1034</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="4"/>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C52" s="2">
         <v>45400</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E52" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H52" s="2">
         <v>45790</v>
       </c>
       <c r="I52" s="3">
-        <v>485</v>
+        <v>519</v>
       </c>
       <c r="J52" t="s">
         <v>28</v>
       </c>
       <c r="K52" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L52" s="2">
         <v>45580</v>
@@ -4191,10 +4213,10 @@
     </row>
     <row r="53" spans="1:22">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C53" s="2">
         <v>45553</v>
@@ -4203,19 +4225,19 @@
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F53" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G53" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H53" s="2">
         <v>45567</v>
       </c>
       <c r="I53" s="3">
-        <v>708</v>
+        <v>742</v>
       </c>
       <c r="J53" t="s">
         <v>28</v>
@@ -4227,31 +4249,31 @@
     </row>
     <row r="54" spans="1:22">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C54" s="2">
         <v>45516</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F54" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G54" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H54" s="2">
         <v>45590</v>
       </c>
       <c r="I54" s="3">
-        <v>685</v>
+        <v>719</v>
       </c>
       <c r="J54" t="s">
         <v>28</v>
@@ -4263,31 +4285,31 @@
     </row>
     <row r="55" spans="1:22">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C55" s="2">
         <v>45701</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E55" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F55" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G55" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H55" s="2">
         <v>45758</v>
       </c>
       <c r="I55" s="3">
-        <v>517</v>
+        <v>551</v>
       </c>
       <c r="J55" t="s">
         <v>28</v>
@@ -4299,10 +4321,10 @@
     </row>
     <row r="56" spans="1:22">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B56" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C56" s="2">
         <v>45308</v>
@@ -4311,25 +4333,25 @@
         <v>35</v>
       </c>
       <c r="E56" t="s">
+        <v>235</v>
+      </c>
+      <c r="F56" t="s">
         <v>233</v>
       </c>
-      <c r="F56" t="s">
-        <v>231</v>
-      </c>
       <c r="G56" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H56" s="2">
         <v>45454</v>
       </c>
       <c r="I56" s="3">
-        <v>821</v>
+        <v>855</v>
       </c>
       <c r="J56" t="s">
         <v>38</v>
       </c>
       <c r="K56" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L56" s="2">
         <v>45408</v>
@@ -4349,28 +4371,28 @@
         <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C57" s="2">
         <v>45051</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E57" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F57" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G57" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H57" s="2">
         <v>45573</v>
       </c>
       <c r="I57" s="3">
-        <v>702</v>
+        <v>736</v>
       </c>
       <c r="J57" t="s">
         <v>38</v>
@@ -4385,7 +4407,7 @@
         <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C58" s="2">
         <v>45016</v>
@@ -4394,19 +4416,19 @@
         <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F58" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G58" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H58" s="2">
         <v>45219</v>
       </c>
       <c r="I58" s="3">
-        <v>1056</v>
+        <v>1090</v>
       </c>
       <c r="J58" t="s">
         <v>28</v>
@@ -4421,7 +4443,7 @@
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C59" s="2">
         <v>45016</v>
@@ -4430,19 +4452,19 @@
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F59" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G59" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H59" s="2">
         <v>45315</v>
       </c>
       <c r="I59" s="3">
-        <v>960</v>
+        <v>994</v>
       </c>
       <c r="J59" t="s">
         <v>38</v>
@@ -4457,28 +4479,28 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C60" s="2">
         <v>45251</v>
       </c>
       <c r="D60" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E60" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
       </c>
       <c r="G60" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H60" s="2">
         <v>45299</v>
       </c>
       <c r="I60" s="3">
-        <v>976</v>
+        <v>1010</v>
       </c>
       <c r="J60" t="s">
         <v>28</v>
@@ -4493,28 +4515,28 @@
         <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C61" s="2">
         <v>45314</v>
       </c>
       <c r="D61" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E61" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F61" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G61" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H61" s="2">
         <v>45462</v>
       </c>
       <c r="I61" s="3">
-        <v>813</v>
+        <v>847</v>
       </c>
       <c r="J61" t="s">
         <v>38</v>
@@ -4529,7 +4551,7 @@
         <v>26</v>
       </c>
       <c r="B62" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C62" s="2">
         <v>45216</v>
@@ -4538,25 +4560,25 @@
         <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F62" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G62" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H62" s="2">
         <v>45538</v>
       </c>
       <c r="I62" s="3">
-        <v>737</v>
+        <v>771</v>
       </c>
       <c r="J62" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K62" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L62" s="2">
         <v>45475</v>
@@ -4568,7 +4590,7 @@
         <v>47301</v>
       </c>
       <c r="T62" s="3">
-        <v>1026</v>
+        <v>992</v>
       </c>
       <c r="U62" s="3"/>
       <c r="V62" s="4"/>
@@ -4578,7 +4600,7 @@
         <v>26</v>
       </c>
       <c r="B63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C63" s="2">
         <v>45742</v>
@@ -4587,19 +4609,19 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G63" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H63" s="2">
         <v>45847</v>
       </c>
       <c r="I63" s="3">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="J63" t="s">
         <v>28</v>
@@ -4614,28 +4636,28 @@
         <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C64" s="2">
         <v>45734</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E64" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
       </c>
       <c r="G64" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H64" s="2">
         <v>45839</v>
       </c>
       <c r="I64" s="3">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="J64" t="s">
         <v>28</v>
@@ -4650,7 +4672,7 @@
         <v>26</v>
       </c>
       <c r="B65" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C65" s="2">
         <v>46162</v>
@@ -4659,19 +4681,19 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H65" s="2">
         <v>46246</v>
       </c>
       <c r="I65" s="3">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J65" t="s">
         <v>28</v>
@@ -4686,7 +4708,7 @@
         <v>26</v>
       </c>
       <c r="B66" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C66" s="2">
         <v>46245</v>
@@ -4695,22 +4717,22 @@
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F66" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G66" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H66" s="2">
-        <v>46259</v>
+        <v>46304</v>
       </c>
       <c r="I66" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J66" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M66" s="3"/>
       <c r="T66" s="3"/>
@@ -4722,31 +4744,31 @@
         <v>26</v>
       </c>
       <c r="B67" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2">
         <v>46126</v>
       </c>
       <c r="D67" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E67" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F67" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="H67" s="2">
         <v>46182</v>
       </c>
       <c r="I67" s="3">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="J67" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M67" s="3"/>
       <c r="T67" s="3"/>
@@ -4758,7 +4780,7 @@
         <v>26</v>
       </c>
       <c r="B68" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C68" s="2">
         <v>46211</v>
@@ -4767,22 +4789,22 @@
         <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F68" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="G68" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H68" s="2">
-        <v>46267</v>
+        <v>46304</v>
       </c>
       <c r="I68" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J68" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M68" s="3"/>
       <c r="T68" s="3"/>
@@ -4793,10 +4815,10 @@
     </row>
     <row r="69" spans="1:22">
       <c r="A69" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B69" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C69" s="2">
         <v>46136</v>
@@ -4805,19 +4827,19 @@
         <v>35</v>
       </c>
       <c r="E69" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F69" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G69" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H69" s="2">
         <v>46156</v>
       </c>
       <c r="I69" s="3">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="J69" t="s">
         <v>38</v>
@@ -4831,10 +4853,10 @@
     </row>
     <row r="70" spans="1:22">
       <c r="A70" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C70" s="2">
         <v>46135</v>
@@ -4843,19 +4865,19 @@
         <v>35</v>
       </c>
       <c r="E70" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
       </c>
       <c r="G70" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H70" s="2">
         <v>46155</v>
       </c>
       <c r="I70" s="3">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="J70" t="s">
         <v>38</v>
@@ -4869,10 +4891,10 @@
     </row>
     <row r="71" spans="1:22">
       <c r="A71" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C71" s="2">
         <v>46136</v>
@@ -4881,19 +4903,19 @@
         <v>35</v>
       </c>
       <c r="E71" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
       </c>
       <c r="G71" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H71" s="2">
         <v>46157</v>
       </c>
       <c r="I71" s="3">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="J71" t="s">
         <v>38</v>
@@ -4907,10 +4929,10 @@
     </row>
     <row r="72" spans="1:22">
       <c r="A72" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C72" s="2">
         <v>45804</v>
@@ -4919,19 +4941,19 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
       </c>
       <c r="G72" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H72" s="2">
         <v>45943</v>
       </c>
       <c r="I72" s="3">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="J72" t="s">
         <v>28</v>
@@ -4945,10 +4967,10 @@
     </row>
     <row r="73" spans="1:22">
       <c r="A73" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C73" s="2">
         <v>45513</v>
@@ -4957,25 +4979,25 @@
         <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F73" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G73" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H73" s="2">
         <v>45715</v>
       </c>
       <c r="I73" s="3">
-        <v>560</v>
+        <v>594</v>
       </c>
       <c r="J73" t="s">
         <v>38</v>
       </c>
       <c r="K73" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="L73" s="2">
         <v>45712</v>
@@ -4994,10 +5016,10 @@
     </row>
     <row r="74" spans="1:22">
       <c r="A74" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B74" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C74" s="2">
         <v>45659</v>
@@ -5006,25 +5028,25 @@
         <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F74" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G74" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H74" s="2">
         <v>45817</v>
       </c>
       <c r="I74" s="3">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="J74" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K74" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L74" s="2">
         <v>45812</v>
@@ -5036,7 +5058,7 @@
         <v>46909</v>
       </c>
       <c r="T74" s="3">
-        <v>634</v>
+        <v>600</v>
       </c>
       <c r="U74" s="3"/>
       <c r="V74" s="4">
@@ -5045,37 +5067,37 @@
     </row>
     <row r="75" spans="1:22">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C75" s="2">
         <v>45492</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E75" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F75" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G75" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H75" s="2">
         <v>45911</v>
       </c>
       <c r="I75" s="3">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="J75" t="s">
         <v>38</v>
       </c>
       <c r="K75" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L75" s="2">
         <v>45546</v>
@@ -5084,7 +5106,7 @@
         <v>54</v>
       </c>
       <c r="O75" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P75" s="2">
         <v>45966</v>
@@ -5100,28 +5122,28 @@
         <v>26</v>
       </c>
       <c r="B76" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C76" s="2">
         <v>45786</v>
       </c>
       <c r="D76" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E76" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F76" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G76" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H76" s="2">
         <v>45895</v>
       </c>
       <c r="I76" s="3">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="J76" t="s">
         <v>38</v>
@@ -5135,10 +5157,10 @@
     </row>
     <row r="77" spans="1:22">
       <c r="A77" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B77" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C77" s="2">
         <v>45946</v>
@@ -5147,19 +5169,19 @@
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F77" t="s">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="G77" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H77" s="2">
         <v>46196</v>
       </c>
       <c r="I77" s="3">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="J77" t="s">
         <v>28</v>
@@ -5173,10 +5195,10 @@
     </row>
     <row r="78" spans="1:22">
       <c r="A78" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B78" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C78" s="2">
         <v>45665</v>
@@ -5185,25 +5207,25 @@
         <v>35</v>
       </c>
       <c r="E78" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H78" s="2">
         <v>46198</v>
       </c>
       <c r="I78" s="3">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="J78" t="s">
         <v>38</v>
       </c>
       <c r="K78" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L78" s="2">
         <v>46071</v>
@@ -5212,7 +5234,7 @@
         <v>406</v>
       </c>
       <c r="O78" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P78" s="2">
         <v>46294</v>
@@ -5221,19 +5243,17 @@
         <v>46202</v>
       </c>
       <c r="T78" s="3"/>
-      <c r="U78" s="3">
-        <v>19</v>
-      </c>
+      <c r="U78" s="3"/>
       <c r="V78" s="4">
         <v>51071</v>
       </c>
     </row>
     <row r="79" spans="1:22">
       <c r="A79" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B79" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C79" s="2">
         <v>43902</v>
@@ -5242,25 +5262,25 @@
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F79" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G79" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H79" s="2">
         <v>45790</v>
       </c>
       <c r="I79" s="3">
-        <v>485</v>
+        <v>519</v>
       </c>
       <c r="J79" t="s">
         <v>38</v>
       </c>
       <c r="K79" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L79" s="2">
         <v>43964</v>
@@ -5269,7 +5289,7 @@
         <v>62</v>
       </c>
       <c r="O79" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P79" s="2">
         <v>46160</v>
@@ -5288,7 +5308,7 @@
         <v>26</v>
       </c>
       <c r="B80" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C80" s="2">
         <v>46210</v>
@@ -5297,22 +5317,22 @@
         <v>35</v>
       </c>
       <c r="E80" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F80" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="G80" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H80" s="2">
-        <v>46259</v>
+        <v>46302</v>
       </c>
       <c r="I80" s="3">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J80" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M80" s="3"/>
       <c r="T80" s="3"/>
@@ -5323,10 +5343,10 @@
     </row>
     <row r="81" spans="1:22">
       <c r="A81" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C81" s="2">
         <v>45915</v>
@@ -5335,25 +5355,25 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F81" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G81" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H81" s="2">
         <v>46094</v>
       </c>
       <c r="I81" s="3">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="J81" t="s">
         <v>38</v>
       </c>
       <c r="K81" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L81" s="2">
         <v>46086</v>
@@ -5365,7 +5385,7 @@
         <v>47181</v>
       </c>
       <c r="T81" s="3">
-        <v>906</v>
+        <v>872</v>
       </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4">
@@ -5374,37 +5394,37 @@
     </row>
     <row r="82" spans="1:22">
       <c r="A82" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C82" s="2">
         <v>45950</v>
       </c>
       <c r="D82" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E82" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F82" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G82" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H82" s="2">
         <v>45975</v>
       </c>
       <c r="I82" s="3">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="J82" t="s">
         <v>38</v>
       </c>
       <c r="K82" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L82" s="2">
         <v>45978</v>
@@ -5413,7 +5433,7 @@
         <v>28</v>
       </c>
       <c r="O82" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P82" s="2">
         <v>46220</v>
@@ -5429,10 +5449,10 @@
     </row>
     <row r="83" spans="1:22">
       <c r="A83" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C83" s="2">
         <v>45915</v>
@@ -5441,25 +5461,25 @@
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F83" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G83" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H83" s="2">
         <v>46241</v>
       </c>
       <c r="I83" s="3">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="J83" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K83" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L83" s="2">
         <v>46086</v>
@@ -5471,7 +5491,7 @@
         <v>47181</v>
       </c>
       <c r="T83" s="3">
-        <v>906</v>
+        <v>872</v>
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="4">
@@ -5480,10 +5500,10 @@
     </row>
     <row r="84" spans="1:22">
       <c r="A84" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B84" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C84" s="2">
         <v>45915</v>
@@ -5492,25 +5512,25 @@
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F84" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G84" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H84" s="2">
         <v>46094</v>
       </c>
       <c r="I84" s="3">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="J84" t="s">
         <v>38</v>
       </c>
       <c r="K84" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L84" s="2">
         <v>46086</v>
@@ -5522,7 +5542,7 @@
         <v>47181</v>
       </c>
       <c r="T84" s="3">
-        <v>906</v>
+        <v>872</v>
       </c>
       <c r="U84" s="3"/>
       <c r="V84" s="4">
@@ -5531,10 +5551,10 @@
     </row>
     <row r="85" spans="1:22">
       <c r="A85" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B85" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C85" s="2">
         <v>43902</v>
@@ -5543,25 +5563,25 @@
         <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F85" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G85" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H85" s="2">
         <v>45790</v>
       </c>
       <c r="I85" s="3">
-        <v>485</v>
+        <v>519</v>
       </c>
       <c r="J85" t="s">
         <v>38</v>
       </c>
       <c r="K85" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L85" s="2">
         <v>43964</v>
@@ -5570,7 +5590,7 @@
         <v>62</v>
       </c>
       <c r="O85" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P85" s="2">
         <v>46160</v>
@@ -5586,31 +5606,31 @@
     </row>
     <row r="86" spans="1:22">
       <c r="A86" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B86" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C86" s="2">
         <v>46260</v>
       </c>
       <c r="D86" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E86" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F86" t="s">
         <v>26</v>
       </c>
       <c r="G86" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H86" s="2">
         <v>46261</v>
       </c>
       <c r="I86" s="3">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="J86" t="s">
         <v>28</v>
@@ -5624,34 +5644,34 @@
     </row>
     <row r="87" spans="1:22">
       <c r="A87" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B87" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C87" s="2">
         <v>46266</v>
       </c>
       <c r="D87" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E87" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F87" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G87" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H87" s="2">
-        <v>46274</v>
+        <v>46304</v>
       </c>
       <c r="I87" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J87" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M87" s="3"/>
       <c r="T87" s="3"/>
@@ -5662,34 +5682,34 @@
     </row>
     <row r="88" spans="1:22">
       <c r="A88" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B88" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C88" s="2">
         <v>46245</v>
       </c>
       <c r="D88" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E88" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F88" t="s">
-        <v>308</v>
+        <v>186</v>
       </c>
       <c r="G88" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
       <c r="H88" s="2">
-        <v>46273</v>
+        <v>46304</v>
       </c>
       <c r="I88" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J88" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M88" s="3"/>
       <c r="T88" s="3"/>
@@ -5700,37 +5720,37 @@
     </row>
     <row r="89" spans="1:22">
       <c r="A89" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B89" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C89" s="2">
         <v>45819</v>
       </c>
       <c r="D89" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E89" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F89" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G89" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H89" s="2">
         <v>46170</v>
       </c>
       <c r="I89" s="3">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="J89" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K89" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L89" s="2">
         <v>45904</v>
@@ -5749,10 +5769,10 @@
     </row>
     <row r="90" spans="1:22">
       <c r="A90" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B90" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C90" s="2">
         <v>45952</v>
@@ -5761,25 +5781,25 @@
         <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F90" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H90" s="2">
         <v>46087</v>
       </c>
       <c r="I90" s="3">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="J90" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L90" s="2">
         <v>46086</v>
@@ -5791,7 +5811,7 @@
         <v>47910</v>
       </c>
       <c r="T90" s="3">
-        <v>1635</v>
+        <v>1601</v>
       </c>
       <c r="U90" s="3"/>
       <c r="V90" s="4">
@@ -5800,37 +5820,37 @@
     </row>
     <row r="91" spans="1:22">
       <c r="A91" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B91" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C91" s="2">
         <v>45775</v>
       </c>
       <c r="D91" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F91" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G91" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H91" s="2">
         <v>45861</v>
       </c>
       <c r="I91" s="3">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="J91" t="s">
         <v>38</v>
       </c>
       <c r="K91" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L91" s="2">
         <v>45856</v>
@@ -5849,31 +5869,31 @@
     </row>
     <row r="92" spans="1:22">
       <c r="A92" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C92" s="2">
         <v>45539</v>
       </c>
       <c r="D92" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E92" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F92" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G92" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H92" s="2">
         <v>45607</v>
       </c>
       <c r="I92" s="3">
-        <v>668</v>
+        <v>702</v>
       </c>
       <c r="J92" t="s">
         <v>38</v>
@@ -5887,10 +5907,10 @@
     </row>
     <row r="93" spans="1:22">
       <c r="A93" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B93" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C93" s="2">
         <v>45840</v>
@@ -5899,25 +5919,25 @@
         <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F93" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G93" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H93" s="2">
         <v>46002</v>
       </c>
       <c r="I93" s="3">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="J93" t="s">
         <v>38</v>
       </c>
       <c r="K93" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L93" s="2">
         <v>46001</v>
@@ -5929,7 +5949,7 @@
         <v>47097</v>
       </c>
       <c r="T93" s="3">
-        <v>822</v>
+        <v>788</v>
       </c>
       <c r="U93" s="3"/>
       <c r="V93" s="4">
@@ -5938,10 +5958,10 @@
     </row>
     <row r="94" spans="1:22">
       <c r="A94" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B94" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C94" s="2">
         <v>45868</v>
@@ -5950,25 +5970,25 @@
         <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F94" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G94" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="H94" s="2">
         <v>46146</v>
       </c>
       <c r="I94" s="3">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="J94" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K94" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L94" s="2">
         <v>46077</v>
@@ -5980,7 +6000,7 @@
         <v>47905</v>
       </c>
       <c r="T94" s="3">
-        <v>1630</v>
+        <v>1596</v>
       </c>
       <c r="U94" s="3"/>
       <c r="V94" s="4">
@@ -5989,10 +6009,10 @@
     </row>
     <row r="95" spans="1:22">
       <c r="A95" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B95" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C95" s="2">
         <v>44370</v>
@@ -6001,25 +6021,25 @@
         <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F95" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G95" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H95" s="2">
         <v>45881</v>
       </c>
       <c r="I95" s="3">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="J95" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K95" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L95" s="2">
         <v>44589</v>
@@ -6028,7 +6048,7 @@
         <v>219</v>
       </c>
       <c r="O95" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="P95" s="2">
         <v>46419</v>
@@ -6038,7 +6058,7 @@
       </c>
       <c r="T95" s="3"/>
       <c r="U95" s="3">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="V95" s="4">
         <v>374899.96</v>
@@ -6046,37 +6066,37 @@
     </row>
     <row r="96" spans="1:22">
       <c r="A96" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B96" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C96" s="2">
         <v>45422</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E96" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F96" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G96" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="H96" s="2">
         <v>45624</v>
       </c>
       <c r="I96" s="3">
-        <v>651</v>
+        <v>685</v>
       </c>
       <c r="J96" t="s">
         <v>38</v>
       </c>
       <c r="K96" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L96" s="2">
         <v>45544</v>
@@ -6098,31 +6118,31 @@
         <v>26</v>
       </c>
       <c r="B97" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C97" s="2">
         <v>46038</v>
       </c>
       <c r="D97" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E97" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F97" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G97" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H97" s="2">
         <v>46237</v>
       </c>
       <c r="I97" s="3">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="J97" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M97" s="3"/>
       <c r="T97" s="3"/>
@@ -6136,34 +6156,34 @@
         <v>29</v>
       </c>
       <c r="B98" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C98" s="2">
         <v>44939</v>
       </c>
       <c r="D98" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E98" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F98" t="s">
-        <v>29</v>
+        <v>385</v>
       </c>
       <c r="G98" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H98" s="2">
-        <v>46274</v>
+        <v>46303</v>
       </c>
       <c r="I98" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J98" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K98" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="L98" s="2">
         <v>45968</v>
@@ -6172,7 +6192,7 @@
         <v>1029</v>
       </c>
       <c r="O98" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="P98" s="2">
         <v>46426</v>
@@ -6182,7 +6202,7 @@
       </c>
       <c r="T98" s="3"/>
       <c r="U98" s="3">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="V98" s="4">
         <v>706431.6</v>
@@ -6190,10 +6210,10 @@
     </row>
     <row r="99" spans="1:22">
       <c r="A99" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B99" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C99" s="2">
         <v>45673</v>
@@ -6202,32 +6222,32 @@
         <v>24</v>
       </c>
       <c r="E99" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F99" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G99" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H99" s="2">
         <v>46140</v>
       </c>
       <c r="I99" s="3">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="J99" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K99" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M99" s="3"/>
       <c r="S99" s="2">
         <v>46598</v>
       </c>
       <c r="T99" s="3">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="U99" s="3"/>
       <c r="V99" s="4">
@@ -6236,34 +6256,34 @@
     </row>
     <row r="100" spans="1:22">
       <c r="A100" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B100" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C100" s="2">
         <v>46260</v>
       </c>
       <c r="D100" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E100" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F100" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="G100" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H100" s="2">
-        <v>46274</v>
+        <v>46304</v>
       </c>
       <c r="I100" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J100" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M100" s="3"/>
       <c r="T100" s="3"/>
@@ -6274,10 +6294,10 @@
     </row>
     <row r="101" spans="1:22">
       <c r="A101" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C101" s="2">
         <v>45215</v>
@@ -6286,25 +6306,25 @@
         <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F101" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G101" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H101" s="2">
         <v>45687</v>
       </c>
       <c r="I101" s="3">
-        <v>588</v>
+        <v>622</v>
       </c>
       <c r="J101" t="s">
         <v>38</v>
       </c>
       <c r="K101" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L101" s="2">
         <v>45685</v>
@@ -6316,7 +6336,7 @@
         <v>46780</v>
       </c>
       <c r="T101" s="3">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="U101" s="3"/>
       <c r="V101" s="4">
@@ -6325,37 +6345,37 @@
     </row>
     <row r="102" spans="1:22">
       <c r="A102" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C102" s="2">
         <v>45366</v>
       </c>
       <c r="D102" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E102" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F102" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G102" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H102" s="2">
         <v>45481</v>
       </c>
       <c r="I102" s="3">
-        <v>794</v>
+        <v>828</v>
       </c>
       <c r="J102" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K102" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="L102" s="2">
         <v>45471</v>
@@ -6367,7 +6387,7 @@
         <v>47301</v>
       </c>
       <c r="T102" s="3">
-        <v>1026</v>
+        <v>992</v>
       </c>
       <c r="U102" s="3"/>
       <c r="V102" s="4">
@@ -6379,34 +6399,34 @@
         <v>26</v>
       </c>
       <c r="B103" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C103" s="2">
         <v>45152</v>
       </c>
       <c r="D103" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E103" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F103" t="s">
         <v>29</v>
       </c>
       <c r="G103" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H103" s="2">
         <v>45440</v>
       </c>
       <c r="I103" s="3">
-        <v>835</v>
+        <v>869</v>
       </c>
       <c r="J103" t="s">
         <v>38</v>
       </c>
       <c r="K103" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="L103" s="2">
         <v>45303</v>
@@ -6425,37 +6445,37 @@
     </row>
     <row r="104" spans="1:22">
       <c r="A104" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B104" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C104" s="2">
         <v>45373</v>
       </c>
       <c r="D104" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E104" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F104" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G104" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H104" s="2">
         <v>45492</v>
       </c>
       <c r="I104" s="3">
-        <v>783</v>
+        <v>817</v>
       </c>
       <c r="J104" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K104" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="L104" s="2">
         <v>45492</v>
@@ -6467,7 +6487,7 @@
         <v>46587</v>
       </c>
       <c r="T104" s="3">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="U104" s="3"/>
       <c r="V104" s="4">
@@ -6476,10 +6496,10 @@
     </row>
     <row r="105" spans="1:22">
       <c r="A105" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B105" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C105" s="2">
         <v>44663</v>
@@ -6488,25 +6508,25 @@
         <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F105" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G105" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H105" s="2">
         <v>45588</v>
       </c>
       <c r="I105" s="3">
-        <v>687</v>
+        <v>721</v>
       </c>
       <c r="J105" t="s">
         <v>38</v>
       </c>
       <c r="K105" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L105" s="2">
         <v>44893</v>
@@ -6515,7 +6535,7 @@
         <v>230</v>
       </c>
       <c r="O105" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P105" s="2">
         <v>45996</v>
@@ -6531,10 +6551,10 @@
     </row>
     <row r="106" spans="1:22">
       <c r="A106" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B106" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C106" s="2">
         <v>45826</v>
@@ -6543,25 +6563,25 @@
         <v>24</v>
       </c>
       <c r="E106" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F106" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G106" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H106" s="2">
         <v>46079</v>
       </c>
       <c r="I106" s="3">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="J106" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K106" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="L106" s="2">
         <v>46076</v>
@@ -6573,7 +6593,7 @@
         <v>47903</v>
       </c>
       <c r="T106" s="3">
-        <v>1628</v>
+        <v>1594</v>
       </c>
       <c r="U106" s="3"/>
       <c r="V106" s="4">
@@ -6582,34 +6602,34 @@
     </row>
     <row r="107" spans="1:22">
       <c r="A107" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B107" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C107" s="2">
         <v>46150</v>
       </c>
       <c r="D107" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E107" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F107" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G107" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H107" s="2">
         <v>46206</v>
       </c>
       <c r="I107" s="3">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="J107" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M107" s="3"/>
       <c r="T107" s="3"/>
@@ -6620,34 +6640,34 @@
     </row>
     <row r="108" spans="1:22">
       <c r="A108" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B108" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C108" s="2">
         <v>46094</v>
       </c>
       <c r="D108" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E108" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F108" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G108" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H108" s="2">
         <v>46211</v>
       </c>
       <c r="I108" s="3">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="J108" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M108" s="3"/>
       <c r="T108" s="3"/>
@@ -6658,37 +6678,37 @@
     </row>
     <row r="109" spans="1:22">
       <c r="A109" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B109" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C109" s="2">
         <v>45950</v>
       </c>
       <c r="D109" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E109" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F109" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G109" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="H109" s="2">
         <v>45988</v>
       </c>
       <c r="I109" s="3">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="J109" t="s">
         <v>38</v>
       </c>
       <c r="K109" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="L109" s="2">
         <v>45979</v>
@@ -6700,7 +6720,7 @@
         <v>46343</v>
       </c>
       <c r="T109" s="3">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="U109" s="3"/>
       <c r="V109" s="4">
@@ -6709,10 +6729,10 @@
     </row>
     <row r="110" spans="1:22">
       <c r="A110" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B110" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C110" s="2">
         <v>45511</v>
@@ -6721,25 +6741,25 @@
         <v>24</v>
       </c>
       <c r="E110" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F110" t="s">
         <v>26</v>
       </c>
       <c r="G110" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="H110" s="2">
         <v>45786</v>
       </c>
       <c r="I110" s="3">
-        <v>489</v>
+        <v>523</v>
       </c>
       <c r="J110" t="s">
         <v>38</v>
       </c>
       <c r="K110" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="L110" s="2">
         <v>45794</v>
@@ -6758,7 +6778,7 @@
         <v>26</v>
       </c>
       <c r="B111" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C111" s="2">
         <v>45848</v>
@@ -6767,25 +6787,25 @@
         <v>35</v>
       </c>
       <c r="E111" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F111" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G111" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="H111" s="2">
         <v>46014</v>
       </c>
       <c r="I111" s="3">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="J111" t="s">
         <v>38</v>
       </c>
       <c r="K111" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L111" s="2">
         <v>46008</v>
@@ -6797,7 +6817,7 @@
         <v>46373</v>
       </c>
       <c r="T111" s="3">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="U111" s="3"/>
       <c r="V111" s="4">
@@ -6809,31 +6829,31 @@
         <v>26</v>
       </c>
       <c r="B112" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C112" s="2">
         <v>46030</v>
       </c>
       <c r="D112" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E112" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F112" t="s">
         <v>29</v>
       </c>
       <c r="G112" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H112" s="2">
         <v>46237</v>
       </c>
       <c r="I112" s="3">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="J112" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M112" s="3"/>
       <c r="T112" s="3"/>
@@ -6844,10 +6864,10 @@
     </row>
     <row r="113" spans="1:22">
       <c r="A113" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B113" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C113" s="2">
         <v>45365</v>
@@ -6856,25 +6876,25 @@
         <v>35</v>
       </c>
       <c r="E113" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F113" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G113" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H113" s="2">
         <v>45568</v>
       </c>
       <c r="I113" s="3">
-        <v>707</v>
+        <v>741</v>
       </c>
       <c r="J113" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K113" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="L113" s="2">
         <v>45567</v>
@@ -6886,7 +6906,7 @@
         <v>46479</v>
       </c>
       <c r="T113" s="3">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="U113" s="3"/>
       <c r="V113" s="4">
@@ -6895,34 +6915,34 @@
     </row>
     <row r="114" spans="1:22">
       <c r="A114" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B114" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C114" s="2">
         <v>46245</v>
       </c>
       <c r="D114" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E114" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F114" t="s">
-        <v>176</v>
+        <v>444</v>
       </c>
       <c r="G114" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="H114" s="2">
-        <v>46274</v>
+        <v>46304</v>
       </c>
       <c r="I114" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J114" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M114" s="3"/>
       <c r="T114" s="3"/>
@@ -6933,31 +6953,31 @@
     </row>
     <row r="115" spans="1:22">
       <c r="A115" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B115" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C115" s="2">
         <v>46232</v>
       </c>
       <c r="D115" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E115" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F115" t="s">
         <v>26</v>
       </c>
       <c r="G115" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="H115" s="2">
         <v>46237</v>
       </c>
       <c r="I115" s="3">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="J115" t="s">
         <v>28</v>
@@ -6974,7 +6994,7 @@
         <v>26</v>
       </c>
       <c r="B116" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C116" s="2">
         <v>45824</v>
@@ -6983,25 +7003,25 @@
         <v>24</v>
       </c>
       <c r="E116" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F116" t="s">
-        <v>446</v>
+        <v>165</v>
       </c>
       <c r="G116" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H116" s="2">
-        <v>46274</v>
+        <v>46297</v>
       </c>
       <c r="I116" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J116" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K116" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L116" s="2">
         <v>45951</v>
@@ -7010,13 +7030,13 @@
         <v>127</v>
       </c>
       <c r="O116" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S116" s="2">
         <v>46316</v>
       </c>
       <c r="T116" s="3">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="U116" s="3"/>
       <c r="V116" s="4">
@@ -7025,10 +7045,10 @@
     </row>
     <row r="117" spans="1:22">
       <c r="A117" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B117" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C117" s="2">
         <v>45526</v>
@@ -7037,32 +7057,32 @@
         <v>35</v>
       </c>
       <c r="E117" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F117" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G117" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H117" s="2">
         <v>45932</v>
       </c>
       <c r="I117" s="3">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="J117" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K117" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="M117" s="3"/>
       <c r="S117" s="2">
         <v>47748</v>
       </c>
       <c r="T117" s="3">
-        <v>1473</v>
+        <v>1439</v>
       </c>
       <c r="U117" s="3"/>
       <c r="V117" s="4">
@@ -7074,7 +7094,7 @@
         <v>26</v>
       </c>
       <c r="B118" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C118" s="2">
         <v>45560</v>
@@ -7083,25 +7103,25 @@
         <v>24</v>
       </c>
       <c r="E118" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F118" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G118" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H118" s="2">
         <v>45930</v>
       </c>
       <c r="I118" s="3">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="J118" t="s">
         <v>38</v>
       </c>
       <c r="K118" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="L118" s="2">
         <v>45854</v>
@@ -7113,7 +7133,7 @@
         <v>46950</v>
       </c>
       <c r="T118" s="3">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="U118" s="3"/>
       <c r="V118" s="4">
@@ -7122,37 +7142,37 @@
     </row>
     <row r="119" spans="1:22">
       <c r="A119" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B119" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C119" s="2">
         <v>44607</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E119" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F119" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G119" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="H119" s="2">
         <v>46196</v>
       </c>
       <c r="I119" s="3">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="J119" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K119" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="L119" s="2">
         <v>44747</v>
@@ -7161,7 +7181,7 @@
         <v>140</v>
       </c>
       <c r="O119" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="P119" s="2">
         <v>46573</v>
@@ -7171,7 +7191,7 @@
       </c>
       <c r="T119" s="3"/>
       <c r="U119" s="3">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="V119" s="4">
         <v>6571898.25</v>
@@ -7179,10 +7199,10 @@
     </row>
     <row r="120" spans="1:22">
       <c r="A120" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B120" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C120" s="2">
         <v>38661</v>
@@ -7191,25 +7211,25 @@
         <v>35</v>
       </c>
       <c r="E120" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F120" t="s">
         <v>26</v>
       </c>
       <c r="G120" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H120" s="2">
         <v>45993</v>
       </c>
       <c r="I120" s="3">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="J120" t="s">
         <v>38</v>
       </c>
       <c r="K120" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="L120" s="2">
         <v>45993</v>
@@ -7221,7 +7241,7 @@
         <v>46540</v>
       </c>
       <c r="T120" s="3">
-        <v>265</v>
+        <v>231</v>
       </c>
       <c r="U120" s="3"/>
       <c r="V120" s="4">
@@ -7230,10 +7250,10 @@
     </row>
     <row r="121" spans="1:22">
       <c r="A121" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B121" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C121" s="2">
         <v>45560</v>
@@ -7242,32 +7262,32 @@
         <v>24</v>
       </c>
       <c r="E121" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F121" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G121" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="H121" s="2">
         <v>45797</v>
       </c>
       <c r="I121" s="3">
-        <v>478</v>
+        <v>512</v>
       </c>
       <c r="J121" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K121" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M121" s="3"/>
       <c r="S121" s="2">
         <v>46523</v>
       </c>
       <c r="T121" s="3">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="U121" s="3"/>
       <c r="V121" s="4">
@@ -7276,10 +7296,10 @@
     </row>
     <row r="122" spans="1:22">
       <c r="A122" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B122" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C122" s="2">
         <v>44763</v>
@@ -7288,25 +7308,25 @@
         <v>24</v>
       </c>
       <c r="E122" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F122" t="s">
-        <v>446</v>
+        <v>75</v>
       </c>
       <c r="G122" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="H122" s="2">
-        <v>46266</v>
+        <v>46308</v>
       </c>
       <c r="I122" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J122" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K122" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="L122" s="2">
         <v>45574</v>
@@ -7315,13 +7335,13 @@
         <v>811</v>
       </c>
       <c r="O122" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="P122" s="2">
         <v>46313</v>
       </c>
       <c r="Q122" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R122" s="2">
         <v>46073</v>
@@ -7331,7 +7351,7 @@
       </c>
       <c r="T122" s="3"/>
       <c r="U122" s="3">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="V122" s="4">
         <v>10934411.34</v>
@@ -7342,34 +7362,34 @@
         <v>26</v>
       </c>
       <c r="B123" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C123" s="2">
         <v>45014</v>
       </c>
       <c r="D123" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E123" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F123" t="s">
         <v>26</v>
       </c>
       <c r="G123" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H123" s="2">
         <v>46219</v>
       </c>
       <c r="I123" s="3">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="J123" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K123" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L123" s="2">
         <v>45148</v>
@@ -7378,7 +7398,7 @@
         <v>134</v>
       </c>
       <c r="O123" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="P123" s="2">
         <v>46609</v>
@@ -7388,7 +7408,7 @@
       </c>
       <c r="T123" s="3"/>
       <c r="U123" s="3">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="V123" s="4">
         <v>17946403.739999998</v>
@@ -7396,34 +7416,34 @@
     </row>
     <row r="124" spans="1:22">
       <c r="A124" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B124" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C124" s="2">
         <v>45666</v>
       </c>
       <c r="D124" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E124" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F124" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G124" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H124" s="2">
         <v>46174</v>
       </c>
       <c r="I124" s="3">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="J124" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M124" s="3"/>
       <c r="T124" s="3"/>
@@ -7434,10 +7454,10 @@
     </row>
     <row r="125" spans="1:22">
       <c r="A125" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B125" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C125" s="2">
         <v>45250</v>
@@ -7446,25 +7466,25 @@
         <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F125" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G125" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="H125" s="2">
         <v>45400</v>
       </c>
       <c r="I125" s="3">
-        <v>875</v>
+        <v>909</v>
       </c>
       <c r="J125" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K125" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L125" s="2">
         <v>45401</v>
@@ -7476,7 +7496,7 @@
         <v>47227</v>
       </c>
       <c r="T125" s="3">
-        <v>952</v>
+        <v>918</v>
       </c>
       <c r="U125" s="3"/>
       <c r="V125" s="4">
@@ -7485,10 +7505,10 @@
     </row>
     <row r="126" spans="1:22">
       <c r="A126" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B126" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C126" s="2">
         <v>44238</v>
@@ -7497,25 +7517,25 @@
         <v>24</v>
       </c>
       <c r="E126" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F126" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G126" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H126" s="2">
         <v>46211</v>
       </c>
       <c r="I126" s="3">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="J126" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K126" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L126" s="2">
         <v>44969</v>
@@ -7524,7 +7544,7 @@
         <v>731</v>
       </c>
       <c r="O126" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="P126" s="2">
         <v>46798</v>
@@ -7534,7 +7554,7 @@
       </c>
       <c r="T126" s="3"/>
       <c r="U126" s="3">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="V126" s="4">
         <v>41936400</v>
@@ -7542,10 +7562,10 @@
     </row>
     <row r="127" spans="1:22">
       <c r="A127" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B127" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C127" s="2">
         <v>45607</v>
@@ -7554,25 +7574,25 @@
         <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F127" t="s">
-        <v>446</v>
+        <v>137</v>
       </c>
       <c r="G127" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H127" s="2">
-        <v>46274</v>
+        <v>46302</v>
       </c>
       <c r="I127" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J127" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K127" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L127" s="2">
         <v>45798</v>
@@ -7584,7 +7604,7 @@
         <v>46712</v>
       </c>
       <c r="T127" s="3">
-        <v>437</v>
+        <v>403</v>
       </c>
       <c r="U127" s="3"/>
       <c r="V127" s="4">
@@ -7593,10 +7613,10 @@
     </row>
     <row r="128" spans="1:22">
       <c r="A128" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B128" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C128" s="2">
         <v>45664</v>
@@ -7605,19 +7625,19 @@
         <v>24</v>
       </c>
       <c r="E128" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F128" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G128" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="H128" s="2">
         <v>45958</v>
       </c>
       <c r="I128" s="3">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="J128" t="s">
         <v>28</v>
